--- a/frontend/public/Mau_nhap_nhan_vien_AsiaPortal.xlsx
+++ b/frontend/public/Mau_nhap_nhan_vien_AsiaPortal.xlsx
@@ -25,10 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -78,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -87,9 +84,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -574,8 +568,8 @@
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="2" t="n"/>
@@ -590,8 +584,8 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="2" t="n"/>
@@ -606,8 +600,8 @@
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="2" t="n"/>
@@ -622,8 +616,8 @@
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="2" t="n"/>
@@ -638,8 +632,8 @@
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="2" t="n"/>
@@ -654,8 +648,8 @@
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="2" t="n"/>
@@ -670,8 +664,8 @@
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="2" t="n"/>
@@ -686,8 +680,8 @@
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="2" t="n"/>
@@ -702,8 +696,8 @@
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="2" t="n"/>
@@ -718,8 +712,8 @@
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="2" t="n"/>
@@ -734,8 +728,8 @@
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="2" t="n"/>
@@ -750,8 +744,8 @@
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="2" t="n"/>
@@ -766,8 +760,8 @@
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="2" t="n"/>
@@ -782,8 +776,8 @@
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="2" t="n"/>
@@ -798,8 +792,8 @@
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="2" t="n"/>
@@ -814,8 +808,8 @@
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="2" t="n"/>
@@ -830,8 +824,8 @@
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="2" t="n"/>
@@ -846,8 +840,8 @@
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="2" t="n"/>
@@ -862,8 +856,8 @@
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="2" t="n"/>
@@ -878,8 +872,8 @@
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="2" t="n"/>
@@ -894,8 +888,8 @@
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="2" t="n"/>
@@ -910,8 +904,8 @@
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="2" t="n"/>
@@ -926,8 +920,8 @@
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="2" t="n"/>
@@ -942,8 +936,8 @@
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="2" t="n"/>
@@ -958,8 +952,8 @@
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="2" t="n"/>
@@ -974,8 +968,8 @@
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="2" t="n"/>
@@ -990,8 +984,8 @@
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="2" t="n"/>
@@ -1006,8 +1000,8 @@
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="2" t="n"/>
@@ -1022,8 +1016,8 @@
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="2" t="n"/>
@@ -1038,8 +1032,8 @@
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="2" t="n"/>
@@ -1054,8 +1048,8 @@
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="2" t="n"/>
@@ -1070,8 +1064,8 @@
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="2" t="n"/>
@@ -1086,8 +1080,8 @@
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="2" t="n"/>
@@ -1102,8 +1096,8 @@
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="2" t="n"/>
@@ -1118,8 +1112,8 @@
       <c r="D36" s="3" t="n"/>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="2" t="n"/>
@@ -1134,8 +1128,8 @@
       <c r="D37" s="3" t="n"/>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="2" t="n"/>
@@ -1150,8 +1144,8 @@
       <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="2" t="n"/>
@@ -1166,8 +1160,8 @@
       <c r="D39" s="3" t="n"/>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="2" t="n"/>
@@ -1182,8 +1176,8 @@
       <c r="D40" s="3" t="n"/>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="2" t="n"/>
@@ -1198,8 +1192,8 @@
       <c r="D41" s="3" t="n"/>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="2" t="n"/>
@@ -1214,8 +1208,8 @@
       <c r="D42" s="3" t="n"/>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="2" t="n"/>
@@ -1230,8 +1224,8 @@
       <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="2" t="n"/>
@@ -1246,8 +1240,8 @@
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
       <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="2" t="n"/>
@@ -1262,8 +1256,8 @@
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="2" t="n"/>
@@ -1278,8 +1272,8 @@
       <c r="D46" s="3" t="n"/>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="2" t="n"/>
@@ -1294,8 +1288,8 @@
       <c r="D47" s="3" t="n"/>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n"/>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
       <c r="I47" s="3" t="n"/>
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="2" t="n"/>
@@ -1310,8 +1304,8 @@
       <c r="D48" s="3" t="n"/>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
       <c r="I48" s="3" t="n"/>
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="2" t="n"/>
@@ -1326,8 +1320,8 @@
       <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n"/>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
       <c r="I49" s="3" t="n"/>
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="2" t="n"/>
@@ -1342,8 +1336,8 @@
       <c r="D50" s="3" t="n"/>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
       <c r="I50" s="3" t="n"/>
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="2" t="n"/>
@@ -1358,8 +1352,8 @@
       <c r="D51" s="3" t="n"/>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
       <c r="I51" s="3" t="n"/>
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="2" t="n"/>
@@ -1374,8 +1368,8 @@
       <c r="D52" s="3" t="n"/>
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
       <c r="I52" s="3" t="n"/>
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="2" t="n"/>
@@ -1390,8 +1384,8 @@
       <c r="D53" s="3" t="n"/>
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
       <c r="I53" s="3" t="n"/>
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="2" t="n"/>
@@ -1406,8 +1400,8 @@
       <c r="D54" s="3" t="n"/>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
       <c r="I54" s="3" t="n"/>
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="2" t="n"/>
@@ -1422,8 +1416,8 @@
       <c r="D55" s="3" t="n"/>
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="n"/>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
       <c r="I55" s="3" t="n"/>
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="2" t="n"/>
@@ -1438,8 +1432,8 @@
       <c r="D56" s="3" t="n"/>
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
       <c r="I56" s="3" t="n"/>
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="2" t="n"/>
@@ -1454,8 +1448,8 @@
       <c r="D57" s="3" t="n"/>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="n"/>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
       <c r="I57" s="3" t="n"/>
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="2" t="n"/>
@@ -1470,8 +1464,8 @@
       <c r="D58" s="3" t="n"/>
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
       <c r="I58" s="3" t="n"/>
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="2" t="n"/>
@@ -1486,8 +1480,8 @@
       <c r="D59" s="3" t="n"/>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>
-      <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
       <c r="I59" s="3" t="n"/>
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="2" t="n"/>
@@ -1502,8 +1496,8 @@
       <c r="D60" s="3" t="n"/>
       <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="n"/>
-      <c r="G60" s="4" t="n"/>
-      <c r="H60" s="4" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
       <c r="I60" s="3" t="n"/>
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="2" t="n"/>
@@ -1518,8 +1512,8 @@
       <c r="D61" s="3" t="n"/>
       <c r="E61" s="3" t="n"/>
       <c r="F61" s="3" t="n"/>
-      <c r="G61" s="4" t="n"/>
-      <c r="H61" s="4" t="n"/>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="n"/>
       <c r="I61" s="3" t="n"/>
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="2" t="n"/>
@@ -1534,8 +1528,8 @@
       <c r="D62" s="3" t="n"/>
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="n"/>
-      <c r="G62" s="4" t="n"/>
-      <c r="H62" s="4" t="n"/>
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="n"/>
       <c r="I62" s="3" t="n"/>
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="2" t="n"/>
@@ -1550,8 +1544,8 @@
       <c r="D63" s="3" t="n"/>
       <c r="E63" s="3" t="n"/>
       <c r="F63" s="3" t="n"/>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n"/>
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="n"/>
       <c r="I63" s="3" t="n"/>
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="2" t="n"/>
@@ -1566,8 +1560,8 @@
       <c r="D64" s="3" t="n"/>
       <c r="E64" s="3" t="n"/>
       <c r="F64" s="3" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="n"/>
       <c r="I64" s="3" t="n"/>
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="2" t="n"/>
@@ -1582,8 +1576,8 @@
       <c r="D65" s="3" t="n"/>
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="n"/>
-      <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="n"/>
       <c r="I65" s="3" t="n"/>
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="2" t="n"/>
@@ -1598,8 +1592,8 @@
       <c r="D66" s="3" t="n"/>
       <c r="E66" s="3" t="n"/>
       <c r="F66" s="3" t="n"/>
-      <c r="G66" s="4" t="n"/>
-      <c r="H66" s="4" t="n"/>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="n"/>
       <c r="I66" s="3" t="n"/>
       <c r="J66" s="3" t="n"/>
       <c r="K66" s="2" t="n"/>
@@ -1614,8 +1608,8 @@
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="n"/>
-      <c r="G67" s="4" t="n"/>
-      <c r="H67" s="4" t="n"/>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="n"/>
       <c r="I67" s="3" t="n"/>
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="2" t="n"/>
@@ -1630,8 +1624,8 @@
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="3" t="n"/>
       <c r="F68" s="3" t="n"/>
-      <c r="G68" s="4" t="n"/>
-      <c r="H68" s="4" t="n"/>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
       <c r="I68" s="3" t="n"/>
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="2" t="n"/>
@@ -1646,8 +1640,8 @@
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="n"/>
-      <c r="G69" s="4" t="n"/>
-      <c r="H69" s="4" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
       <c r="I69" s="3" t="n"/>
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="2" t="n"/>
@@ -1662,8 +1656,8 @@
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="3" t="n"/>
       <c r="F70" s="3" t="n"/>
-      <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="n"/>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="n"/>
       <c r="I70" s="3" t="n"/>
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="2" t="n"/>
@@ -1678,8 +1672,8 @@
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="3" t="n"/>
       <c r="F71" s="3" t="n"/>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n"/>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="n"/>
       <c r="I71" s="3" t="n"/>
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="2" t="n"/>
@@ -1694,8 +1688,8 @@
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="3" t="n"/>
       <c r="F72" s="3" t="n"/>
-      <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="n"/>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="n"/>
       <c r="I72" s="3" t="n"/>
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="2" t="n"/>
@@ -1710,8 +1704,8 @@
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="3" t="n"/>
       <c r="F73" s="3" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="n"/>
       <c r="I73" s="3" t="n"/>
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="2" t="n"/>
@@ -1726,8 +1720,8 @@
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="3" t="n"/>
       <c r="F74" s="3" t="n"/>
-      <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n"/>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="n"/>
       <c r="I74" s="3" t="n"/>
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="2" t="n"/>
@@ -1742,8 +1736,8 @@
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="3" t="n"/>
       <c r="F75" s="3" t="n"/>
-      <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="n"/>
       <c r="I75" s="3" t="n"/>
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="2" t="n"/>
@@ -1758,8 +1752,8 @@
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="3" t="n"/>
-      <c r="G76" s="4" t="n"/>
-      <c r="H76" s="4" t="n"/>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="n"/>
       <c r="I76" s="3" t="n"/>
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="2" t="n"/>
@@ -1774,8 +1768,8 @@
       <c r="D77" s="3" t="n"/>
       <c r="E77" s="3" t="n"/>
       <c r="F77" s="3" t="n"/>
-      <c r="G77" s="4" t="n"/>
-      <c r="H77" s="4" t="n"/>
+      <c r="G77" s="2" t="n"/>
+      <c r="H77" s="2" t="n"/>
       <c r="I77" s="3" t="n"/>
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="2" t="n"/>
@@ -1790,8 +1784,8 @@
       <c r="D78" s="3" t="n"/>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n"/>
-      <c r="G78" s="4" t="n"/>
-      <c r="H78" s="4" t="n"/>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="n"/>
       <c r="I78" s="3" t="n"/>
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="2" t="n"/>
@@ -1806,8 +1800,8 @@
       <c r="D79" s="3" t="n"/>
       <c r="E79" s="3" t="n"/>
       <c r="F79" s="3" t="n"/>
-      <c r="G79" s="4" t="n"/>
-      <c r="H79" s="4" t="n"/>
+      <c r="G79" s="2" t="n"/>
+      <c r="H79" s="2" t="n"/>
       <c r="I79" s="3" t="n"/>
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="2" t="n"/>
@@ -1822,8 +1816,8 @@
       <c r="D80" s="3" t="n"/>
       <c r="E80" s="3" t="n"/>
       <c r="F80" s="3" t="n"/>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="n"/>
       <c r="I80" s="3" t="n"/>
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="2" t="n"/>
@@ -1838,8 +1832,8 @@
       <c r="D81" s="3" t="n"/>
       <c r="E81" s="3" t="n"/>
       <c r="F81" s="3" t="n"/>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
+      <c r="G81" s="2" t="n"/>
+      <c r="H81" s="2" t="n"/>
       <c r="I81" s="3" t="n"/>
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="2" t="n"/>
@@ -1854,8 +1848,8 @@
       <c r="D82" s="3" t="n"/>
       <c r="E82" s="3" t="n"/>
       <c r="F82" s="3" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
+      <c r="G82" s="2" t="n"/>
+      <c r="H82" s="2" t="n"/>
       <c r="I82" s="3" t="n"/>
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="2" t="n"/>
@@ -1870,8 +1864,8 @@
       <c r="D83" s="3" t="n"/>
       <c r="E83" s="3" t="n"/>
       <c r="F83" s="3" t="n"/>
-      <c r="G83" s="4" t="n"/>
-      <c r="H83" s="4" t="n"/>
+      <c r="G83" s="2" t="n"/>
+      <c r="H83" s="2" t="n"/>
       <c r="I83" s="3" t="n"/>
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="2" t="n"/>
@@ -1886,8 +1880,8 @@
       <c r="D84" s="3" t="n"/>
       <c r="E84" s="3" t="n"/>
       <c r="F84" s="3" t="n"/>
-      <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="n"/>
       <c r="I84" s="3" t="n"/>
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="2" t="n"/>
@@ -1902,8 +1896,8 @@
       <c r="D85" s="3" t="n"/>
       <c r="E85" s="3" t="n"/>
       <c r="F85" s="3" t="n"/>
-      <c r="G85" s="4" t="n"/>
-      <c r="H85" s="4" t="n"/>
+      <c r="G85" s="2" t="n"/>
+      <c r="H85" s="2" t="n"/>
       <c r="I85" s="3" t="n"/>
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="2" t="n"/>
@@ -1918,8 +1912,8 @@
       <c r="D86" s="3" t="n"/>
       <c r="E86" s="3" t="n"/>
       <c r="F86" s="3" t="n"/>
-      <c r="G86" s="4" t="n"/>
-      <c r="H86" s="4" t="n"/>
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="n"/>
       <c r="I86" s="3" t="n"/>
       <c r="J86" s="3" t="n"/>
       <c r="K86" s="2" t="n"/>
@@ -1934,8 +1928,8 @@
       <c r="D87" s="3" t="n"/>
       <c r="E87" s="3" t="n"/>
       <c r="F87" s="3" t="n"/>
-      <c r="G87" s="4" t="n"/>
-      <c r="H87" s="4" t="n"/>
+      <c r="G87" s="2" t="n"/>
+      <c r="H87" s="2" t="n"/>
       <c r="I87" s="3" t="n"/>
       <c r="J87" s="3" t="n"/>
       <c r="K87" s="2" t="n"/>
@@ -1950,8 +1944,8 @@
       <c r="D88" s="3" t="n"/>
       <c r="E88" s="3" t="n"/>
       <c r="F88" s="3" t="n"/>
-      <c r="G88" s="4" t="n"/>
-      <c r="H88" s="4" t="n"/>
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="n"/>
       <c r="I88" s="3" t="n"/>
       <c r="J88" s="3" t="n"/>
       <c r="K88" s="2" t="n"/>
@@ -1966,8 +1960,8 @@
       <c r="D89" s="3" t="n"/>
       <c r="E89" s="3" t="n"/>
       <c r="F89" s="3" t="n"/>
-      <c r="G89" s="4" t="n"/>
-      <c r="H89" s="4" t="n"/>
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="n"/>
       <c r="I89" s="3" t="n"/>
       <c r="J89" s="3" t="n"/>
       <c r="K89" s="2" t="n"/>
@@ -1982,8 +1976,8 @@
       <c r="D90" s="3" t="n"/>
       <c r="E90" s="3" t="n"/>
       <c r="F90" s="3" t="n"/>
-      <c r="G90" s="4" t="n"/>
-      <c r="H90" s="4" t="n"/>
+      <c r="G90" s="2" t="n"/>
+      <c r="H90" s="2" t="n"/>
       <c r="I90" s="3" t="n"/>
       <c r="J90" s="3" t="n"/>
       <c r="K90" s="2" t="n"/>
@@ -1998,8 +1992,8 @@
       <c r="D91" s="3" t="n"/>
       <c r="E91" s="3" t="n"/>
       <c r="F91" s="3" t="n"/>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="n"/>
+      <c r="G91" s="2" t="n"/>
+      <c r="H91" s="2" t="n"/>
       <c r="I91" s="3" t="n"/>
       <c r="J91" s="3" t="n"/>
       <c r="K91" s="2" t="n"/>
@@ -2014,8 +2008,8 @@
       <c r="D92" s="3" t="n"/>
       <c r="E92" s="3" t="n"/>
       <c r="F92" s="3" t="n"/>
-      <c r="G92" s="4" t="n"/>
-      <c r="H92" s="4" t="n"/>
+      <c r="G92" s="2" t="n"/>
+      <c r="H92" s="2" t="n"/>
       <c r="I92" s="3" t="n"/>
       <c r="J92" s="3" t="n"/>
       <c r="K92" s="2" t="n"/>
@@ -2030,8 +2024,8 @@
       <c r="D93" s="3" t="n"/>
       <c r="E93" s="3" t="n"/>
       <c r="F93" s="3" t="n"/>
-      <c r="G93" s="4" t="n"/>
-      <c r="H93" s="4" t="n"/>
+      <c r="G93" s="2" t="n"/>
+      <c r="H93" s="2" t="n"/>
       <c r="I93" s="3" t="n"/>
       <c r="J93" s="3" t="n"/>
       <c r="K93" s="2" t="n"/>
@@ -2046,8 +2040,8 @@
       <c r="D94" s="3" t="n"/>
       <c r="E94" s="3" t="n"/>
       <c r="F94" s="3" t="n"/>
-      <c r="G94" s="4" t="n"/>
-      <c r="H94" s="4" t="n"/>
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="n"/>
       <c r="I94" s="3" t="n"/>
       <c r="J94" s="3" t="n"/>
       <c r="K94" s="2" t="n"/>
@@ -2062,8 +2056,8 @@
       <c r="D95" s="3" t="n"/>
       <c r="E95" s="3" t="n"/>
       <c r="F95" s="3" t="n"/>
-      <c r="G95" s="4" t="n"/>
-      <c r="H95" s="4" t="n"/>
+      <c r="G95" s="2" t="n"/>
+      <c r="H95" s="2" t="n"/>
       <c r="I95" s="3" t="n"/>
       <c r="J95" s="3" t="n"/>
       <c r="K95" s="2" t="n"/>
@@ -2078,8 +2072,8 @@
       <c r="D96" s="3" t="n"/>
       <c r="E96" s="3" t="n"/>
       <c r="F96" s="3" t="n"/>
-      <c r="G96" s="4" t="n"/>
-      <c r="H96" s="4" t="n"/>
+      <c r="G96" s="2" t="n"/>
+      <c r="H96" s="2" t="n"/>
       <c r="I96" s="3" t="n"/>
       <c r="J96" s="3" t="n"/>
       <c r="K96" s="2" t="n"/>
@@ -2094,8 +2088,8 @@
       <c r="D97" s="3" t="n"/>
       <c r="E97" s="3" t="n"/>
       <c r="F97" s="3" t="n"/>
-      <c r="G97" s="4" t="n"/>
-      <c r="H97" s="4" t="n"/>
+      <c r="G97" s="2" t="n"/>
+      <c r="H97" s="2" t="n"/>
       <c r="I97" s="3" t="n"/>
       <c r="J97" s="3" t="n"/>
       <c r="K97" s="2" t="n"/>
@@ -2110,8 +2104,8 @@
       <c r="D98" s="3" t="n"/>
       <c r="E98" s="3" t="n"/>
       <c r="F98" s="3" t="n"/>
-      <c r="G98" s="4" t="n"/>
-      <c r="H98" s="4" t="n"/>
+      <c r="G98" s="2" t="n"/>
+      <c r="H98" s="2" t="n"/>
       <c r="I98" s="3" t="n"/>
       <c r="J98" s="3" t="n"/>
       <c r="K98" s="2" t="n"/>
@@ -2126,8 +2120,8 @@
       <c r="D99" s="3" t="n"/>
       <c r="E99" s="3" t="n"/>
       <c r="F99" s="3" t="n"/>
-      <c r="G99" s="4" t="n"/>
-      <c r="H99" s="4" t="n"/>
+      <c r="G99" s="2" t="n"/>
+      <c r="H99" s="2" t="n"/>
       <c r="I99" s="3" t="n"/>
       <c r="J99" s="3" t="n"/>
       <c r="K99" s="2" t="n"/>
@@ -2142,8 +2136,8 @@
       <c r="D100" s="3" t="n"/>
       <c r="E100" s="3" t="n"/>
       <c r="F100" s="3" t="n"/>
-      <c r="G100" s="4" t="n"/>
-      <c r="H100" s="4" t="n"/>
+      <c r="G100" s="2" t="n"/>
+      <c r="H100" s="2" t="n"/>
       <c r="I100" s="3" t="n"/>
       <c r="J100" s="3" t="n"/>
       <c r="K100" s="2" t="n"/>
@@ -2158,8 +2152,8 @@
       <c r="D101" s="3" t="n"/>
       <c r="E101" s="3" t="n"/>
       <c r="F101" s="3" t="n"/>
-      <c r="G101" s="4" t="n"/>
-      <c r="H101" s="4" t="n"/>
+      <c r="G101" s="2" t="n"/>
+      <c r="H101" s="2" t="n"/>
       <c r="I101" s="3" t="n"/>
       <c r="J101" s="3" t="n"/>
       <c r="K101" s="2" t="n"/>
@@ -2174,8 +2168,8 @@
       <c r="D102" s="3" t="n"/>
       <c r="E102" s="3" t="n"/>
       <c r="F102" s="3" t="n"/>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="n"/>
+      <c r="G102" s="2" t="n"/>
+      <c r="H102" s="2" t="n"/>
       <c r="I102" s="3" t="n"/>
       <c r="J102" s="3" t="n"/>
       <c r="K102" s="2" t="n"/>
@@ -2190,8 +2184,8 @@
       <c r="D103" s="3" t="n"/>
       <c r="E103" s="3" t="n"/>
       <c r="F103" s="3" t="n"/>
-      <c r="G103" s="4" t="n"/>
-      <c r="H103" s="4" t="n"/>
+      <c r="G103" s="2" t="n"/>
+      <c r="H103" s="2" t="n"/>
       <c r="I103" s="3" t="n"/>
       <c r="J103" s="3" t="n"/>
       <c r="K103" s="2" t="n"/>
@@ -2206,8 +2200,8 @@
       <c r="D104" s="3" t="n"/>
       <c r="E104" s="3" t="n"/>
       <c r="F104" s="3" t="n"/>
-      <c r="G104" s="4" t="n"/>
-      <c r="H104" s="4" t="n"/>
+      <c r="G104" s="2" t="n"/>
+      <c r="H104" s="2" t="n"/>
       <c r="I104" s="3" t="n"/>
       <c r="J104" s="3" t="n"/>
       <c r="K104" s="2" t="n"/>
@@ -2222,8 +2216,8 @@
       <c r="D105" s="3" t="n"/>
       <c r="E105" s="3" t="n"/>
       <c r="F105" s="3" t="n"/>
-      <c r="G105" s="4" t="n"/>
-      <c r="H105" s="4" t="n"/>
+      <c r="G105" s="2" t="n"/>
+      <c r="H105" s="2" t="n"/>
       <c r="I105" s="3" t="n"/>
       <c r="J105" s="3" t="n"/>
       <c r="K105" s="2" t="n"/>
@@ -2238,8 +2232,8 @@
       <c r="D106" s="3" t="n"/>
       <c r="E106" s="3" t="n"/>
       <c r="F106" s="3" t="n"/>
-      <c r="G106" s="4" t="n"/>
-      <c r="H106" s="4" t="n"/>
+      <c r="G106" s="2" t="n"/>
+      <c r="H106" s="2" t="n"/>
       <c r="I106" s="3" t="n"/>
       <c r="J106" s="3" t="n"/>
       <c r="K106" s="2" t="n"/>
@@ -2254,8 +2248,8 @@
       <c r="D107" s="3" t="n"/>
       <c r="E107" s="3" t="n"/>
       <c r="F107" s="3" t="n"/>
-      <c r="G107" s="4" t="n"/>
-      <c r="H107" s="4" t="n"/>
+      <c r="G107" s="2" t="n"/>
+      <c r="H107" s="2" t="n"/>
       <c r="I107" s="3" t="n"/>
       <c r="J107" s="3" t="n"/>
       <c r="K107" s="2" t="n"/>
@@ -2270,8 +2264,8 @@
       <c r="D108" s="3" t="n"/>
       <c r="E108" s="3" t="n"/>
       <c r="F108" s="3" t="n"/>
-      <c r="G108" s="4" t="n"/>
-      <c r="H108" s="4" t="n"/>
+      <c r="G108" s="2" t="n"/>
+      <c r="H108" s="2" t="n"/>
       <c r="I108" s="3" t="n"/>
       <c r="J108" s="3" t="n"/>
       <c r="K108" s="2" t="n"/>
@@ -2286,8 +2280,8 @@
       <c r="D109" s="3" t="n"/>
       <c r="E109" s="3" t="n"/>
       <c r="F109" s="3" t="n"/>
-      <c r="G109" s="4" t="n"/>
-      <c r="H109" s="4" t="n"/>
+      <c r="G109" s="2" t="n"/>
+      <c r="H109" s="2" t="n"/>
       <c r="I109" s="3" t="n"/>
       <c r="J109" s="3" t="n"/>
       <c r="K109" s="2" t="n"/>
@@ -2302,8 +2296,8 @@
       <c r="D110" s="3" t="n"/>
       <c r="E110" s="3" t="n"/>
       <c r="F110" s="3" t="n"/>
-      <c r="G110" s="4" t="n"/>
-      <c r="H110" s="4" t="n"/>
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="n"/>
       <c r="I110" s="3" t="n"/>
       <c r="J110" s="3" t="n"/>
       <c r="K110" s="2" t="n"/>
@@ -2318,8 +2312,8 @@
       <c r="D111" s="3" t="n"/>
       <c r="E111" s="3" t="n"/>
       <c r="F111" s="3" t="n"/>
-      <c r="G111" s="4" t="n"/>
-      <c r="H111" s="4" t="n"/>
+      <c r="G111" s="2" t="n"/>
+      <c r="H111" s="2" t="n"/>
       <c r="I111" s="3" t="n"/>
       <c r="J111" s="3" t="n"/>
       <c r="K111" s="2" t="n"/>
@@ -2334,8 +2328,8 @@
       <c r="D112" s="3" t="n"/>
       <c r="E112" s="3" t="n"/>
       <c r="F112" s="3" t="n"/>
-      <c r="G112" s="4" t="n"/>
-      <c r="H112" s="4" t="n"/>
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="n"/>
       <c r="I112" s="3" t="n"/>
       <c r="J112" s="3" t="n"/>
       <c r="K112" s="2" t="n"/>
@@ -2350,8 +2344,8 @@
       <c r="D113" s="3" t="n"/>
       <c r="E113" s="3" t="n"/>
       <c r="F113" s="3" t="n"/>
-      <c r="G113" s="4" t="n"/>
-      <c r="H113" s="4" t="n"/>
+      <c r="G113" s="2" t="n"/>
+      <c r="H113" s="2" t="n"/>
       <c r="I113" s="3" t="n"/>
       <c r="J113" s="3" t="n"/>
       <c r="K113" s="2" t="n"/>
@@ -2366,8 +2360,8 @@
       <c r="D114" s="3" t="n"/>
       <c r="E114" s="3" t="n"/>
       <c r="F114" s="3" t="n"/>
-      <c r="G114" s="4" t="n"/>
-      <c r="H114" s="4" t="n"/>
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="2" t="n"/>
       <c r="I114" s="3" t="n"/>
       <c r="J114" s="3" t="n"/>
       <c r="K114" s="2" t="n"/>
@@ -2382,8 +2376,8 @@
       <c r="D115" s="3" t="n"/>
       <c r="E115" s="3" t="n"/>
       <c r="F115" s="3" t="n"/>
-      <c r="G115" s="4" t="n"/>
-      <c r="H115" s="4" t="n"/>
+      <c r="G115" s="2" t="n"/>
+      <c r="H115" s="2" t="n"/>
       <c r="I115" s="3" t="n"/>
       <c r="J115" s="3" t="n"/>
       <c r="K115" s="2" t="n"/>
@@ -2398,8 +2392,8 @@
       <c r="D116" s="3" t="n"/>
       <c r="E116" s="3" t="n"/>
       <c r="F116" s="3" t="n"/>
-      <c r="G116" s="4" t="n"/>
-      <c r="H116" s="4" t="n"/>
+      <c r="G116" s="2" t="n"/>
+      <c r="H116" s="2" t="n"/>
       <c r="I116" s="3" t="n"/>
       <c r="J116" s="3" t="n"/>
       <c r="K116" s="2" t="n"/>
@@ -2414,8 +2408,8 @@
       <c r="D117" s="3" t="n"/>
       <c r="E117" s="3" t="n"/>
       <c r="F117" s="3" t="n"/>
-      <c r="G117" s="4" t="n"/>
-      <c r="H117" s="4" t="n"/>
+      <c r="G117" s="2" t="n"/>
+      <c r="H117" s="2" t="n"/>
       <c r="I117" s="3" t="n"/>
       <c r="J117" s="3" t="n"/>
       <c r="K117" s="2" t="n"/>
@@ -2430,8 +2424,8 @@
       <c r="D118" s="3" t="n"/>
       <c r="E118" s="3" t="n"/>
       <c r="F118" s="3" t="n"/>
-      <c r="G118" s="4" t="n"/>
-      <c r="H118" s="4" t="n"/>
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="n"/>
       <c r="I118" s="3" t="n"/>
       <c r="J118" s="3" t="n"/>
       <c r="K118" s="2" t="n"/>
@@ -2446,8 +2440,8 @@
       <c r="D119" s="3" t="n"/>
       <c r="E119" s="3" t="n"/>
       <c r="F119" s="3" t="n"/>
-      <c r="G119" s="4" t="n"/>
-      <c r="H119" s="4" t="n"/>
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="2" t="n"/>
       <c r="I119" s="3" t="n"/>
       <c r="J119" s="3" t="n"/>
       <c r="K119" s="2" t="n"/>
@@ -2462,8 +2456,8 @@
       <c r="D120" s="3" t="n"/>
       <c r="E120" s="3" t="n"/>
       <c r="F120" s="3" t="n"/>
-      <c r="G120" s="4" t="n"/>
-      <c r="H120" s="4" t="n"/>
+      <c r="G120" s="2" t="n"/>
+      <c r="H120" s="2" t="n"/>
       <c r="I120" s="3" t="n"/>
       <c r="J120" s="3" t="n"/>
       <c r="K120" s="2" t="n"/>
@@ -2478,8 +2472,8 @@
       <c r="D121" s="3" t="n"/>
       <c r="E121" s="3" t="n"/>
       <c r="F121" s="3" t="n"/>
-      <c r="G121" s="4" t="n"/>
-      <c r="H121" s="4" t="n"/>
+      <c r="G121" s="2" t="n"/>
+      <c r="H121" s="2" t="n"/>
       <c r="I121" s="3" t="n"/>
       <c r="J121" s="3" t="n"/>
       <c r="K121" s="2" t="n"/>
@@ -2494,8 +2488,8 @@
       <c r="D122" s="3" t="n"/>
       <c r="E122" s="3" t="n"/>
       <c r="F122" s="3" t="n"/>
-      <c r="G122" s="4" t="n"/>
-      <c r="H122" s="4" t="n"/>
+      <c r="G122" s="2" t="n"/>
+      <c r="H122" s="2" t="n"/>
       <c r="I122" s="3" t="n"/>
       <c r="J122" s="3" t="n"/>
       <c r="K122" s="2" t="n"/>
@@ -2510,8 +2504,8 @@
       <c r="D123" s="3" t="n"/>
       <c r="E123" s="3" t="n"/>
       <c r="F123" s="3" t="n"/>
-      <c r="G123" s="4" t="n"/>
-      <c r="H123" s="4" t="n"/>
+      <c r="G123" s="2" t="n"/>
+      <c r="H123" s="2" t="n"/>
       <c r="I123" s="3" t="n"/>
       <c r="J123" s="3" t="n"/>
       <c r="K123" s="2" t="n"/>
@@ -2526,8 +2520,8 @@
       <c r="D124" s="3" t="n"/>
       <c r="E124" s="3" t="n"/>
       <c r="F124" s="3" t="n"/>
-      <c r="G124" s="4" t="n"/>
-      <c r="H124" s="4" t="n"/>
+      <c r="G124" s="2" t="n"/>
+      <c r="H124" s="2" t="n"/>
       <c r="I124" s="3" t="n"/>
       <c r="J124" s="3" t="n"/>
       <c r="K124" s="2" t="n"/>
@@ -2542,8 +2536,8 @@
       <c r="D125" s="3" t="n"/>
       <c r="E125" s="3" t="n"/>
       <c r="F125" s="3" t="n"/>
-      <c r="G125" s="4" t="n"/>
-      <c r="H125" s="4" t="n"/>
+      <c r="G125" s="2" t="n"/>
+      <c r="H125" s="2" t="n"/>
       <c r="I125" s="3" t="n"/>
       <c r="J125" s="3" t="n"/>
       <c r="K125" s="2" t="n"/>
@@ -2558,8 +2552,8 @@
       <c r="D126" s="3" t="n"/>
       <c r="E126" s="3" t="n"/>
       <c r="F126" s="3" t="n"/>
-      <c r="G126" s="4" t="n"/>
-      <c r="H126" s="4" t="n"/>
+      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="2" t="n"/>
       <c r="I126" s="3" t="n"/>
       <c r="J126" s="3" t="n"/>
       <c r="K126" s="2" t="n"/>
@@ -2574,8 +2568,8 @@
       <c r="D127" s="3" t="n"/>
       <c r="E127" s="3" t="n"/>
       <c r="F127" s="3" t="n"/>
-      <c r="G127" s="4" t="n"/>
-      <c r="H127" s="4" t="n"/>
+      <c r="G127" s="2" t="n"/>
+      <c r="H127" s="2" t="n"/>
       <c r="I127" s="3" t="n"/>
       <c r="J127" s="3" t="n"/>
       <c r="K127" s="2" t="n"/>
@@ -2590,8 +2584,8 @@
       <c r="D128" s="3" t="n"/>
       <c r="E128" s="3" t="n"/>
       <c r="F128" s="3" t="n"/>
-      <c r="G128" s="4" t="n"/>
-      <c r="H128" s="4" t="n"/>
+      <c r="G128" s="2" t="n"/>
+      <c r="H128" s="2" t="n"/>
       <c r="I128" s="3" t="n"/>
       <c r="J128" s="3" t="n"/>
       <c r="K128" s="2" t="n"/>
@@ -2606,8 +2600,8 @@
       <c r="D129" s="3" t="n"/>
       <c r="E129" s="3" t="n"/>
       <c r="F129" s="3" t="n"/>
-      <c r="G129" s="4" t="n"/>
-      <c r="H129" s="4" t="n"/>
+      <c r="G129" s="2" t="n"/>
+      <c r="H129" s="2" t="n"/>
       <c r="I129" s="3" t="n"/>
       <c r="J129" s="3" t="n"/>
       <c r="K129" s="2" t="n"/>
@@ -2622,8 +2616,8 @@
       <c r="D130" s="3" t="n"/>
       <c r="E130" s="3" t="n"/>
       <c r="F130" s="3" t="n"/>
-      <c r="G130" s="4" t="n"/>
-      <c r="H130" s="4" t="n"/>
+      <c r="G130" s="2" t="n"/>
+      <c r="H130" s="2" t="n"/>
       <c r="I130" s="3" t="n"/>
       <c r="J130" s="3" t="n"/>
       <c r="K130" s="2" t="n"/>
@@ -2638,8 +2632,8 @@
       <c r="D131" s="3" t="n"/>
       <c r="E131" s="3" t="n"/>
       <c r="F131" s="3" t="n"/>
-      <c r="G131" s="4" t="n"/>
-      <c r="H131" s="4" t="n"/>
+      <c r="G131" s="2" t="n"/>
+      <c r="H131" s="2" t="n"/>
       <c r="I131" s="3" t="n"/>
       <c r="J131" s="3" t="n"/>
       <c r="K131" s="2" t="n"/>
@@ -2654,8 +2648,8 @@
       <c r="D132" s="3" t="n"/>
       <c r="E132" s="3" t="n"/>
       <c r="F132" s="3" t="n"/>
-      <c r="G132" s="4" t="n"/>
-      <c r="H132" s="4" t="n"/>
+      <c r="G132" s="2" t="n"/>
+      <c r="H132" s="2" t="n"/>
       <c r="I132" s="3" t="n"/>
       <c r="J132" s="3" t="n"/>
       <c r="K132" s="2" t="n"/>
@@ -2670,8 +2664,8 @@
       <c r="D133" s="3" t="n"/>
       <c r="E133" s="3" t="n"/>
       <c r="F133" s="3" t="n"/>
-      <c r="G133" s="4" t="n"/>
-      <c r="H133" s="4" t="n"/>
+      <c r="G133" s="2" t="n"/>
+      <c r="H133" s="2" t="n"/>
       <c r="I133" s="3" t="n"/>
       <c r="J133" s="3" t="n"/>
       <c r="K133" s="2" t="n"/>
@@ -2686,8 +2680,8 @@
       <c r="D134" s="3" t="n"/>
       <c r="E134" s="3" t="n"/>
       <c r="F134" s="3" t="n"/>
-      <c r="G134" s="4" t="n"/>
-      <c r="H134" s="4" t="n"/>
+      <c r="G134" s="2" t="n"/>
+      <c r="H134" s="2" t="n"/>
       <c r="I134" s="3" t="n"/>
       <c r="J134" s="3" t="n"/>
       <c r="K134" s="2" t="n"/>
@@ -2702,8 +2696,8 @@
       <c r="D135" s="3" t="n"/>
       <c r="E135" s="3" t="n"/>
       <c r="F135" s="3" t="n"/>
-      <c r="G135" s="4" t="n"/>
-      <c r="H135" s="4" t="n"/>
+      <c r="G135" s="2" t="n"/>
+      <c r="H135" s="2" t="n"/>
       <c r="I135" s="3" t="n"/>
       <c r="J135" s="3" t="n"/>
       <c r="K135" s="2" t="n"/>
@@ -2718,8 +2712,8 @@
       <c r="D136" s="3" t="n"/>
       <c r="E136" s="3" t="n"/>
       <c r="F136" s="3" t="n"/>
-      <c r="G136" s="4" t="n"/>
-      <c r="H136" s="4" t="n"/>
+      <c r="G136" s="2" t="n"/>
+      <c r="H136" s="2" t="n"/>
       <c r="I136" s="3" t="n"/>
       <c r="J136" s="3" t="n"/>
       <c r="K136" s="2" t="n"/>
@@ -2734,8 +2728,8 @@
       <c r="D137" s="3" t="n"/>
       <c r="E137" s="3" t="n"/>
       <c r="F137" s="3" t="n"/>
-      <c r="G137" s="4" t="n"/>
-      <c r="H137" s="4" t="n"/>
+      <c r="G137" s="2" t="n"/>
+      <c r="H137" s="2" t="n"/>
       <c r="I137" s="3" t="n"/>
       <c r="J137" s="3" t="n"/>
       <c r="K137" s="2" t="n"/>
@@ -2750,8 +2744,8 @@
       <c r="D138" s="3" t="n"/>
       <c r="E138" s="3" t="n"/>
       <c r="F138" s="3" t="n"/>
-      <c r="G138" s="4" t="n"/>
-      <c r="H138" s="4" t="n"/>
+      <c r="G138" s="2" t="n"/>
+      <c r="H138" s="2" t="n"/>
       <c r="I138" s="3" t="n"/>
       <c r="J138" s="3" t="n"/>
       <c r="K138" s="2" t="n"/>
@@ -2766,8 +2760,8 @@
       <c r="D139" s="3" t="n"/>
       <c r="E139" s="3" t="n"/>
       <c r="F139" s="3" t="n"/>
-      <c r="G139" s="4" t="n"/>
-      <c r="H139" s="4" t="n"/>
+      <c r="G139" s="2" t="n"/>
+      <c r="H139" s="2" t="n"/>
       <c r="I139" s="3" t="n"/>
       <c r="J139" s="3" t="n"/>
       <c r="K139" s="2" t="n"/>
@@ -2782,8 +2776,8 @@
       <c r="D140" s="3" t="n"/>
       <c r="E140" s="3" t="n"/>
       <c r="F140" s="3" t="n"/>
-      <c r="G140" s="4" t="n"/>
-      <c r="H140" s="4" t="n"/>
+      <c r="G140" s="2" t="n"/>
+      <c r="H140" s="2" t="n"/>
       <c r="I140" s="3" t="n"/>
       <c r="J140" s="3" t="n"/>
       <c r="K140" s="2" t="n"/>
@@ -2798,8 +2792,8 @@
       <c r="D141" s="3" t="n"/>
       <c r="E141" s="3" t="n"/>
       <c r="F141" s="3" t="n"/>
-      <c r="G141" s="4" t="n"/>
-      <c r="H141" s="4" t="n"/>
+      <c r="G141" s="2" t="n"/>
+      <c r="H141" s="2" t="n"/>
       <c r="I141" s="3" t="n"/>
       <c r="J141" s="3" t="n"/>
       <c r="K141" s="2" t="n"/>
@@ -2814,8 +2808,8 @@
       <c r="D142" s="3" t="n"/>
       <c r="E142" s="3" t="n"/>
       <c r="F142" s="3" t="n"/>
-      <c r="G142" s="4" t="n"/>
-      <c r="H142" s="4" t="n"/>
+      <c r="G142" s="2" t="n"/>
+      <c r="H142" s="2" t="n"/>
       <c r="I142" s="3" t="n"/>
       <c r="J142" s="3" t="n"/>
       <c r="K142" s="2" t="n"/>
@@ -2830,8 +2824,8 @@
       <c r="D143" s="3" t="n"/>
       <c r="E143" s="3" t="n"/>
       <c r="F143" s="3" t="n"/>
-      <c r="G143" s="4" t="n"/>
-      <c r="H143" s="4" t="n"/>
+      <c r="G143" s="2" t="n"/>
+      <c r="H143" s="2" t="n"/>
       <c r="I143" s="3" t="n"/>
       <c r="J143" s="3" t="n"/>
       <c r="K143" s="2" t="n"/>
@@ -2846,8 +2840,8 @@
       <c r="D144" s="3" t="n"/>
       <c r="E144" s="3" t="n"/>
       <c r="F144" s="3" t="n"/>
-      <c r="G144" s="4" t="n"/>
-      <c r="H144" s="4" t="n"/>
+      <c r="G144" s="2" t="n"/>
+      <c r="H144" s="2" t="n"/>
       <c r="I144" s="3" t="n"/>
       <c r="J144" s="3" t="n"/>
       <c r="K144" s="2" t="n"/>
@@ -2862,8 +2856,8 @@
       <c r="D145" s="3" t="n"/>
       <c r="E145" s="3" t="n"/>
       <c r="F145" s="3" t="n"/>
-      <c r="G145" s="4" t="n"/>
-      <c r="H145" s="4" t="n"/>
+      <c r="G145" s="2" t="n"/>
+      <c r="H145" s="2" t="n"/>
       <c r="I145" s="3" t="n"/>
       <c r="J145" s="3" t="n"/>
       <c r="K145" s="2" t="n"/>
@@ -2878,8 +2872,8 @@
       <c r="D146" s="3" t="n"/>
       <c r="E146" s="3" t="n"/>
       <c r="F146" s="3" t="n"/>
-      <c r="G146" s="4" t="n"/>
-      <c r="H146" s="4" t="n"/>
+      <c r="G146" s="2" t="n"/>
+      <c r="H146" s="2" t="n"/>
       <c r="I146" s="3" t="n"/>
       <c r="J146" s="3" t="n"/>
       <c r="K146" s="2" t="n"/>
@@ -2894,8 +2888,8 @@
       <c r="D147" s="3" t="n"/>
       <c r="E147" s="3" t="n"/>
       <c r="F147" s="3" t="n"/>
-      <c r="G147" s="4" t="n"/>
-      <c r="H147" s="4" t="n"/>
+      <c r="G147" s="2" t="n"/>
+      <c r="H147" s="2" t="n"/>
       <c r="I147" s="3" t="n"/>
       <c r="J147" s="3" t="n"/>
       <c r="K147" s="2" t="n"/>
@@ -2910,8 +2904,8 @@
       <c r="D148" s="3" t="n"/>
       <c r="E148" s="3" t="n"/>
       <c r="F148" s="3" t="n"/>
-      <c r="G148" s="4" t="n"/>
-      <c r="H148" s="4" t="n"/>
+      <c r="G148" s="2" t="n"/>
+      <c r="H148" s="2" t="n"/>
       <c r="I148" s="3" t="n"/>
       <c r="J148" s="3" t="n"/>
       <c r="K148" s="2" t="n"/>
@@ -2926,8 +2920,8 @@
       <c r="D149" s="3" t="n"/>
       <c r="E149" s="3" t="n"/>
       <c r="F149" s="3" t="n"/>
-      <c r="G149" s="4" t="n"/>
-      <c r="H149" s="4" t="n"/>
+      <c r="G149" s="2" t="n"/>
+      <c r="H149" s="2" t="n"/>
       <c r="I149" s="3" t="n"/>
       <c r="J149" s="3" t="n"/>
       <c r="K149" s="2" t="n"/>
@@ -2942,8 +2936,8 @@
       <c r="D150" s="3" t="n"/>
       <c r="E150" s="3" t="n"/>
       <c r="F150" s="3" t="n"/>
-      <c r="G150" s="4" t="n"/>
-      <c r="H150" s="4" t="n"/>
+      <c r="G150" s="2" t="n"/>
+      <c r="H150" s="2" t="n"/>
       <c r="I150" s="3" t="n"/>
       <c r="J150" s="3" t="n"/>
       <c r="K150" s="2" t="n"/>
@@ -2958,8 +2952,8 @@
       <c r="D151" s="3" t="n"/>
       <c r="E151" s="3" t="n"/>
       <c r="F151" s="3" t="n"/>
-      <c r="G151" s="4" t="n"/>
-      <c r="H151" s="4" t="n"/>
+      <c r="G151" s="2" t="n"/>
+      <c r="H151" s="2" t="n"/>
       <c r="I151" s="3" t="n"/>
       <c r="J151" s="3" t="n"/>
       <c r="K151" s="2" t="n"/>
@@ -2974,8 +2968,8 @@
       <c r="D152" s="3" t="n"/>
       <c r="E152" s="3" t="n"/>
       <c r="F152" s="3" t="n"/>
-      <c r="G152" s="4" t="n"/>
-      <c r="H152" s="4" t="n"/>
+      <c r="G152" s="2" t="n"/>
+      <c r="H152" s="2" t="n"/>
       <c r="I152" s="3" t="n"/>
       <c r="J152" s="3" t="n"/>
       <c r="K152" s="2" t="n"/>
@@ -2990,8 +2984,8 @@
       <c r="D153" s="3" t="n"/>
       <c r="E153" s="3" t="n"/>
       <c r="F153" s="3" t="n"/>
-      <c r="G153" s="4" t="n"/>
-      <c r="H153" s="4" t="n"/>
+      <c r="G153" s="2" t="n"/>
+      <c r="H153" s="2" t="n"/>
       <c r="I153" s="3" t="n"/>
       <c r="J153" s="3" t="n"/>
       <c r="K153" s="2" t="n"/>
@@ -3006,8 +3000,8 @@
       <c r="D154" s="3" t="n"/>
       <c r="E154" s="3" t="n"/>
       <c r="F154" s="3" t="n"/>
-      <c r="G154" s="4" t="n"/>
-      <c r="H154" s="4" t="n"/>
+      <c r="G154" s="2" t="n"/>
+      <c r="H154" s="2" t="n"/>
       <c r="I154" s="3" t="n"/>
       <c r="J154" s="3" t="n"/>
       <c r="K154" s="2" t="n"/>
@@ -3022,8 +3016,8 @@
       <c r="D155" s="3" t="n"/>
       <c r="E155" s="3" t="n"/>
       <c r="F155" s="3" t="n"/>
-      <c r="G155" s="4" t="n"/>
-      <c r="H155" s="4" t="n"/>
+      <c r="G155" s="2" t="n"/>
+      <c r="H155" s="2" t="n"/>
       <c r="I155" s="3" t="n"/>
       <c r="J155" s="3" t="n"/>
       <c r="K155" s="2" t="n"/>
@@ -3038,8 +3032,8 @@
       <c r="D156" s="3" t="n"/>
       <c r="E156" s="3" t="n"/>
       <c r="F156" s="3" t="n"/>
-      <c r="G156" s="4" t="n"/>
-      <c r="H156" s="4" t="n"/>
+      <c r="G156" s="2" t="n"/>
+      <c r="H156" s="2" t="n"/>
       <c r="I156" s="3" t="n"/>
       <c r="J156" s="3" t="n"/>
       <c r="K156" s="2" t="n"/>
@@ -3054,8 +3048,8 @@
       <c r="D157" s="3" t="n"/>
       <c r="E157" s="3" t="n"/>
       <c r="F157" s="3" t="n"/>
-      <c r="G157" s="4" t="n"/>
-      <c r="H157" s="4" t="n"/>
+      <c r="G157" s="2" t="n"/>
+      <c r="H157" s="2" t="n"/>
       <c r="I157" s="3" t="n"/>
       <c r="J157" s="3" t="n"/>
       <c r="K157" s="2" t="n"/>
@@ -3070,8 +3064,8 @@
       <c r="D158" s="3" t="n"/>
       <c r="E158" s="3" t="n"/>
       <c r="F158" s="3" t="n"/>
-      <c r="G158" s="4" t="n"/>
-      <c r="H158" s="4" t="n"/>
+      <c r="G158" s="2" t="n"/>
+      <c r="H158" s="2" t="n"/>
       <c r="I158" s="3" t="n"/>
       <c r="J158" s="3" t="n"/>
       <c r="K158" s="2" t="n"/>
@@ -3086,8 +3080,8 @@
       <c r="D159" s="3" t="n"/>
       <c r="E159" s="3" t="n"/>
       <c r="F159" s="3" t="n"/>
-      <c r="G159" s="4" t="n"/>
-      <c r="H159" s="4" t="n"/>
+      <c r="G159" s="2" t="n"/>
+      <c r="H159" s="2" t="n"/>
       <c r="I159" s="3" t="n"/>
       <c r="J159" s="3" t="n"/>
       <c r="K159" s="2" t="n"/>
@@ -3102,8 +3096,8 @@
       <c r="D160" s="3" t="n"/>
       <c r="E160" s="3" t="n"/>
       <c r="F160" s="3" t="n"/>
-      <c r="G160" s="4" t="n"/>
-      <c r="H160" s="4" t="n"/>
+      <c r="G160" s="2" t="n"/>
+      <c r="H160" s="2" t="n"/>
       <c r="I160" s="3" t="n"/>
       <c r="J160" s="3" t="n"/>
       <c r="K160" s="2" t="n"/>
@@ -3118,8 +3112,8 @@
       <c r="D161" s="3" t="n"/>
       <c r="E161" s="3" t="n"/>
       <c r="F161" s="3" t="n"/>
-      <c r="G161" s="4" t="n"/>
-      <c r="H161" s="4" t="n"/>
+      <c r="G161" s="2" t="n"/>
+      <c r="H161" s="2" t="n"/>
       <c r="I161" s="3" t="n"/>
       <c r="J161" s="3" t="n"/>
       <c r="K161" s="2" t="n"/>
@@ -3134,8 +3128,8 @@
       <c r="D162" s="3" t="n"/>
       <c r="E162" s="3" t="n"/>
       <c r="F162" s="3" t="n"/>
-      <c r="G162" s="4" t="n"/>
-      <c r="H162" s="4" t="n"/>
+      <c r="G162" s="2" t="n"/>
+      <c r="H162" s="2" t="n"/>
       <c r="I162" s="3" t="n"/>
       <c r="J162" s="3" t="n"/>
       <c r="K162" s="2" t="n"/>
@@ -3150,8 +3144,8 @@
       <c r="D163" s="3" t="n"/>
       <c r="E163" s="3" t="n"/>
       <c r="F163" s="3" t="n"/>
-      <c r="G163" s="4" t="n"/>
-      <c r="H163" s="4" t="n"/>
+      <c r="G163" s="2" t="n"/>
+      <c r="H163" s="2" t="n"/>
       <c r="I163" s="3" t="n"/>
       <c r="J163" s="3" t="n"/>
       <c r="K163" s="2" t="n"/>
@@ -3166,8 +3160,8 @@
       <c r="D164" s="3" t="n"/>
       <c r="E164" s="3" t="n"/>
       <c r="F164" s="3" t="n"/>
-      <c r="G164" s="4" t="n"/>
-      <c r="H164" s="4" t="n"/>
+      <c r="G164" s="2" t="n"/>
+      <c r="H164" s="2" t="n"/>
       <c r="I164" s="3" t="n"/>
       <c r="J164" s="3" t="n"/>
       <c r="K164" s="2" t="n"/>
@@ -3182,8 +3176,8 @@
       <c r="D165" s="3" t="n"/>
       <c r="E165" s="3" t="n"/>
       <c r="F165" s="3" t="n"/>
-      <c r="G165" s="4" t="n"/>
-      <c r="H165" s="4" t="n"/>
+      <c r="G165" s="2" t="n"/>
+      <c r="H165" s="2" t="n"/>
       <c r="I165" s="3" t="n"/>
       <c r="J165" s="3" t="n"/>
       <c r="K165" s="2" t="n"/>
@@ -3198,8 +3192,8 @@
       <c r="D166" s="3" t="n"/>
       <c r="E166" s="3" t="n"/>
       <c r="F166" s="3" t="n"/>
-      <c r="G166" s="4" t="n"/>
-      <c r="H166" s="4" t="n"/>
+      <c r="G166" s="2" t="n"/>
+      <c r="H166" s="2" t="n"/>
       <c r="I166" s="3" t="n"/>
       <c r="J166" s="3" t="n"/>
       <c r="K166" s="2" t="n"/>
@@ -3214,8 +3208,8 @@
       <c r="D167" s="3" t="n"/>
       <c r="E167" s="3" t="n"/>
       <c r="F167" s="3" t="n"/>
-      <c r="G167" s="4" t="n"/>
-      <c r="H167" s="4" t="n"/>
+      <c r="G167" s="2" t="n"/>
+      <c r="H167" s="2" t="n"/>
       <c r="I167" s="3" t="n"/>
       <c r="J167" s="3" t="n"/>
       <c r="K167" s="2" t="n"/>
@@ -3230,8 +3224,8 @@
       <c r="D168" s="3" t="n"/>
       <c r="E168" s="3" t="n"/>
       <c r="F168" s="3" t="n"/>
-      <c r="G168" s="4" t="n"/>
-      <c r="H168" s="4" t="n"/>
+      <c r="G168" s="2" t="n"/>
+      <c r="H168" s="2" t="n"/>
       <c r="I168" s="3" t="n"/>
       <c r="J168" s="3" t="n"/>
       <c r="K168" s="2" t="n"/>
@@ -3246,8 +3240,8 @@
       <c r="D169" s="3" t="n"/>
       <c r="E169" s="3" t="n"/>
       <c r="F169" s="3" t="n"/>
-      <c r="G169" s="4" t="n"/>
-      <c r="H169" s="4" t="n"/>
+      <c r="G169" s="2" t="n"/>
+      <c r="H169" s="2" t="n"/>
       <c r="I169" s="3" t="n"/>
       <c r="J169" s="3" t="n"/>
       <c r="K169" s="2" t="n"/>
@@ -3262,8 +3256,8 @@
       <c r="D170" s="3" t="n"/>
       <c r="E170" s="3" t="n"/>
       <c r="F170" s="3" t="n"/>
-      <c r="G170" s="4" t="n"/>
-      <c r="H170" s="4" t="n"/>
+      <c r="G170" s="2" t="n"/>
+      <c r="H170" s="2" t="n"/>
       <c r="I170" s="3" t="n"/>
       <c r="J170" s="3" t="n"/>
       <c r="K170" s="2" t="n"/>
@@ -3278,8 +3272,8 @@
       <c r="D171" s="3" t="n"/>
       <c r="E171" s="3" t="n"/>
       <c r="F171" s="3" t="n"/>
-      <c r="G171" s="4" t="n"/>
-      <c r="H171" s="4" t="n"/>
+      <c r="G171" s="2" t="n"/>
+      <c r="H171" s="2" t="n"/>
       <c r="I171" s="3" t="n"/>
       <c r="J171" s="3" t="n"/>
       <c r="K171" s="2" t="n"/>
@@ -3294,8 +3288,8 @@
       <c r="D172" s="3" t="n"/>
       <c r="E172" s="3" t="n"/>
       <c r="F172" s="3" t="n"/>
-      <c r="G172" s="4" t="n"/>
-      <c r="H172" s="4" t="n"/>
+      <c r="G172" s="2" t="n"/>
+      <c r="H172" s="2" t="n"/>
       <c r="I172" s="3" t="n"/>
       <c r="J172" s="3" t="n"/>
       <c r="K172" s="2" t="n"/>
@@ -3310,8 +3304,8 @@
       <c r="D173" s="3" t="n"/>
       <c r="E173" s="3" t="n"/>
       <c r="F173" s="3" t="n"/>
-      <c r="G173" s="4" t="n"/>
-      <c r="H173" s="4" t="n"/>
+      <c r="G173" s="2" t="n"/>
+      <c r="H173" s="2" t="n"/>
       <c r="I173" s="3" t="n"/>
       <c r="J173" s="3" t="n"/>
       <c r="K173" s="2" t="n"/>
@@ -3326,8 +3320,8 @@
       <c r="D174" s="3" t="n"/>
       <c r="E174" s="3" t="n"/>
       <c r="F174" s="3" t="n"/>
-      <c r="G174" s="4" t="n"/>
-      <c r="H174" s="4" t="n"/>
+      <c r="G174" s="2" t="n"/>
+      <c r="H174" s="2" t="n"/>
       <c r="I174" s="3" t="n"/>
       <c r="J174" s="3" t="n"/>
       <c r="K174" s="2" t="n"/>
@@ -3342,8 +3336,8 @@
       <c r="D175" s="3" t="n"/>
       <c r="E175" s="3" t="n"/>
       <c r="F175" s="3" t="n"/>
-      <c r="G175" s="4" t="n"/>
-      <c r="H175" s="4" t="n"/>
+      <c r="G175" s="2" t="n"/>
+      <c r="H175" s="2" t="n"/>
       <c r="I175" s="3" t="n"/>
       <c r="J175" s="3" t="n"/>
       <c r="K175" s="2" t="n"/>
@@ -3358,8 +3352,8 @@
       <c r="D176" s="3" t="n"/>
       <c r="E176" s="3" t="n"/>
       <c r="F176" s="3" t="n"/>
-      <c r="G176" s="4" t="n"/>
-      <c r="H176" s="4" t="n"/>
+      <c r="G176" s="2" t="n"/>
+      <c r="H176" s="2" t="n"/>
       <c r="I176" s="3" t="n"/>
       <c r="J176" s="3" t="n"/>
       <c r="K176" s="2" t="n"/>
@@ -3374,8 +3368,8 @@
       <c r="D177" s="3" t="n"/>
       <c r="E177" s="3" t="n"/>
       <c r="F177" s="3" t="n"/>
-      <c r="G177" s="4" t="n"/>
-      <c r="H177" s="4" t="n"/>
+      <c r="G177" s="2" t="n"/>
+      <c r="H177" s="2" t="n"/>
       <c r="I177" s="3" t="n"/>
       <c r="J177" s="3" t="n"/>
       <c r="K177" s="2" t="n"/>
@@ -3390,8 +3384,8 @@
       <c r="D178" s="3" t="n"/>
       <c r="E178" s="3" t="n"/>
       <c r="F178" s="3" t="n"/>
-      <c r="G178" s="4" t="n"/>
-      <c r="H178" s="4" t="n"/>
+      <c r="G178" s="2" t="n"/>
+      <c r="H178" s="2" t="n"/>
       <c r="I178" s="3" t="n"/>
       <c r="J178" s="3" t="n"/>
       <c r="K178" s="2" t="n"/>
@@ -3406,8 +3400,8 @@
       <c r="D179" s="3" t="n"/>
       <c r="E179" s="3" t="n"/>
       <c r="F179" s="3" t="n"/>
-      <c r="G179" s="4" t="n"/>
-      <c r="H179" s="4" t="n"/>
+      <c r="G179" s="2" t="n"/>
+      <c r="H179" s="2" t="n"/>
       <c r="I179" s="3" t="n"/>
       <c r="J179" s="3" t="n"/>
       <c r="K179" s="2" t="n"/>
@@ -3422,8 +3416,8 @@
       <c r="D180" s="3" t="n"/>
       <c r="E180" s="3" t="n"/>
       <c r="F180" s="3" t="n"/>
-      <c r="G180" s="4" t="n"/>
-      <c r="H180" s="4" t="n"/>
+      <c r="G180" s="2" t="n"/>
+      <c r="H180" s="2" t="n"/>
       <c r="I180" s="3" t="n"/>
       <c r="J180" s="3" t="n"/>
       <c r="K180" s="2" t="n"/>
@@ -3438,8 +3432,8 @@
       <c r="D181" s="3" t="n"/>
       <c r="E181" s="3" t="n"/>
       <c r="F181" s="3" t="n"/>
-      <c r="G181" s="4" t="n"/>
-      <c r="H181" s="4" t="n"/>
+      <c r="G181" s="2" t="n"/>
+      <c r="H181" s="2" t="n"/>
       <c r="I181" s="3" t="n"/>
       <c r="J181" s="3" t="n"/>
       <c r="K181" s="2" t="n"/>
@@ -3454,8 +3448,8 @@
       <c r="D182" s="3" t="n"/>
       <c r="E182" s="3" t="n"/>
       <c r="F182" s="3" t="n"/>
-      <c r="G182" s="4" t="n"/>
-      <c r="H182" s="4" t="n"/>
+      <c r="G182" s="2" t="n"/>
+      <c r="H182" s="2" t="n"/>
       <c r="I182" s="3" t="n"/>
       <c r="J182" s="3" t="n"/>
       <c r="K182" s="2" t="n"/>
@@ -3470,8 +3464,8 @@
       <c r="D183" s="3" t="n"/>
       <c r="E183" s="3" t="n"/>
       <c r="F183" s="3" t="n"/>
-      <c r="G183" s="4" t="n"/>
-      <c r="H183" s="4" t="n"/>
+      <c r="G183" s="2" t="n"/>
+      <c r="H183" s="2" t="n"/>
       <c r="I183" s="3" t="n"/>
       <c r="J183" s="3" t="n"/>
       <c r="K183" s="2" t="n"/>
@@ -3486,8 +3480,8 @@
       <c r="D184" s="3" t="n"/>
       <c r="E184" s="3" t="n"/>
       <c r="F184" s="3" t="n"/>
-      <c r="G184" s="4" t="n"/>
-      <c r="H184" s="4" t="n"/>
+      <c r="G184" s="2" t="n"/>
+      <c r="H184" s="2" t="n"/>
       <c r="I184" s="3" t="n"/>
       <c r="J184" s="3" t="n"/>
       <c r="K184" s="2" t="n"/>
@@ -3502,8 +3496,8 @@
       <c r="D185" s="3" t="n"/>
       <c r="E185" s="3" t="n"/>
       <c r="F185" s="3" t="n"/>
-      <c r="G185" s="4" t="n"/>
-      <c r="H185" s="4" t="n"/>
+      <c r="G185" s="2" t="n"/>
+      <c r="H185" s="2" t="n"/>
       <c r="I185" s="3" t="n"/>
       <c r="J185" s="3" t="n"/>
       <c r="K185" s="2" t="n"/>
@@ -3518,8 +3512,8 @@
       <c r="D186" s="3" t="n"/>
       <c r="E186" s="3" t="n"/>
       <c r="F186" s="3" t="n"/>
-      <c r="G186" s="4" t="n"/>
-      <c r="H186" s="4" t="n"/>
+      <c r="G186" s="2" t="n"/>
+      <c r="H186" s="2" t="n"/>
       <c r="I186" s="3" t="n"/>
       <c r="J186" s="3" t="n"/>
       <c r="K186" s="2" t="n"/>
@@ -3534,8 +3528,8 @@
       <c r="D187" s="3" t="n"/>
       <c r="E187" s="3" t="n"/>
       <c r="F187" s="3" t="n"/>
-      <c r="G187" s="4" t="n"/>
-      <c r="H187" s="4" t="n"/>
+      <c r="G187" s="2" t="n"/>
+      <c r="H187" s="2" t="n"/>
       <c r="I187" s="3" t="n"/>
       <c r="J187" s="3" t="n"/>
       <c r="K187" s="2" t="n"/>
@@ -3550,8 +3544,8 @@
       <c r="D188" s="3" t="n"/>
       <c r="E188" s="3" t="n"/>
       <c r="F188" s="3" t="n"/>
-      <c r="G188" s="4" t="n"/>
-      <c r="H188" s="4" t="n"/>
+      <c r="G188" s="2" t="n"/>
+      <c r="H188" s="2" t="n"/>
       <c r="I188" s="3" t="n"/>
       <c r="J188" s="3" t="n"/>
       <c r="K188" s="2" t="n"/>
@@ -3566,8 +3560,8 @@
       <c r="D189" s="3" t="n"/>
       <c r="E189" s="3" t="n"/>
       <c r="F189" s="3" t="n"/>
-      <c r="G189" s="4" t="n"/>
-      <c r="H189" s="4" t="n"/>
+      <c r="G189" s="2" t="n"/>
+      <c r="H189" s="2" t="n"/>
       <c r="I189" s="3" t="n"/>
       <c r="J189" s="3" t="n"/>
       <c r="K189" s="2" t="n"/>
@@ -3582,8 +3576,8 @@
       <c r="D190" s="3" t="n"/>
       <c r="E190" s="3" t="n"/>
       <c r="F190" s="3" t="n"/>
-      <c r="G190" s="4" t="n"/>
-      <c r="H190" s="4" t="n"/>
+      <c r="G190" s="2" t="n"/>
+      <c r="H190" s="2" t="n"/>
       <c r="I190" s="3" t="n"/>
       <c r="J190" s="3" t="n"/>
       <c r="K190" s="2" t="n"/>
@@ -3598,8 +3592,8 @@
       <c r="D191" s="3" t="n"/>
       <c r="E191" s="3" t="n"/>
       <c r="F191" s="3" t="n"/>
-      <c r="G191" s="4" t="n"/>
-      <c r="H191" s="4" t="n"/>
+      <c r="G191" s="2" t="n"/>
+      <c r="H191" s="2" t="n"/>
       <c r="I191" s="3" t="n"/>
       <c r="J191" s="3" t="n"/>
       <c r="K191" s="2" t="n"/>
@@ -3614,8 +3608,8 @@
       <c r="D192" s="3" t="n"/>
       <c r="E192" s="3" t="n"/>
       <c r="F192" s="3" t="n"/>
-      <c r="G192" s="4" t="n"/>
-      <c r="H192" s="4" t="n"/>
+      <c r="G192" s="2" t="n"/>
+      <c r="H192" s="2" t="n"/>
       <c r="I192" s="3" t="n"/>
       <c r="J192" s="3" t="n"/>
       <c r="K192" s="2" t="n"/>
@@ -3630,8 +3624,8 @@
       <c r="D193" s="3" t="n"/>
       <c r="E193" s="3" t="n"/>
       <c r="F193" s="3" t="n"/>
-      <c r="G193" s="4" t="n"/>
-      <c r="H193" s="4" t="n"/>
+      <c r="G193" s="2" t="n"/>
+      <c r="H193" s="2" t="n"/>
       <c r="I193" s="3" t="n"/>
       <c r="J193" s="3" t="n"/>
       <c r="K193" s="2" t="n"/>
@@ -3646,8 +3640,8 @@
       <c r="D194" s="3" t="n"/>
       <c r="E194" s="3" t="n"/>
       <c r="F194" s="3" t="n"/>
-      <c r="G194" s="4" t="n"/>
-      <c r="H194" s="4" t="n"/>
+      <c r="G194" s="2" t="n"/>
+      <c r="H194" s="2" t="n"/>
       <c r="I194" s="3" t="n"/>
       <c r="J194" s="3" t="n"/>
       <c r="K194" s="2" t="n"/>
@@ -3662,8 +3656,8 @@
       <c r="D195" s="3" t="n"/>
       <c r="E195" s="3" t="n"/>
       <c r="F195" s="3" t="n"/>
-      <c r="G195" s="4" t="n"/>
-      <c r="H195" s="4" t="n"/>
+      <c r="G195" s="2" t="n"/>
+      <c r="H195" s="2" t="n"/>
       <c r="I195" s="3" t="n"/>
       <c r="J195" s="3" t="n"/>
       <c r="K195" s="2" t="n"/>
@@ -3678,8 +3672,8 @@
       <c r="D196" s="3" t="n"/>
       <c r="E196" s="3" t="n"/>
       <c r="F196" s="3" t="n"/>
-      <c r="G196" s="4" t="n"/>
-      <c r="H196" s="4" t="n"/>
+      <c r="G196" s="2" t="n"/>
+      <c r="H196" s="2" t="n"/>
       <c r="I196" s="3" t="n"/>
       <c r="J196" s="3" t="n"/>
       <c r="K196" s="2" t="n"/>
@@ -3694,8 +3688,8 @@
       <c r="D197" s="3" t="n"/>
       <c r="E197" s="3" t="n"/>
       <c r="F197" s="3" t="n"/>
-      <c r="G197" s="4" t="n"/>
-      <c r="H197" s="4" t="n"/>
+      <c r="G197" s="2" t="n"/>
+      <c r="H197" s="2" t="n"/>
       <c r="I197" s="3" t="n"/>
       <c r="J197" s="3" t="n"/>
       <c r="K197" s="2" t="n"/>
@@ -3710,8 +3704,8 @@
       <c r="D198" s="3" t="n"/>
       <c r="E198" s="3" t="n"/>
       <c r="F198" s="3" t="n"/>
-      <c r="G198" s="4" t="n"/>
-      <c r="H198" s="4" t="n"/>
+      <c r="G198" s="2" t="n"/>
+      <c r="H198" s="2" t="n"/>
       <c r="I198" s="3" t="n"/>
       <c r="J198" s="3" t="n"/>
       <c r="K198" s="2" t="n"/>
@@ -3726,8 +3720,8 @@
       <c r="D199" s="3" t="n"/>
       <c r="E199" s="3" t="n"/>
       <c r="F199" s="3" t="n"/>
-      <c r="G199" s="4" t="n"/>
-      <c r="H199" s="4" t="n"/>
+      <c r="G199" s="2" t="n"/>
+      <c r="H199" s="2" t="n"/>
       <c r="I199" s="3" t="n"/>
       <c r="J199" s="3" t="n"/>
       <c r="K199" s="2" t="n"/>
@@ -3742,8 +3736,8 @@
       <c r="D200" s="3" t="n"/>
       <c r="E200" s="3" t="n"/>
       <c r="F200" s="3" t="n"/>
-      <c r="G200" s="4" t="n"/>
-      <c r="H200" s="4" t="n"/>
+      <c r="G200" s="2" t="n"/>
+      <c r="H200" s="2" t="n"/>
       <c r="I200" s="3" t="n"/>
       <c r="J200" s="3" t="n"/>
       <c r="K200" s="2" t="n"/>
@@ -3758,8 +3752,8 @@
       <c r="D201" s="3" t="n"/>
       <c r="E201" s="3" t="n"/>
       <c r="F201" s="3" t="n"/>
-      <c r="G201" s="4" t="n"/>
-      <c r="H201" s="4" t="n"/>
+      <c r="G201" s="2" t="n"/>
+      <c r="H201" s="2" t="n"/>
       <c r="I201" s="3" t="n"/>
       <c r="J201" s="3" t="n"/>
       <c r="K201" s="2" t="n"/>
@@ -3774,8 +3768,8 @@
       <c r="D202" s="3" t="n"/>
       <c r="E202" s="3" t="n"/>
       <c r="F202" s="3" t="n"/>
-      <c r="G202" s="4" t="n"/>
-      <c r="H202" s="4" t="n"/>
+      <c r="G202" s="2" t="n"/>
+      <c r="H202" s="2" t="n"/>
       <c r="I202" s="3" t="n"/>
       <c r="J202" s="3" t="n"/>
       <c r="K202" s="2" t="n"/>
@@ -3790,8 +3784,8 @@
       <c r="D203" s="3" t="n"/>
       <c r="E203" s="3" t="n"/>
       <c r="F203" s="3" t="n"/>
-      <c r="G203" s="4" t="n"/>
-      <c r="H203" s="4" t="n"/>
+      <c r="G203" s="2" t="n"/>
+      <c r="H203" s="2" t="n"/>
       <c r="I203" s="3" t="n"/>
       <c r="J203" s="3" t="n"/>
       <c r="K203" s="2" t="n"/>
@@ -3806,8 +3800,8 @@
       <c r="D204" s="3" t="n"/>
       <c r="E204" s="3" t="n"/>
       <c r="F204" s="3" t="n"/>
-      <c r="G204" s="4" t="n"/>
-      <c r="H204" s="4" t="n"/>
+      <c r="G204" s="2" t="n"/>
+      <c r="H204" s="2" t="n"/>
       <c r="I204" s="3" t="n"/>
       <c r="J204" s="3" t="n"/>
       <c r="K204" s="2" t="n"/>
@@ -3822,8 +3816,8 @@
       <c r="D205" s="3" t="n"/>
       <c r="E205" s="3" t="n"/>
       <c r="F205" s="3" t="n"/>
-      <c r="G205" s="4" t="n"/>
-      <c r="H205" s="4" t="n"/>
+      <c r="G205" s="2" t="n"/>
+      <c r="H205" s="2" t="n"/>
       <c r="I205" s="3" t="n"/>
       <c r="J205" s="3" t="n"/>
       <c r="K205" s="2" t="n"/>
@@ -3838,8 +3832,8 @@
       <c r="D206" s="3" t="n"/>
       <c r="E206" s="3" t="n"/>
       <c r="F206" s="3" t="n"/>
-      <c r="G206" s="4" t="n"/>
-      <c r="H206" s="4" t="n"/>
+      <c r="G206" s="2" t="n"/>
+      <c r="H206" s="2" t="n"/>
       <c r="I206" s="3" t="n"/>
       <c r="J206" s="3" t="n"/>
       <c r="K206" s="2" t="n"/>
@@ -3854,8 +3848,8 @@
       <c r="D207" s="3" t="n"/>
       <c r="E207" s="3" t="n"/>
       <c r="F207" s="3" t="n"/>
-      <c r="G207" s="4" t="n"/>
-      <c r="H207" s="4" t="n"/>
+      <c r="G207" s="2" t="n"/>
+      <c r="H207" s="2" t="n"/>
       <c r="I207" s="3" t="n"/>
       <c r="J207" s="3" t="n"/>
       <c r="K207" s="2" t="n"/>
@@ -3870,8 +3864,8 @@
       <c r="D208" s="3" t="n"/>
       <c r="E208" s="3" t="n"/>
       <c r="F208" s="3" t="n"/>
-      <c r="G208" s="4" t="n"/>
-      <c r="H208" s="4" t="n"/>
+      <c r="G208" s="2" t="n"/>
+      <c r="H208" s="2" t="n"/>
       <c r="I208" s="3" t="n"/>
       <c r="J208" s="3" t="n"/>
       <c r="K208" s="2" t="n"/>
@@ -3886,8 +3880,8 @@
       <c r="D209" s="3" t="n"/>
       <c r="E209" s="3" t="n"/>
       <c r="F209" s="3" t="n"/>
-      <c r="G209" s="4" t="n"/>
-      <c r="H209" s="4" t="n"/>
+      <c r="G209" s="2" t="n"/>
+      <c r="H209" s="2" t="n"/>
       <c r="I209" s="3" t="n"/>
       <c r="J209" s="3" t="n"/>
       <c r="K209" s="2" t="n"/>
@@ -3902,8 +3896,8 @@
       <c r="D210" s="3" t="n"/>
       <c r="E210" s="3" t="n"/>
       <c r="F210" s="3" t="n"/>
-      <c r="G210" s="4" t="n"/>
-      <c r="H210" s="4" t="n"/>
+      <c r="G210" s="2" t="n"/>
+      <c r="H210" s="2" t="n"/>
       <c r="I210" s="3" t="n"/>
       <c r="J210" s="3" t="n"/>
       <c r="K210" s="2" t="n"/>
@@ -3918,8 +3912,8 @@
       <c r="D211" s="3" t="n"/>
       <c r="E211" s="3" t="n"/>
       <c r="F211" s="3" t="n"/>
-      <c r="G211" s="4" t="n"/>
-      <c r="H211" s="4" t="n"/>
+      <c r="G211" s="2" t="n"/>
+      <c r="H211" s="2" t="n"/>
       <c r="I211" s="3" t="n"/>
       <c r="J211" s="3" t="n"/>
       <c r="K211" s="2" t="n"/>
@@ -3934,8 +3928,8 @@
       <c r="D212" s="3" t="n"/>
       <c r="E212" s="3" t="n"/>
       <c r="F212" s="3" t="n"/>
-      <c r="G212" s="4" t="n"/>
-      <c r="H212" s="4" t="n"/>
+      <c r="G212" s="2" t="n"/>
+      <c r="H212" s="2" t="n"/>
       <c r="I212" s="3" t="n"/>
       <c r="J212" s="3" t="n"/>
       <c r="K212" s="2" t="n"/>
@@ -3950,8 +3944,8 @@
       <c r="D213" s="3" t="n"/>
       <c r="E213" s="3" t="n"/>
       <c r="F213" s="3" t="n"/>
-      <c r="G213" s="4" t="n"/>
-      <c r="H213" s="4" t="n"/>
+      <c r="G213" s="2" t="n"/>
+      <c r="H213" s="2" t="n"/>
       <c r="I213" s="3" t="n"/>
       <c r="J213" s="3" t="n"/>
       <c r="K213" s="2" t="n"/>
@@ -3966,8 +3960,8 @@
       <c r="D214" s="3" t="n"/>
       <c r="E214" s="3" t="n"/>
       <c r="F214" s="3" t="n"/>
-      <c r="G214" s="4" t="n"/>
-      <c r="H214" s="4" t="n"/>
+      <c r="G214" s="2" t="n"/>
+      <c r="H214" s="2" t="n"/>
       <c r="I214" s="3" t="n"/>
       <c r="J214" s="3" t="n"/>
       <c r="K214" s="2" t="n"/>
@@ -3982,8 +3976,8 @@
       <c r="D215" s="3" t="n"/>
       <c r="E215" s="3" t="n"/>
       <c r="F215" s="3" t="n"/>
-      <c r="G215" s="4" t="n"/>
-      <c r="H215" s="4" t="n"/>
+      <c r="G215" s="2" t="n"/>
+      <c r="H215" s="2" t="n"/>
       <c r="I215" s="3" t="n"/>
       <c r="J215" s="3" t="n"/>
       <c r="K215" s="2" t="n"/>
@@ -3998,8 +3992,8 @@
       <c r="D216" s="3" t="n"/>
       <c r="E216" s="3" t="n"/>
       <c r="F216" s="3" t="n"/>
-      <c r="G216" s="4" t="n"/>
-      <c r="H216" s="4" t="n"/>
+      <c r="G216" s="2" t="n"/>
+      <c r="H216" s="2" t="n"/>
       <c r="I216" s="3" t="n"/>
       <c r="J216" s="3" t="n"/>
       <c r="K216" s="2" t="n"/>
@@ -4014,8 +4008,8 @@
       <c r="D217" s="3" t="n"/>
       <c r="E217" s="3" t="n"/>
       <c r="F217" s="3" t="n"/>
-      <c r="G217" s="4" t="n"/>
-      <c r="H217" s="4" t="n"/>
+      <c r="G217" s="2" t="n"/>
+      <c r="H217" s="2" t="n"/>
       <c r="I217" s="3" t="n"/>
       <c r="J217" s="3" t="n"/>
       <c r="K217" s="2" t="n"/>
@@ -4030,8 +4024,8 @@
       <c r="D218" s="3" t="n"/>
       <c r="E218" s="3" t="n"/>
       <c r="F218" s="3" t="n"/>
-      <c r="G218" s="4" t="n"/>
-      <c r="H218" s="4" t="n"/>
+      <c r="G218" s="2" t="n"/>
+      <c r="H218" s="2" t="n"/>
       <c r="I218" s="3" t="n"/>
       <c r="J218" s="3" t="n"/>
       <c r="K218" s="2" t="n"/>
@@ -4046,8 +4040,8 @@
       <c r="D219" s="3" t="n"/>
       <c r="E219" s="3" t="n"/>
       <c r="F219" s="3" t="n"/>
-      <c r="G219" s="4" t="n"/>
-      <c r="H219" s="4" t="n"/>
+      <c r="G219" s="2" t="n"/>
+      <c r="H219" s="2" t="n"/>
       <c r="I219" s="3" t="n"/>
       <c r="J219" s="3" t="n"/>
       <c r="K219" s="2" t="n"/>
@@ -4062,8 +4056,8 @@
       <c r="D220" s="3" t="n"/>
       <c r="E220" s="3" t="n"/>
       <c r="F220" s="3" t="n"/>
-      <c r="G220" s="4" t="n"/>
-      <c r="H220" s="4" t="n"/>
+      <c r="G220" s="2" t="n"/>
+      <c r="H220" s="2" t="n"/>
       <c r="I220" s="3" t="n"/>
       <c r="J220" s="3" t="n"/>
       <c r="K220" s="2" t="n"/>
@@ -4078,8 +4072,8 @@
       <c r="D221" s="3" t="n"/>
       <c r="E221" s="3" t="n"/>
       <c r="F221" s="3" t="n"/>
-      <c r="G221" s="4" t="n"/>
-      <c r="H221" s="4" t="n"/>
+      <c r="G221" s="2" t="n"/>
+      <c r="H221" s="2" t="n"/>
       <c r="I221" s="3" t="n"/>
       <c r="J221" s="3" t="n"/>
       <c r="K221" s="2" t="n"/>
@@ -4094,8 +4088,8 @@
       <c r="D222" s="3" t="n"/>
       <c r="E222" s="3" t="n"/>
       <c r="F222" s="3" t="n"/>
-      <c r="G222" s="4" t="n"/>
-      <c r="H222" s="4" t="n"/>
+      <c r="G222" s="2" t="n"/>
+      <c r="H222" s="2" t="n"/>
       <c r="I222" s="3" t="n"/>
       <c r="J222" s="3" t="n"/>
       <c r="K222" s="2" t="n"/>
@@ -4110,8 +4104,8 @@
       <c r="D223" s="3" t="n"/>
       <c r="E223" s="3" t="n"/>
       <c r="F223" s="3" t="n"/>
-      <c r="G223" s="4" t="n"/>
-      <c r="H223" s="4" t="n"/>
+      <c r="G223" s="2" t="n"/>
+      <c r="H223" s="2" t="n"/>
       <c r="I223" s="3" t="n"/>
       <c r="J223" s="3" t="n"/>
       <c r="K223" s="2" t="n"/>
@@ -4126,8 +4120,8 @@
       <c r="D224" s="3" t="n"/>
       <c r="E224" s="3" t="n"/>
       <c r="F224" s="3" t="n"/>
-      <c r="G224" s="4" t="n"/>
-      <c r="H224" s="4" t="n"/>
+      <c r="G224" s="2" t="n"/>
+      <c r="H224" s="2" t="n"/>
       <c r="I224" s="3" t="n"/>
       <c r="J224" s="3" t="n"/>
       <c r="K224" s="2" t="n"/>
@@ -4142,8 +4136,8 @@
       <c r="D225" s="3" t="n"/>
       <c r="E225" s="3" t="n"/>
       <c r="F225" s="3" t="n"/>
-      <c r="G225" s="4" t="n"/>
-      <c r="H225" s="4" t="n"/>
+      <c r="G225" s="2" t="n"/>
+      <c r="H225" s="2" t="n"/>
       <c r="I225" s="3" t="n"/>
       <c r="J225" s="3" t="n"/>
       <c r="K225" s="2" t="n"/>
@@ -4158,8 +4152,8 @@
       <c r="D226" s="3" t="n"/>
       <c r="E226" s="3" t="n"/>
       <c r="F226" s="3" t="n"/>
-      <c r="G226" s="4" t="n"/>
-      <c r="H226" s="4" t="n"/>
+      <c r="G226" s="2" t="n"/>
+      <c r="H226" s="2" t="n"/>
       <c r="I226" s="3" t="n"/>
       <c r="J226" s="3" t="n"/>
       <c r="K226" s="2" t="n"/>
@@ -4174,8 +4168,8 @@
       <c r="D227" s="3" t="n"/>
       <c r="E227" s="3" t="n"/>
       <c r="F227" s="3" t="n"/>
-      <c r="G227" s="4" t="n"/>
-      <c r="H227" s="4" t="n"/>
+      <c r="G227" s="2" t="n"/>
+      <c r="H227" s="2" t="n"/>
       <c r="I227" s="3" t="n"/>
       <c r="J227" s="3" t="n"/>
       <c r="K227" s="2" t="n"/>
@@ -4190,8 +4184,8 @@
       <c r="D228" s="3" t="n"/>
       <c r="E228" s="3" t="n"/>
       <c r="F228" s="3" t="n"/>
-      <c r="G228" s="4" t="n"/>
-      <c r="H228" s="4" t="n"/>
+      <c r="G228" s="2" t="n"/>
+      <c r="H228" s="2" t="n"/>
       <c r="I228" s="3" t="n"/>
       <c r="J228" s="3" t="n"/>
       <c r="K228" s="2" t="n"/>
@@ -4206,8 +4200,8 @@
       <c r="D229" s="3" t="n"/>
       <c r="E229" s="3" t="n"/>
       <c r="F229" s="3" t="n"/>
-      <c r="G229" s="4" t="n"/>
-      <c r="H229" s="4" t="n"/>
+      <c r="G229" s="2" t="n"/>
+      <c r="H229" s="2" t="n"/>
       <c r="I229" s="3" t="n"/>
       <c r="J229" s="3" t="n"/>
       <c r="K229" s="2" t="n"/>
@@ -4222,8 +4216,8 @@
       <c r="D230" s="3" t="n"/>
       <c r="E230" s="3" t="n"/>
       <c r="F230" s="3" t="n"/>
-      <c r="G230" s="4" t="n"/>
-      <c r="H230" s="4" t="n"/>
+      <c r="G230" s="2" t="n"/>
+      <c r="H230" s="2" t="n"/>
       <c r="I230" s="3" t="n"/>
       <c r="J230" s="3" t="n"/>
       <c r="K230" s="2" t="n"/>
@@ -4238,8 +4232,8 @@
       <c r="D231" s="3" t="n"/>
       <c r="E231" s="3" t="n"/>
       <c r="F231" s="3" t="n"/>
-      <c r="G231" s="4" t="n"/>
-      <c r="H231" s="4" t="n"/>
+      <c r="G231" s="2" t="n"/>
+      <c r="H231" s="2" t="n"/>
       <c r="I231" s="3" t="n"/>
       <c r="J231" s="3" t="n"/>
       <c r="K231" s="2" t="n"/>
@@ -4254,8 +4248,8 @@
       <c r="D232" s="3" t="n"/>
       <c r="E232" s="3" t="n"/>
       <c r="F232" s="3" t="n"/>
-      <c r="G232" s="4" t="n"/>
-      <c r="H232" s="4" t="n"/>
+      <c r="G232" s="2" t="n"/>
+      <c r="H232" s="2" t="n"/>
       <c r="I232" s="3" t="n"/>
       <c r="J232" s="3" t="n"/>
       <c r="K232" s="2" t="n"/>
@@ -4270,8 +4264,8 @@
       <c r="D233" s="3" t="n"/>
       <c r="E233" s="3" t="n"/>
       <c r="F233" s="3" t="n"/>
-      <c r="G233" s="4" t="n"/>
-      <c r="H233" s="4" t="n"/>
+      <c r="G233" s="2" t="n"/>
+      <c r="H233" s="2" t="n"/>
       <c r="I233" s="3" t="n"/>
       <c r="J233" s="3" t="n"/>
       <c r="K233" s="2" t="n"/>
@@ -4286,8 +4280,8 @@
       <c r="D234" s="3" t="n"/>
       <c r="E234" s="3" t="n"/>
       <c r="F234" s="3" t="n"/>
-      <c r="G234" s="4" t="n"/>
-      <c r="H234" s="4" t="n"/>
+      <c r="G234" s="2" t="n"/>
+      <c r="H234" s="2" t="n"/>
       <c r="I234" s="3" t="n"/>
       <c r="J234" s="3" t="n"/>
       <c r="K234" s="2" t="n"/>
@@ -4302,8 +4296,8 @@
       <c r="D235" s="3" t="n"/>
       <c r="E235" s="3" t="n"/>
       <c r="F235" s="3" t="n"/>
-      <c r="G235" s="4" t="n"/>
-      <c r="H235" s="4" t="n"/>
+      <c r="G235" s="2" t="n"/>
+      <c r="H235" s="2" t="n"/>
       <c r="I235" s="3" t="n"/>
       <c r="J235" s="3" t="n"/>
       <c r="K235" s="2" t="n"/>
@@ -4318,8 +4312,8 @@
       <c r="D236" s="3" t="n"/>
       <c r="E236" s="3" t="n"/>
       <c r="F236" s="3" t="n"/>
-      <c r="G236" s="4" t="n"/>
-      <c r="H236" s="4" t="n"/>
+      <c r="G236" s="2" t="n"/>
+      <c r="H236" s="2" t="n"/>
       <c r="I236" s="3" t="n"/>
       <c r="J236" s="3" t="n"/>
       <c r="K236" s="2" t="n"/>
@@ -4334,8 +4328,8 @@
       <c r="D237" s="3" t="n"/>
       <c r="E237" s="3" t="n"/>
       <c r="F237" s="3" t="n"/>
-      <c r="G237" s="4" t="n"/>
-      <c r="H237" s="4" t="n"/>
+      <c r="G237" s="2" t="n"/>
+      <c r="H237" s="2" t="n"/>
       <c r="I237" s="3" t="n"/>
       <c r="J237" s="3" t="n"/>
       <c r="K237" s="2" t="n"/>
@@ -4350,8 +4344,8 @@
       <c r="D238" s="3" t="n"/>
       <c r="E238" s="3" t="n"/>
       <c r="F238" s="3" t="n"/>
-      <c r="G238" s="4" t="n"/>
-      <c r="H238" s="4" t="n"/>
+      <c r="G238" s="2" t="n"/>
+      <c r="H238" s="2" t="n"/>
       <c r="I238" s="3" t="n"/>
       <c r="J238" s="3" t="n"/>
       <c r="K238" s="2" t="n"/>
@@ -4366,8 +4360,8 @@
       <c r="D239" s="3" t="n"/>
       <c r="E239" s="3" t="n"/>
       <c r="F239" s="3" t="n"/>
-      <c r="G239" s="4" t="n"/>
-      <c r="H239" s="4" t="n"/>
+      <c r="G239" s="2" t="n"/>
+      <c r="H239" s="2" t="n"/>
       <c r="I239" s="3" t="n"/>
       <c r="J239" s="3" t="n"/>
       <c r="K239" s="2" t="n"/>
@@ -4382,8 +4376,8 @@
       <c r="D240" s="3" t="n"/>
       <c r="E240" s="3" t="n"/>
       <c r="F240" s="3" t="n"/>
-      <c r="G240" s="4" t="n"/>
-      <c r="H240" s="4" t="n"/>
+      <c r="G240" s="2" t="n"/>
+      <c r="H240" s="2" t="n"/>
       <c r="I240" s="3" t="n"/>
       <c r="J240" s="3" t="n"/>
       <c r="K240" s="2" t="n"/>
@@ -4398,8 +4392,8 @@
       <c r="D241" s="3" t="n"/>
       <c r="E241" s="3" t="n"/>
       <c r="F241" s="3" t="n"/>
-      <c r="G241" s="4" t="n"/>
-      <c r="H241" s="4" t="n"/>
+      <c r="G241" s="2" t="n"/>
+      <c r="H241" s="2" t="n"/>
       <c r="I241" s="3" t="n"/>
       <c r="J241" s="3" t="n"/>
       <c r="K241" s="2" t="n"/>
@@ -4414,8 +4408,8 @@
       <c r="D242" s="3" t="n"/>
       <c r="E242" s="3" t="n"/>
       <c r="F242" s="3" t="n"/>
-      <c r="G242" s="4" t="n"/>
-      <c r="H242" s="4" t="n"/>
+      <c r="G242" s="2" t="n"/>
+      <c r="H242" s="2" t="n"/>
       <c r="I242" s="3" t="n"/>
       <c r="J242" s="3" t="n"/>
       <c r="K242" s="2" t="n"/>
@@ -4430,8 +4424,8 @@
       <c r="D243" s="3" t="n"/>
       <c r="E243" s="3" t="n"/>
       <c r="F243" s="3" t="n"/>
-      <c r="G243" s="4" t="n"/>
-      <c r="H243" s="4" t="n"/>
+      <c r="G243" s="2" t="n"/>
+      <c r="H243" s="2" t="n"/>
       <c r="I243" s="3" t="n"/>
       <c r="J243" s="3" t="n"/>
       <c r="K243" s="2" t="n"/>
@@ -4446,8 +4440,8 @@
       <c r="D244" s="3" t="n"/>
       <c r="E244" s="3" t="n"/>
       <c r="F244" s="3" t="n"/>
-      <c r="G244" s="4" t="n"/>
-      <c r="H244" s="4" t="n"/>
+      <c r="G244" s="2" t="n"/>
+      <c r="H244" s="2" t="n"/>
       <c r="I244" s="3" t="n"/>
       <c r="J244" s="3" t="n"/>
       <c r="K244" s="2" t="n"/>
@@ -4462,8 +4456,8 @@
       <c r="D245" s="3" t="n"/>
       <c r="E245" s="3" t="n"/>
       <c r="F245" s="3" t="n"/>
-      <c r="G245" s="4" t="n"/>
-      <c r="H245" s="4" t="n"/>
+      <c r="G245" s="2" t="n"/>
+      <c r="H245" s="2" t="n"/>
       <c r="I245" s="3" t="n"/>
       <c r="J245" s="3" t="n"/>
       <c r="K245" s="2" t="n"/>
@@ -4478,8 +4472,8 @@
       <c r="D246" s="3" t="n"/>
       <c r="E246" s="3" t="n"/>
       <c r="F246" s="3" t="n"/>
-      <c r="G246" s="4" t="n"/>
-      <c r="H246" s="4" t="n"/>
+      <c r="G246" s="2" t="n"/>
+      <c r="H246" s="2" t="n"/>
       <c r="I246" s="3" t="n"/>
       <c r="J246" s="3" t="n"/>
       <c r="K246" s="2" t="n"/>
@@ -4494,8 +4488,8 @@
       <c r="D247" s="3" t="n"/>
       <c r="E247" s="3" t="n"/>
       <c r="F247" s="3" t="n"/>
-      <c r="G247" s="4" t="n"/>
-      <c r="H247" s="4" t="n"/>
+      <c r="G247" s="2" t="n"/>
+      <c r="H247" s="2" t="n"/>
       <c r="I247" s="3" t="n"/>
       <c r="J247" s="3" t="n"/>
       <c r="K247" s="2" t="n"/>
@@ -4510,8 +4504,8 @@
       <c r="D248" s="3" t="n"/>
       <c r="E248" s="3" t="n"/>
       <c r="F248" s="3" t="n"/>
-      <c r="G248" s="4" t="n"/>
-      <c r="H248" s="4" t="n"/>
+      <c r="G248" s="2" t="n"/>
+      <c r="H248" s="2" t="n"/>
       <c r="I248" s="3" t="n"/>
       <c r="J248" s="3" t="n"/>
       <c r="K248" s="2" t="n"/>
@@ -4526,8 +4520,8 @@
       <c r="D249" s="3" t="n"/>
       <c r="E249" s="3" t="n"/>
       <c r="F249" s="3" t="n"/>
-      <c r="G249" s="4" t="n"/>
-      <c r="H249" s="4" t="n"/>
+      <c r="G249" s="2" t="n"/>
+      <c r="H249" s="2" t="n"/>
       <c r="I249" s="3" t="n"/>
       <c r="J249" s="3" t="n"/>
       <c r="K249" s="2" t="n"/>
@@ -4542,8 +4536,8 @@
       <c r="D250" s="3" t="n"/>
       <c r="E250" s="3" t="n"/>
       <c r="F250" s="3" t="n"/>
-      <c r="G250" s="4" t="n"/>
-      <c r="H250" s="4" t="n"/>
+      <c r="G250" s="2" t="n"/>
+      <c r="H250" s="2" t="n"/>
       <c r="I250" s="3" t="n"/>
       <c r="J250" s="3" t="n"/>
       <c r="K250" s="2" t="n"/>
@@ -4558,8 +4552,8 @@
       <c r="D251" s="3" t="n"/>
       <c r="E251" s="3" t="n"/>
       <c r="F251" s="3" t="n"/>
-      <c r="G251" s="4" t="n"/>
-      <c r="H251" s="4" t="n"/>
+      <c r="G251" s="2" t="n"/>
+      <c r="H251" s="2" t="n"/>
       <c r="I251" s="3" t="n"/>
       <c r="J251" s="3" t="n"/>
       <c r="K251" s="2" t="n"/>
@@ -4574,8 +4568,8 @@
       <c r="D252" s="3" t="n"/>
       <c r="E252" s="3" t="n"/>
       <c r="F252" s="3" t="n"/>
-      <c r="G252" s="4" t="n"/>
-      <c r="H252" s="4" t="n"/>
+      <c r="G252" s="2" t="n"/>
+      <c r="H252" s="2" t="n"/>
       <c r="I252" s="3" t="n"/>
       <c r="J252" s="3" t="n"/>
       <c r="K252" s="2" t="n"/>
@@ -4590,8 +4584,8 @@
       <c r="D253" s="3" t="n"/>
       <c r="E253" s="3" t="n"/>
       <c r="F253" s="3" t="n"/>
-      <c r="G253" s="4" t="n"/>
-      <c r="H253" s="4" t="n"/>
+      <c r="G253" s="2" t="n"/>
+      <c r="H253" s="2" t="n"/>
       <c r="I253" s="3" t="n"/>
       <c r="J253" s="3" t="n"/>
       <c r="K253" s="2" t="n"/>
@@ -4606,8 +4600,8 @@
       <c r="D254" s="3" t="n"/>
       <c r="E254" s="3" t="n"/>
       <c r="F254" s="3" t="n"/>
-      <c r="G254" s="4" t="n"/>
-      <c r="H254" s="4" t="n"/>
+      <c r="G254" s="2" t="n"/>
+      <c r="H254" s="2" t="n"/>
       <c r="I254" s="3" t="n"/>
       <c r="J254" s="3" t="n"/>
       <c r="K254" s="2" t="n"/>
@@ -4622,8 +4616,8 @@
       <c r="D255" s="3" t="n"/>
       <c r="E255" s="3" t="n"/>
       <c r="F255" s="3" t="n"/>
-      <c r="G255" s="4" t="n"/>
-      <c r="H255" s="4" t="n"/>
+      <c r="G255" s="2" t="n"/>
+      <c r="H255" s="2" t="n"/>
       <c r="I255" s="3" t="n"/>
       <c r="J255" s="3" t="n"/>
       <c r="K255" s="2" t="n"/>
@@ -4638,8 +4632,8 @@
       <c r="D256" s="3" t="n"/>
       <c r="E256" s="3" t="n"/>
       <c r="F256" s="3" t="n"/>
-      <c r="G256" s="4" t="n"/>
-      <c r="H256" s="4" t="n"/>
+      <c r="G256" s="2" t="n"/>
+      <c r="H256" s="2" t="n"/>
       <c r="I256" s="3" t="n"/>
       <c r="J256" s="3" t="n"/>
       <c r="K256" s="2" t="n"/>
@@ -4654,8 +4648,8 @@
       <c r="D257" s="3" t="n"/>
       <c r="E257" s="3" t="n"/>
       <c r="F257" s="3" t="n"/>
-      <c r="G257" s="4" t="n"/>
-      <c r="H257" s="4" t="n"/>
+      <c r="G257" s="2" t="n"/>
+      <c r="H257" s="2" t="n"/>
       <c r="I257" s="3" t="n"/>
       <c r="J257" s="3" t="n"/>
       <c r="K257" s="2" t="n"/>
@@ -4670,8 +4664,8 @@
       <c r="D258" s="3" t="n"/>
       <c r="E258" s="3" t="n"/>
       <c r="F258" s="3" t="n"/>
-      <c r="G258" s="4" t="n"/>
-      <c r="H258" s="4" t="n"/>
+      <c r="G258" s="2" t="n"/>
+      <c r="H258" s="2" t="n"/>
       <c r="I258" s="3" t="n"/>
       <c r="J258" s="3" t="n"/>
       <c r="K258" s="2" t="n"/>
@@ -4686,8 +4680,8 @@
       <c r="D259" s="3" t="n"/>
       <c r="E259" s="3" t="n"/>
       <c r="F259" s="3" t="n"/>
-      <c r="G259" s="4" t="n"/>
-      <c r="H259" s="4" t="n"/>
+      <c r="G259" s="2" t="n"/>
+      <c r="H259" s="2" t="n"/>
       <c r="I259" s="3" t="n"/>
       <c r="J259" s="3" t="n"/>
       <c r="K259" s="2" t="n"/>
@@ -4702,8 +4696,8 @@
       <c r="D260" s="3" t="n"/>
       <c r="E260" s="3" t="n"/>
       <c r="F260" s="3" t="n"/>
-      <c r="G260" s="4" t="n"/>
-      <c r="H260" s="4" t="n"/>
+      <c r="G260" s="2" t="n"/>
+      <c r="H260" s="2" t="n"/>
       <c r="I260" s="3" t="n"/>
       <c r="J260" s="3" t="n"/>
       <c r="K260" s="2" t="n"/>
@@ -4718,8 +4712,8 @@
       <c r="D261" s="3" t="n"/>
       <c r="E261" s="3" t="n"/>
       <c r="F261" s="3" t="n"/>
-      <c r="G261" s="4" t="n"/>
-      <c r="H261" s="4" t="n"/>
+      <c r="G261" s="2" t="n"/>
+      <c r="H261" s="2" t="n"/>
       <c r="I261" s="3" t="n"/>
       <c r="J261" s="3" t="n"/>
       <c r="K261" s="2" t="n"/>
@@ -4734,8 +4728,8 @@
       <c r="D262" s="3" t="n"/>
       <c r="E262" s="3" t="n"/>
       <c r="F262" s="3" t="n"/>
-      <c r="G262" s="4" t="n"/>
-      <c r="H262" s="4" t="n"/>
+      <c r="G262" s="2" t="n"/>
+      <c r="H262" s="2" t="n"/>
       <c r="I262" s="3" t="n"/>
       <c r="J262" s="3" t="n"/>
       <c r="K262" s="2" t="n"/>
@@ -4750,8 +4744,8 @@
       <c r="D263" s="3" t="n"/>
       <c r="E263" s="3" t="n"/>
       <c r="F263" s="3" t="n"/>
-      <c r="G263" s="4" t="n"/>
-      <c r="H263" s="4" t="n"/>
+      <c r="G263" s="2" t="n"/>
+      <c r="H263" s="2" t="n"/>
       <c r="I263" s="3" t="n"/>
       <c r="J263" s="3" t="n"/>
       <c r="K263" s="2" t="n"/>
@@ -4766,8 +4760,8 @@
       <c r="D264" s="3" t="n"/>
       <c r="E264" s="3" t="n"/>
       <c r="F264" s="3" t="n"/>
-      <c r="G264" s="4" t="n"/>
-      <c r="H264" s="4" t="n"/>
+      <c r="G264" s="2" t="n"/>
+      <c r="H264" s="2" t="n"/>
       <c r="I264" s="3" t="n"/>
       <c r="J264" s="3" t="n"/>
       <c r="K264" s="2" t="n"/>
@@ -4782,8 +4776,8 @@
       <c r="D265" s="3" t="n"/>
       <c r="E265" s="3" t="n"/>
       <c r="F265" s="3" t="n"/>
-      <c r="G265" s="4" t="n"/>
-      <c r="H265" s="4" t="n"/>
+      <c r="G265" s="2" t="n"/>
+      <c r="H265" s="2" t="n"/>
       <c r="I265" s="3" t="n"/>
       <c r="J265" s="3" t="n"/>
       <c r="K265" s="2" t="n"/>
@@ -4798,8 +4792,8 @@
       <c r="D266" s="3" t="n"/>
       <c r="E266" s="3" t="n"/>
       <c r="F266" s="3" t="n"/>
-      <c r="G266" s="4" t="n"/>
-      <c r="H266" s="4" t="n"/>
+      <c r="G266" s="2" t="n"/>
+      <c r="H266" s="2" t="n"/>
       <c r="I266" s="3" t="n"/>
       <c r="J266" s="3" t="n"/>
       <c r="K266" s="2" t="n"/>
@@ -4814,8 +4808,8 @@
       <c r="D267" s="3" t="n"/>
       <c r="E267" s="3" t="n"/>
       <c r="F267" s="3" t="n"/>
-      <c r="G267" s="4" t="n"/>
-      <c r="H267" s="4" t="n"/>
+      <c r="G267" s="2" t="n"/>
+      <c r="H267" s="2" t="n"/>
       <c r="I267" s="3" t="n"/>
       <c r="J267" s="3" t="n"/>
       <c r="K267" s="2" t="n"/>
@@ -4830,8 +4824,8 @@
       <c r="D268" s="3" t="n"/>
       <c r="E268" s="3" t="n"/>
       <c r="F268" s="3" t="n"/>
-      <c r="G268" s="4" t="n"/>
-      <c r="H268" s="4" t="n"/>
+      <c r="G268" s="2" t="n"/>
+      <c r="H268" s="2" t="n"/>
       <c r="I268" s="3" t="n"/>
       <c r="J268" s="3" t="n"/>
       <c r="K268" s="2" t="n"/>
@@ -4846,8 +4840,8 @@
       <c r="D269" s="3" t="n"/>
       <c r="E269" s="3" t="n"/>
       <c r="F269" s="3" t="n"/>
-      <c r="G269" s="4" t="n"/>
-      <c r="H269" s="4" t="n"/>
+      <c r="G269" s="2" t="n"/>
+      <c r="H269" s="2" t="n"/>
       <c r="I269" s="3" t="n"/>
       <c r="J269" s="3" t="n"/>
       <c r="K269" s="2" t="n"/>
@@ -4862,8 +4856,8 @@
       <c r="D270" s="3" t="n"/>
       <c r="E270" s="3" t="n"/>
       <c r="F270" s="3" t="n"/>
-      <c r="G270" s="4" t="n"/>
-      <c r="H270" s="4" t="n"/>
+      <c r="G270" s="2" t="n"/>
+      <c r="H270" s="2" t="n"/>
       <c r="I270" s="3" t="n"/>
       <c r="J270" s="3" t="n"/>
       <c r="K270" s="2" t="n"/>
@@ -4878,8 +4872,8 @@
       <c r="D271" s="3" t="n"/>
       <c r="E271" s="3" t="n"/>
       <c r="F271" s="3" t="n"/>
-      <c r="G271" s="4" t="n"/>
-      <c r="H271" s="4" t="n"/>
+      <c r="G271" s="2" t="n"/>
+      <c r="H271" s="2" t="n"/>
       <c r="I271" s="3" t="n"/>
       <c r="J271" s="3" t="n"/>
       <c r="K271" s="2" t="n"/>
@@ -4894,8 +4888,8 @@
       <c r="D272" s="3" t="n"/>
       <c r="E272" s="3" t="n"/>
       <c r="F272" s="3" t="n"/>
-      <c r="G272" s="4" t="n"/>
-      <c r="H272" s="4" t="n"/>
+      <c r="G272" s="2" t="n"/>
+      <c r="H272" s="2" t="n"/>
       <c r="I272" s="3" t="n"/>
       <c r="J272" s="3" t="n"/>
       <c r="K272" s="2" t="n"/>
@@ -4910,8 +4904,8 @@
       <c r="D273" s="3" t="n"/>
       <c r="E273" s="3" t="n"/>
       <c r="F273" s="3" t="n"/>
-      <c r="G273" s="4" t="n"/>
-      <c r="H273" s="4" t="n"/>
+      <c r="G273" s="2" t="n"/>
+      <c r="H273" s="2" t="n"/>
       <c r="I273" s="3" t="n"/>
       <c r="J273" s="3" t="n"/>
       <c r="K273" s="2" t="n"/>
@@ -4926,8 +4920,8 @@
       <c r="D274" s="3" t="n"/>
       <c r="E274" s="3" t="n"/>
       <c r="F274" s="3" t="n"/>
-      <c r="G274" s="4" t="n"/>
-      <c r="H274" s="4" t="n"/>
+      <c r="G274" s="2" t="n"/>
+      <c r="H274" s="2" t="n"/>
       <c r="I274" s="3" t="n"/>
       <c r="J274" s="3" t="n"/>
       <c r="K274" s="2" t="n"/>
@@ -4942,8 +4936,8 @@
       <c r="D275" s="3" t="n"/>
       <c r="E275" s="3" t="n"/>
       <c r="F275" s="3" t="n"/>
-      <c r="G275" s="4" t="n"/>
-      <c r="H275" s="4" t="n"/>
+      <c r="G275" s="2" t="n"/>
+      <c r="H275" s="2" t="n"/>
       <c r="I275" s="3" t="n"/>
       <c r="J275" s="3" t="n"/>
       <c r="K275" s="2" t="n"/>
@@ -4958,8 +4952,8 @@
       <c r="D276" s="3" t="n"/>
       <c r="E276" s="3" t="n"/>
       <c r="F276" s="3" t="n"/>
-      <c r="G276" s="4" t="n"/>
-      <c r="H276" s="4" t="n"/>
+      <c r="G276" s="2" t="n"/>
+      <c r="H276" s="2" t="n"/>
       <c r="I276" s="3" t="n"/>
       <c r="J276" s="3" t="n"/>
       <c r="K276" s="2" t="n"/>
@@ -4974,8 +4968,8 @@
       <c r="D277" s="3" t="n"/>
       <c r="E277" s="3" t="n"/>
       <c r="F277" s="3" t="n"/>
-      <c r="G277" s="4" t="n"/>
-      <c r="H277" s="4" t="n"/>
+      <c r="G277" s="2" t="n"/>
+      <c r="H277" s="2" t="n"/>
       <c r="I277" s="3" t="n"/>
       <c r="J277" s="3" t="n"/>
       <c r="K277" s="2" t="n"/>
@@ -4990,8 +4984,8 @@
       <c r="D278" s="3" t="n"/>
       <c r="E278" s="3" t="n"/>
       <c r="F278" s="3" t="n"/>
-      <c r="G278" s="4" t="n"/>
-      <c r="H278" s="4" t="n"/>
+      <c r="G278" s="2" t="n"/>
+      <c r="H278" s="2" t="n"/>
       <c r="I278" s="3" t="n"/>
       <c r="J278" s="3" t="n"/>
       <c r="K278" s="2" t="n"/>
@@ -5006,8 +5000,8 @@
       <c r="D279" s="3" t="n"/>
       <c r="E279" s="3" t="n"/>
       <c r="F279" s="3" t="n"/>
-      <c r="G279" s="4" t="n"/>
-      <c r="H279" s="4" t="n"/>
+      <c r="G279" s="2" t="n"/>
+      <c r="H279" s="2" t="n"/>
       <c r="I279" s="3" t="n"/>
       <c r="J279" s="3" t="n"/>
       <c r="K279" s="2" t="n"/>
@@ -5022,8 +5016,8 @@
       <c r="D280" s="3" t="n"/>
       <c r="E280" s="3" t="n"/>
       <c r="F280" s="3" t="n"/>
-      <c r="G280" s="4" t="n"/>
-      <c r="H280" s="4" t="n"/>
+      <c r="G280" s="2" t="n"/>
+      <c r="H280" s="2" t="n"/>
       <c r="I280" s="3" t="n"/>
       <c r="J280" s="3" t="n"/>
       <c r="K280" s="2" t="n"/>
@@ -5038,8 +5032,8 @@
       <c r="D281" s="3" t="n"/>
       <c r="E281" s="3" t="n"/>
       <c r="F281" s="3" t="n"/>
-      <c r="G281" s="4" t="n"/>
-      <c r="H281" s="4" t="n"/>
+      <c r="G281" s="2" t="n"/>
+      <c r="H281" s="2" t="n"/>
       <c r="I281" s="3" t="n"/>
       <c r="J281" s="3" t="n"/>
       <c r="K281" s="2" t="n"/>
@@ -5054,8 +5048,8 @@
       <c r="D282" s="3" t="n"/>
       <c r="E282" s="3" t="n"/>
       <c r="F282" s="3" t="n"/>
-      <c r="G282" s="4" t="n"/>
-      <c r="H282" s="4" t="n"/>
+      <c r="G282" s="2" t="n"/>
+      <c r="H282" s="2" t="n"/>
       <c r="I282" s="3" t="n"/>
       <c r="J282" s="3" t="n"/>
       <c r="K282" s="2" t="n"/>
@@ -5070,8 +5064,8 @@
       <c r="D283" s="3" t="n"/>
       <c r="E283" s="3" t="n"/>
       <c r="F283" s="3" t="n"/>
-      <c r="G283" s="4" t="n"/>
-      <c r="H283" s="4" t="n"/>
+      <c r="G283" s="2" t="n"/>
+      <c r="H283" s="2" t="n"/>
       <c r="I283" s="3" t="n"/>
       <c r="J283" s="3" t="n"/>
       <c r="K283" s="2" t="n"/>
@@ -5086,8 +5080,8 @@
       <c r="D284" s="3" t="n"/>
       <c r="E284" s="3" t="n"/>
       <c r="F284" s="3" t="n"/>
-      <c r="G284" s="4" t="n"/>
-      <c r="H284" s="4" t="n"/>
+      <c r="G284" s="2" t="n"/>
+      <c r="H284" s="2" t="n"/>
       <c r="I284" s="3" t="n"/>
       <c r="J284" s="3" t="n"/>
       <c r="K284" s="2" t="n"/>
@@ -5102,8 +5096,8 @@
       <c r="D285" s="3" t="n"/>
       <c r="E285" s="3" t="n"/>
       <c r="F285" s="3" t="n"/>
-      <c r="G285" s="4" t="n"/>
-      <c r="H285" s="4" t="n"/>
+      <c r="G285" s="2" t="n"/>
+      <c r="H285" s="2" t="n"/>
       <c r="I285" s="3" t="n"/>
       <c r="J285" s="3" t="n"/>
       <c r="K285" s="2" t="n"/>
@@ -5118,8 +5112,8 @@
       <c r="D286" s="3" t="n"/>
       <c r="E286" s="3" t="n"/>
       <c r="F286" s="3" t="n"/>
-      <c r="G286" s="4" t="n"/>
-      <c r="H286" s="4" t="n"/>
+      <c r="G286" s="2" t="n"/>
+      <c r="H286" s="2" t="n"/>
       <c r="I286" s="3" t="n"/>
       <c r="J286" s="3" t="n"/>
       <c r="K286" s="2" t="n"/>
@@ -5134,8 +5128,8 @@
       <c r="D287" s="3" t="n"/>
       <c r="E287" s="3" t="n"/>
       <c r="F287" s="3" t="n"/>
-      <c r="G287" s="4" t="n"/>
-      <c r="H287" s="4" t="n"/>
+      <c r="G287" s="2" t="n"/>
+      <c r="H287" s="2" t="n"/>
       <c r="I287" s="3" t="n"/>
       <c r="J287" s="3" t="n"/>
       <c r="K287" s="2" t="n"/>
@@ -5150,8 +5144,8 @@
       <c r="D288" s="3" t="n"/>
       <c r="E288" s="3" t="n"/>
       <c r="F288" s="3" t="n"/>
-      <c r="G288" s="4" t="n"/>
-      <c r="H288" s="4" t="n"/>
+      <c r="G288" s="2" t="n"/>
+      <c r="H288" s="2" t="n"/>
       <c r="I288" s="3" t="n"/>
       <c r="J288" s="3" t="n"/>
       <c r="K288" s="2" t="n"/>
@@ -5166,8 +5160,8 @@
       <c r="D289" s="3" t="n"/>
       <c r="E289" s="3" t="n"/>
       <c r="F289" s="3" t="n"/>
-      <c r="G289" s="4" t="n"/>
-      <c r="H289" s="4" t="n"/>
+      <c r="G289" s="2" t="n"/>
+      <c r="H289" s="2" t="n"/>
       <c r="I289" s="3" t="n"/>
       <c r="J289" s="3" t="n"/>
       <c r="K289" s="2" t="n"/>
@@ -5182,8 +5176,8 @@
       <c r="D290" s="3" t="n"/>
       <c r="E290" s="3" t="n"/>
       <c r="F290" s="3" t="n"/>
-      <c r="G290" s="4" t="n"/>
-      <c r="H290" s="4" t="n"/>
+      <c r="G290" s="2" t="n"/>
+      <c r="H290" s="2" t="n"/>
       <c r="I290" s="3" t="n"/>
       <c r="J290" s="3" t="n"/>
       <c r="K290" s="2" t="n"/>
@@ -5198,8 +5192,8 @@
       <c r="D291" s="3" t="n"/>
       <c r="E291" s="3" t="n"/>
       <c r="F291" s="3" t="n"/>
-      <c r="G291" s="4" t="n"/>
-      <c r="H291" s="4" t="n"/>
+      <c r="G291" s="2" t="n"/>
+      <c r="H291" s="2" t="n"/>
       <c r="I291" s="3" t="n"/>
       <c r="J291" s="3" t="n"/>
       <c r="K291" s="2" t="n"/>
@@ -5214,8 +5208,8 @@
       <c r="D292" s="3" t="n"/>
       <c r="E292" s="3" t="n"/>
       <c r="F292" s="3" t="n"/>
-      <c r="G292" s="4" t="n"/>
-      <c r="H292" s="4" t="n"/>
+      <c r="G292" s="2" t="n"/>
+      <c r="H292" s="2" t="n"/>
       <c r="I292" s="3" t="n"/>
       <c r="J292" s="3" t="n"/>
       <c r="K292" s="2" t="n"/>
@@ -5230,8 +5224,8 @@
       <c r="D293" s="3" t="n"/>
       <c r="E293" s="3" t="n"/>
       <c r="F293" s="3" t="n"/>
-      <c r="G293" s="4" t="n"/>
-      <c r="H293" s="4" t="n"/>
+      <c r="G293" s="2" t="n"/>
+      <c r="H293" s="2" t="n"/>
       <c r="I293" s="3" t="n"/>
       <c r="J293" s="3" t="n"/>
       <c r="K293" s="2" t="n"/>
@@ -5246,8 +5240,8 @@
       <c r="D294" s="3" t="n"/>
       <c r="E294" s="3" t="n"/>
       <c r="F294" s="3" t="n"/>
-      <c r="G294" s="4" t="n"/>
-      <c r="H294" s="4" t="n"/>
+      <c r="G294" s="2" t="n"/>
+      <c r="H294" s="2" t="n"/>
       <c r="I294" s="3" t="n"/>
       <c r="J294" s="3" t="n"/>
       <c r="K294" s="2" t="n"/>
@@ -5262,8 +5256,8 @@
       <c r="D295" s="3" t="n"/>
       <c r="E295" s="3" t="n"/>
       <c r="F295" s="3" t="n"/>
-      <c r="G295" s="4" t="n"/>
-      <c r="H295" s="4" t="n"/>
+      <c r="G295" s="2" t="n"/>
+      <c r="H295" s="2" t="n"/>
       <c r="I295" s="3" t="n"/>
       <c r="J295" s="3" t="n"/>
       <c r="K295" s="2" t="n"/>
@@ -5278,8 +5272,8 @@
       <c r="D296" s="3" t="n"/>
       <c r="E296" s="3" t="n"/>
       <c r="F296" s="3" t="n"/>
-      <c r="G296" s="4" t="n"/>
-      <c r="H296" s="4" t="n"/>
+      <c r="G296" s="2" t="n"/>
+      <c r="H296" s="2" t="n"/>
       <c r="I296" s="3" t="n"/>
       <c r="J296" s="3" t="n"/>
       <c r="K296" s="2" t="n"/>
@@ -5294,8 +5288,8 @@
       <c r="D297" s="3" t="n"/>
       <c r="E297" s="3" t="n"/>
       <c r="F297" s="3" t="n"/>
-      <c r="G297" s="4" t="n"/>
-      <c r="H297" s="4" t="n"/>
+      <c r="G297" s="2" t="n"/>
+      <c r="H297" s="2" t="n"/>
       <c r="I297" s="3" t="n"/>
       <c r="J297" s="3" t="n"/>
       <c r="K297" s="2" t="n"/>
@@ -5310,8 +5304,8 @@
       <c r="D298" s="3" t="n"/>
       <c r="E298" s="3" t="n"/>
       <c r="F298" s="3" t="n"/>
-      <c r="G298" s="4" t="n"/>
-      <c r="H298" s="4" t="n"/>
+      <c r="G298" s="2" t="n"/>
+      <c r="H298" s="2" t="n"/>
       <c r="I298" s="3" t="n"/>
       <c r="J298" s="3" t="n"/>
       <c r="K298" s="2" t="n"/>
@@ -5326,8 +5320,8 @@
       <c r="D299" s="3" t="n"/>
       <c r="E299" s="3" t="n"/>
       <c r="F299" s="3" t="n"/>
-      <c r="G299" s="4" t="n"/>
-      <c r="H299" s="4" t="n"/>
+      <c r="G299" s="2" t="n"/>
+      <c r="H299" s="2" t="n"/>
       <c r="I299" s="3" t="n"/>
       <c r="J299" s="3" t="n"/>
       <c r="K299" s="2" t="n"/>
@@ -5342,8 +5336,8 @@
       <c r="D300" s="3" t="n"/>
       <c r="E300" s="3" t="n"/>
       <c r="F300" s="3" t="n"/>
-      <c r="G300" s="4" t="n"/>
-      <c r="H300" s="4" t="n"/>
+      <c r="G300" s="2" t="n"/>
+      <c r="H300" s="2" t="n"/>
       <c r="I300" s="3" t="n"/>
       <c r="J300" s="3" t="n"/>
       <c r="K300" s="2" t="n"/>
@@ -5358,8 +5352,8 @@
       <c r="D301" s="3" t="n"/>
       <c r="E301" s="3" t="n"/>
       <c r="F301" s="3" t="n"/>
-      <c r="G301" s="4" t="n"/>
-      <c r="H301" s="4" t="n"/>
+      <c r="G301" s="2" t="n"/>
+      <c r="H301" s="2" t="n"/>
       <c r="I301" s="3" t="n"/>
       <c r="J301" s="3" t="n"/>
       <c r="K301" s="2" t="n"/>
@@ -5374,8 +5368,8 @@
       <c r="D302" s="3" t="n"/>
       <c r="E302" s="3" t="n"/>
       <c r="F302" s="3" t="n"/>
-      <c r="G302" s="4" t="n"/>
-      <c r="H302" s="4" t="n"/>
+      <c r="G302" s="2" t="n"/>
+      <c r="H302" s="2" t="n"/>
       <c r="I302" s="3" t="n"/>
       <c r="J302" s="3" t="n"/>
       <c r="K302" s="2" t="n"/>
@@ -5390,8 +5384,8 @@
       <c r="D303" s="3" t="n"/>
       <c r="E303" s="3" t="n"/>
       <c r="F303" s="3" t="n"/>
-      <c r="G303" s="4" t="n"/>
-      <c r="H303" s="4" t="n"/>
+      <c r="G303" s="2" t="n"/>
+      <c r="H303" s="2" t="n"/>
       <c r="I303" s="3" t="n"/>
       <c r="J303" s="3" t="n"/>
       <c r="K303" s="2" t="n"/>
@@ -5406,8 +5400,8 @@
       <c r="D304" s="3" t="n"/>
       <c r="E304" s="3" t="n"/>
       <c r="F304" s="3" t="n"/>
-      <c r="G304" s="4" t="n"/>
-      <c r="H304" s="4" t="n"/>
+      <c r="G304" s="2" t="n"/>
+      <c r="H304" s="2" t="n"/>
       <c r="I304" s="3" t="n"/>
       <c r="J304" s="3" t="n"/>
       <c r="K304" s="2" t="n"/>
@@ -5422,8 +5416,8 @@
       <c r="D305" s="3" t="n"/>
       <c r="E305" s="3" t="n"/>
       <c r="F305" s="3" t="n"/>
-      <c r="G305" s="4" t="n"/>
-      <c r="H305" s="4" t="n"/>
+      <c r="G305" s="2" t="n"/>
+      <c r="H305" s="2" t="n"/>
       <c r="I305" s="3" t="n"/>
       <c r="J305" s="3" t="n"/>
       <c r="K305" s="2" t="n"/>
@@ -5438,8 +5432,8 @@
       <c r="D306" s="3" t="n"/>
       <c r="E306" s="3" t="n"/>
       <c r="F306" s="3" t="n"/>
-      <c r="G306" s="4" t="n"/>
-      <c r="H306" s="4" t="n"/>
+      <c r="G306" s="2" t="n"/>
+      <c r="H306" s="2" t="n"/>
       <c r="I306" s="3" t="n"/>
       <c r="J306" s="3" t="n"/>
       <c r="K306" s="2" t="n"/>
@@ -5454,8 +5448,8 @@
       <c r="D307" s="3" t="n"/>
       <c r="E307" s="3" t="n"/>
       <c r="F307" s="3" t="n"/>
-      <c r="G307" s="4" t="n"/>
-      <c r="H307" s="4" t="n"/>
+      <c r="G307" s="2" t="n"/>
+      <c r="H307" s="2" t="n"/>
       <c r="I307" s="3" t="n"/>
       <c r="J307" s="3" t="n"/>
       <c r="K307" s="2" t="n"/>
@@ -5470,8 +5464,8 @@
       <c r="D308" s="3" t="n"/>
       <c r="E308" s="3" t="n"/>
       <c r="F308" s="3" t="n"/>
-      <c r="G308" s="4" t="n"/>
-      <c r="H308" s="4" t="n"/>
+      <c r="G308" s="2" t="n"/>
+      <c r="H308" s="2" t="n"/>
       <c r="I308" s="3" t="n"/>
       <c r="J308" s="3" t="n"/>
       <c r="K308" s="2" t="n"/>
@@ -5486,8 +5480,8 @@
       <c r="D309" s="3" t="n"/>
       <c r="E309" s="3" t="n"/>
       <c r="F309" s="3" t="n"/>
-      <c r="G309" s="4" t="n"/>
-      <c r="H309" s="4" t="n"/>
+      <c r="G309" s="2" t="n"/>
+      <c r="H309" s="2" t="n"/>
       <c r="I309" s="3" t="n"/>
       <c r="J309" s="3" t="n"/>
       <c r="K309" s="2" t="n"/>
@@ -5502,8 +5496,8 @@
       <c r="D310" s="3" t="n"/>
       <c r="E310" s="3" t="n"/>
       <c r="F310" s="3" t="n"/>
-      <c r="G310" s="4" t="n"/>
-      <c r="H310" s="4" t="n"/>
+      <c r="G310" s="2" t="n"/>
+      <c r="H310" s="2" t="n"/>
       <c r="I310" s="3" t="n"/>
       <c r="J310" s="3" t="n"/>
       <c r="K310" s="2" t="n"/>
@@ -5518,8 +5512,8 @@
       <c r="D311" s="3" t="n"/>
       <c r="E311" s="3" t="n"/>
       <c r="F311" s="3" t="n"/>
-      <c r="G311" s="4" t="n"/>
-      <c r="H311" s="4" t="n"/>
+      <c r="G311" s="2" t="n"/>
+      <c r="H311" s="2" t="n"/>
       <c r="I311" s="3" t="n"/>
       <c r="J311" s="3" t="n"/>
       <c r="K311" s="2" t="n"/>
@@ -5534,8 +5528,8 @@
       <c r="D312" s="3" t="n"/>
       <c r="E312" s="3" t="n"/>
       <c r="F312" s="3" t="n"/>
-      <c r="G312" s="4" t="n"/>
-      <c r="H312" s="4" t="n"/>
+      <c r="G312" s="2" t="n"/>
+      <c r="H312" s="2" t="n"/>
       <c r="I312" s="3" t="n"/>
       <c r="J312" s="3" t="n"/>
       <c r="K312" s="2" t="n"/>
@@ -5550,8 +5544,8 @@
       <c r="D313" s="3" t="n"/>
       <c r="E313" s="3" t="n"/>
       <c r="F313" s="3" t="n"/>
-      <c r="G313" s="4" t="n"/>
-      <c r="H313" s="4" t="n"/>
+      <c r="G313" s="2" t="n"/>
+      <c r="H313" s="2" t="n"/>
       <c r="I313" s="3" t="n"/>
       <c r="J313" s="3" t="n"/>
       <c r="K313" s="2" t="n"/>
@@ -5566,8 +5560,8 @@
       <c r="D314" s="3" t="n"/>
       <c r="E314" s="3" t="n"/>
       <c r="F314" s="3" t="n"/>
-      <c r="G314" s="4" t="n"/>
-      <c r="H314" s="4" t="n"/>
+      <c r="G314" s="2" t="n"/>
+      <c r="H314" s="2" t="n"/>
       <c r="I314" s="3" t="n"/>
       <c r="J314" s="3" t="n"/>
       <c r="K314" s="2" t="n"/>
@@ -5582,8 +5576,8 @@
       <c r="D315" s="3" t="n"/>
       <c r="E315" s="3" t="n"/>
       <c r="F315" s="3" t="n"/>
-      <c r="G315" s="4" t="n"/>
-      <c r="H315" s="4" t="n"/>
+      <c r="G315" s="2" t="n"/>
+      <c r="H315" s="2" t="n"/>
       <c r="I315" s="3" t="n"/>
       <c r="J315" s="3" t="n"/>
       <c r="K315" s="2" t="n"/>
@@ -5598,8 +5592,8 @@
       <c r="D316" s="3" t="n"/>
       <c r="E316" s="3" t="n"/>
       <c r="F316" s="3" t="n"/>
-      <c r="G316" s="4" t="n"/>
-      <c r="H316" s="4" t="n"/>
+      <c r="G316" s="2" t="n"/>
+      <c r="H316" s="2" t="n"/>
       <c r="I316" s="3" t="n"/>
       <c r="J316" s="3" t="n"/>
       <c r="K316" s="2" t="n"/>
@@ -5614,8 +5608,8 @@
       <c r="D317" s="3" t="n"/>
       <c r="E317" s="3" t="n"/>
       <c r="F317" s="3" t="n"/>
-      <c r="G317" s="4" t="n"/>
-      <c r="H317" s="4" t="n"/>
+      <c r="G317" s="2" t="n"/>
+      <c r="H317" s="2" t="n"/>
       <c r="I317" s="3" t="n"/>
       <c r="J317" s="3" t="n"/>
       <c r="K317" s="2" t="n"/>
@@ -5630,8 +5624,8 @@
       <c r="D318" s="3" t="n"/>
       <c r="E318" s="3" t="n"/>
       <c r="F318" s="3" t="n"/>
-      <c r="G318" s="4" t="n"/>
-      <c r="H318" s="4" t="n"/>
+      <c r="G318" s="2" t="n"/>
+      <c r="H318" s="2" t="n"/>
       <c r="I318" s="3" t="n"/>
       <c r="J318" s="3" t="n"/>
       <c r="K318" s="2" t="n"/>
@@ -5646,8 +5640,8 @@
       <c r="D319" s="3" t="n"/>
       <c r="E319" s="3" t="n"/>
       <c r="F319" s="3" t="n"/>
-      <c r="G319" s="4" t="n"/>
-      <c r="H319" s="4" t="n"/>
+      <c r="G319" s="2" t="n"/>
+      <c r="H319" s="2" t="n"/>
       <c r="I319" s="3" t="n"/>
       <c r="J319" s="3" t="n"/>
       <c r="K319" s="2" t="n"/>
@@ -5662,8 +5656,8 @@
       <c r="D320" s="3" t="n"/>
       <c r="E320" s="3" t="n"/>
       <c r="F320" s="3" t="n"/>
-      <c r="G320" s="4" t="n"/>
-      <c r="H320" s="4" t="n"/>
+      <c r="G320" s="2" t="n"/>
+      <c r="H320" s="2" t="n"/>
       <c r="I320" s="3" t="n"/>
       <c r="J320" s="3" t="n"/>
       <c r="K320" s="2" t="n"/>
@@ -5678,8 +5672,8 @@
       <c r="D321" s="3" t="n"/>
       <c r="E321" s="3" t="n"/>
       <c r="F321" s="3" t="n"/>
-      <c r="G321" s="4" t="n"/>
-      <c r="H321" s="4" t="n"/>
+      <c r="G321" s="2" t="n"/>
+      <c r="H321" s="2" t="n"/>
       <c r="I321" s="3" t="n"/>
       <c r="J321" s="3" t="n"/>
       <c r="K321" s="2" t="n"/>
@@ -5694,8 +5688,8 @@
       <c r="D322" s="3" t="n"/>
       <c r="E322" s="3" t="n"/>
       <c r="F322" s="3" t="n"/>
-      <c r="G322" s="4" t="n"/>
-      <c r="H322" s="4" t="n"/>
+      <c r="G322" s="2" t="n"/>
+      <c r="H322" s="2" t="n"/>
       <c r="I322" s="3" t="n"/>
       <c r="J322" s="3" t="n"/>
       <c r="K322" s="2" t="n"/>
@@ -5710,8 +5704,8 @@
       <c r="D323" s="3" t="n"/>
       <c r="E323" s="3" t="n"/>
       <c r="F323" s="3" t="n"/>
-      <c r="G323" s="4" t="n"/>
-      <c r="H323" s="4" t="n"/>
+      <c r="G323" s="2" t="n"/>
+      <c r="H323" s="2" t="n"/>
       <c r="I323" s="3" t="n"/>
       <c r="J323" s="3" t="n"/>
       <c r="K323" s="2" t="n"/>
@@ -5726,8 +5720,8 @@
       <c r="D324" s="3" t="n"/>
       <c r="E324" s="3" t="n"/>
       <c r="F324" s="3" t="n"/>
-      <c r="G324" s="4" t="n"/>
-      <c r="H324" s="4" t="n"/>
+      <c r="G324" s="2" t="n"/>
+      <c r="H324" s="2" t="n"/>
       <c r="I324" s="3" t="n"/>
       <c r="J324" s="3" t="n"/>
       <c r="K324" s="2" t="n"/>
@@ -5742,8 +5736,8 @@
       <c r="D325" s="3" t="n"/>
       <c r="E325" s="3" t="n"/>
       <c r="F325" s="3" t="n"/>
-      <c r="G325" s="4" t="n"/>
-      <c r="H325" s="4" t="n"/>
+      <c r="G325" s="2" t="n"/>
+      <c r="H325" s="2" t="n"/>
       <c r="I325" s="3" t="n"/>
       <c r="J325" s="3" t="n"/>
       <c r="K325" s="2" t="n"/>
@@ -5758,8 +5752,8 @@
       <c r="D326" s="3" t="n"/>
       <c r="E326" s="3" t="n"/>
       <c r="F326" s="3" t="n"/>
-      <c r="G326" s="4" t="n"/>
-      <c r="H326" s="4" t="n"/>
+      <c r="G326" s="2" t="n"/>
+      <c r="H326" s="2" t="n"/>
       <c r="I326" s="3" t="n"/>
       <c r="J326" s="3" t="n"/>
       <c r="K326" s="2" t="n"/>
@@ -5774,8 +5768,8 @@
       <c r="D327" s="3" t="n"/>
       <c r="E327" s="3" t="n"/>
       <c r="F327" s="3" t="n"/>
-      <c r="G327" s="4" t="n"/>
-      <c r="H327" s="4" t="n"/>
+      <c r="G327" s="2" t="n"/>
+      <c r="H327" s="2" t="n"/>
       <c r="I327" s="3" t="n"/>
       <c r="J327" s="3" t="n"/>
       <c r="K327" s="2" t="n"/>
@@ -5790,8 +5784,8 @@
       <c r="D328" s="3" t="n"/>
       <c r="E328" s="3" t="n"/>
       <c r="F328" s="3" t="n"/>
-      <c r="G328" s="4" t="n"/>
-      <c r="H328" s="4" t="n"/>
+      <c r="G328" s="2" t="n"/>
+      <c r="H328" s="2" t="n"/>
       <c r="I328" s="3" t="n"/>
       <c r="J328" s="3" t="n"/>
       <c r="K328" s="2" t="n"/>
@@ -5806,8 +5800,8 @@
       <c r="D329" s="3" t="n"/>
       <c r="E329" s="3" t="n"/>
       <c r="F329" s="3" t="n"/>
-      <c r="G329" s="4" t="n"/>
-      <c r="H329" s="4" t="n"/>
+      <c r="G329" s="2" t="n"/>
+      <c r="H329" s="2" t="n"/>
       <c r="I329" s="3" t="n"/>
       <c r="J329" s="3" t="n"/>
       <c r="K329" s="2" t="n"/>
@@ -5822,8 +5816,8 @@
       <c r="D330" s="3" t="n"/>
       <c r="E330" s="3" t="n"/>
       <c r="F330" s="3" t="n"/>
-      <c r="G330" s="4" t="n"/>
-      <c r="H330" s="4" t="n"/>
+      <c r="G330" s="2" t="n"/>
+      <c r="H330" s="2" t="n"/>
       <c r="I330" s="3" t="n"/>
       <c r="J330" s="3" t="n"/>
       <c r="K330" s="2" t="n"/>
@@ -5838,8 +5832,8 @@
       <c r="D331" s="3" t="n"/>
       <c r="E331" s="3" t="n"/>
       <c r="F331" s="3" t="n"/>
-      <c r="G331" s="4" t="n"/>
-      <c r="H331" s="4" t="n"/>
+      <c r="G331" s="2" t="n"/>
+      <c r="H331" s="2" t="n"/>
       <c r="I331" s="3" t="n"/>
       <c r="J331" s="3" t="n"/>
       <c r="K331" s="2" t="n"/>
@@ -5854,8 +5848,8 @@
       <c r="D332" s="3" t="n"/>
       <c r="E332" s="3" t="n"/>
       <c r="F332" s="3" t="n"/>
-      <c r="G332" s="4" t="n"/>
-      <c r="H332" s="4" t="n"/>
+      <c r="G332" s="2" t="n"/>
+      <c r="H332" s="2" t="n"/>
       <c r="I332" s="3" t="n"/>
       <c r="J332" s="3" t="n"/>
       <c r="K332" s="2" t="n"/>
@@ -5870,8 +5864,8 @@
       <c r="D333" s="3" t="n"/>
       <c r="E333" s="3" t="n"/>
       <c r="F333" s="3" t="n"/>
-      <c r="G333" s="4" t="n"/>
-      <c r="H333" s="4" t="n"/>
+      <c r="G333" s="2" t="n"/>
+      <c r="H333" s="2" t="n"/>
       <c r="I333" s="3" t="n"/>
       <c r="J333" s="3" t="n"/>
       <c r="K333" s="2" t="n"/>
@@ -5886,8 +5880,8 @@
       <c r="D334" s="3" t="n"/>
       <c r="E334" s="3" t="n"/>
       <c r="F334" s="3" t="n"/>
-      <c r="G334" s="4" t="n"/>
-      <c r="H334" s="4" t="n"/>
+      <c r="G334" s="2" t="n"/>
+      <c r="H334" s="2" t="n"/>
       <c r="I334" s="3" t="n"/>
       <c r="J334" s="3" t="n"/>
       <c r="K334" s="2" t="n"/>
@@ -5902,8 +5896,8 @@
       <c r="D335" s="3" t="n"/>
       <c r="E335" s="3" t="n"/>
       <c r="F335" s="3" t="n"/>
-      <c r="G335" s="4" t="n"/>
-      <c r="H335" s="4" t="n"/>
+      <c r="G335" s="2" t="n"/>
+      <c r="H335" s="2" t="n"/>
       <c r="I335" s="3" t="n"/>
       <c r="J335" s="3" t="n"/>
       <c r="K335" s="2" t="n"/>
@@ -5918,8 +5912,8 @@
       <c r="D336" s="3" t="n"/>
       <c r="E336" s="3" t="n"/>
       <c r="F336" s="3" t="n"/>
-      <c r="G336" s="4" t="n"/>
-      <c r="H336" s="4" t="n"/>
+      <c r="G336" s="2" t="n"/>
+      <c r="H336" s="2" t="n"/>
       <c r="I336" s="3" t="n"/>
       <c r="J336" s="3" t="n"/>
       <c r="K336" s="2" t="n"/>
@@ -5934,8 +5928,8 @@
       <c r="D337" s="3" t="n"/>
       <c r="E337" s="3" t="n"/>
       <c r="F337" s="3" t="n"/>
-      <c r="G337" s="4" t="n"/>
-      <c r="H337" s="4" t="n"/>
+      <c r="G337" s="2" t="n"/>
+      <c r="H337" s="2" t="n"/>
       <c r="I337" s="3" t="n"/>
       <c r="J337" s="3" t="n"/>
       <c r="K337" s="2" t="n"/>
@@ -5950,8 +5944,8 @@
       <c r="D338" s="3" t="n"/>
       <c r="E338" s="3" t="n"/>
       <c r="F338" s="3" t="n"/>
-      <c r="G338" s="4" t="n"/>
-      <c r="H338" s="4" t="n"/>
+      <c r="G338" s="2" t="n"/>
+      <c r="H338" s="2" t="n"/>
       <c r="I338" s="3" t="n"/>
       <c r="J338" s="3" t="n"/>
       <c r="K338" s="2" t="n"/>
@@ -5966,8 +5960,8 @@
       <c r="D339" s="3" t="n"/>
       <c r="E339" s="3" t="n"/>
       <c r="F339" s="3" t="n"/>
-      <c r="G339" s="4" t="n"/>
-      <c r="H339" s="4" t="n"/>
+      <c r="G339" s="2" t="n"/>
+      <c r="H339" s="2" t="n"/>
       <c r="I339" s="3" t="n"/>
       <c r="J339" s="3" t="n"/>
       <c r="K339" s="2" t="n"/>
@@ -5982,8 +5976,8 @@
       <c r="D340" s="3" t="n"/>
       <c r="E340" s="3" t="n"/>
       <c r="F340" s="3" t="n"/>
-      <c r="G340" s="4" t="n"/>
-      <c r="H340" s="4" t="n"/>
+      <c r="G340" s="2" t="n"/>
+      <c r="H340" s="2" t="n"/>
       <c r="I340" s="3" t="n"/>
       <c r="J340" s="3" t="n"/>
       <c r="K340" s="2" t="n"/>
@@ -5998,8 +5992,8 @@
       <c r="D341" s="3" t="n"/>
       <c r="E341" s="3" t="n"/>
       <c r="F341" s="3" t="n"/>
-      <c r="G341" s="4" t="n"/>
-      <c r="H341" s="4" t="n"/>
+      <c r="G341" s="2" t="n"/>
+      <c r="H341" s="2" t="n"/>
       <c r="I341" s="3" t="n"/>
       <c r="J341" s="3" t="n"/>
       <c r="K341" s="2" t="n"/>
@@ -6014,8 +6008,8 @@
       <c r="D342" s="3" t="n"/>
       <c r="E342" s="3" t="n"/>
       <c r="F342" s="3" t="n"/>
-      <c r="G342" s="4" t="n"/>
-      <c r="H342" s="4" t="n"/>
+      <c r="G342" s="2" t="n"/>
+      <c r="H342" s="2" t="n"/>
       <c r="I342" s="3" t="n"/>
       <c r="J342" s="3" t="n"/>
       <c r="K342" s="2" t="n"/>
@@ -6030,8 +6024,8 @@
       <c r="D343" s="3" t="n"/>
       <c r="E343" s="3" t="n"/>
       <c r="F343" s="3" t="n"/>
-      <c r="G343" s="4" t="n"/>
-      <c r="H343" s="4" t="n"/>
+      <c r="G343" s="2" t="n"/>
+      <c r="H343" s="2" t="n"/>
       <c r="I343" s="3" t="n"/>
       <c r="J343" s="3" t="n"/>
       <c r="K343" s="2" t="n"/>
@@ -6046,8 +6040,8 @@
       <c r="D344" s="3" t="n"/>
       <c r="E344" s="3" t="n"/>
       <c r="F344" s="3" t="n"/>
-      <c r="G344" s="4" t="n"/>
-      <c r="H344" s="4" t="n"/>
+      <c r="G344" s="2" t="n"/>
+      <c r="H344" s="2" t="n"/>
       <c r="I344" s="3" t="n"/>
       <c r="J344" s="3" t="n"/>
       <c r="K344" s="2" t="n"/>
@@ -6062,8 +6056,8 @@
       <c r="D345" s="3" t="n"/>
       <c r="E345" s="3" t="n"/>
       <c r="F345" s="3" t="n"/>
-      <c r="G345" s="4" t="n"/>
-      <c r="H345" s="4" t="n"/>
+      <c r="G345" s="2" t="n"/>
+      <c r="H345" s="2" t="n"/>
       <c r="I345" s="3" t="n"/>
       <c r="J345" s="3" t="n"/>
       <c r="K345" s="2" t="n"/>
@@ -6078,8 +6072,8 @@
       <c r="D346" s="3" t="n"/>
       <c r="E346" s="3" t="n"/>
       <c r="F346" s="3" t="n"/>
-      <c r="G346" s="4" t="n"/>
-      <c r="H346" s="4" t="n"/>
+      <c r="G346" s="2" t="n"/>
+      <c r="H346" s="2" t="n"/>
       <c r="I346" s="3" t="n"/>
       <c r="J346" s="3" t="n"/>
       <c r="K346" s="2" t="n"/>
@@ -6094,8 +6088,8 @@
       <c r="D347" s="3" t="n"/>
       <c r="E347" s="3" t="n"/>
       <c r="F347" s="3" t="n"/>
-      <c r="G347" s="4" t="n"/>
-      <c r="H347" s="4" t="n"/>
+      <c r="G347" s="2" t="n"/>
+      <c r="H347" s="2" t="n"/>
       <c r="I347" s="3" t="n"/>
       <c r="J347" s="3" t="n"/>
       <c r="K347" s="2" t="n"/>
@@ -6110,8 +6104,8 @@
       <c r="D348" s="3" t="n"/>
       <c r="E348" s="3" t="n"/>
       <c r="F348" s="3" t="n"/>
-      <c r="G348" s="4" t="n"/>
-      <c r="H348" s="4" t="n"/>
+      <c r="G348" s="2" t="n"/>
+      <c r="H348" s="2" t="n"/>
       <c r="I348" s="3" t="n"/>
       <c r="J348" s="3" t="n"/>
       <c r="K348" s="2" t="n"/>
@@ -6126,8 +6120,8 @@
       <c r="D349" s="3" t="n"/>
       <c r="E349" s="3" t="n"/>
       <c r="F349" s="3" t="n"/>
-      <c r="G349" s="4" t="n"/>
-      <c r="H349" s="4" t="n"/>
+      <c r="G349" s="2" t="n"/>
+      <c r="H349" s="2" t="n"/>
       <c r="I349" s="3" t="n"/>
       <c r="J349" s="3" t="n"/>
       <c r="K349" s="2" t="n"/>
@@ -6142,8 +6136,8 @@
       <c r="D350" s="3" t="n"/>
       <c r="E350" s="3" t="n"/>
       <c r="F350" s="3" t="n"/>
-      <c r="G350" s="4" t="n"/>
-      <c r="H350" s="4" t="n"/>
+      <c r="G350" s="2" t="n"/>
+      <c r="H350" s="2" t="n"/>
       <c r="I350" s="3" t="n"/>
       <c r="J350" s="3" t="n"/>
       <c r="K350" s="2" t="n"/>
@@ -6158,8 +6152,8 @@
       <c r="D351" s="3" t="n"/>
       <c r="E351" s="3" t="n"/>
       <c r="F351" s="3" t="n"/>
-      <c r="G351" s="4" t="n"/>
-      <c r="H351" s="4" t="n"/>
+      <c r="G351" s="2" t="n"/>
+      <c r="H351" s="2" t="n"/>
       <c r="I351" s="3" t="n"/>
       <c r="J351" s="3" t="n"/>
       <c r="K351" s="2" t="n"/>
@@ -6174,8 +6168,8 @@
       <c r="D352" s="3" t="n"/>
       <c r="E352" s="3" t="n"/>
       <c r="F352" s="3" t="n"/>
-      <c r="G352" s="4" t="n"/>
-      <c r="H352" s="4" t="n"/>
+      <c r="G352" s="2" t="n"/>
+      <c r="H352" s="2" t="n"/>
       <c r="I352" s="3" t="n"/>
       <c r="J352" s="3" t="n"/>
       <c r="K352" s="2" t="n"/>
@@ -6190,8 +6184,8 @@
       <c r="D353" s="3" t="n"/>
       <c r="E353" s="3" t="n"/>
       <c r="F353" s="3" t="n"/>
-      <c r="G353" s="4" t="n"/>
-      <c r="H353" s="4" t="n"/>
+      <c r="G353" s="2" t="n"/>
+      <c r="H353" s="2" t="n"/>
       <c r="I353" s="3" t="n"/>
       <c r="J353" s="3" t="n"/>
       <c r="K353" s="2" t="n"/>
@@ -6206,8 +6200,8 @@
       <c r="D354" s="3" t="n"/>
       <c r="E354" s="3" t="n"/>
       <c r="F354" s="3" t="n"/>
-      <c r="G354" s="4" t="n"/>
-      <c r="H354" s="4" t="n"/>
+      <c r="G354" s="2" t="n"/>
+      <c r="H354" s="2" t="n"/>
       <c r="I354" s="3" t="n"/>
       <c r="J354" s="3" t="n"/>
       <c r="K354" s="2" t="n"/>
@@ -6222,8 +6216,8 @@
       <c r="D355" s="3" t="n"/>
       <c r="E355" s="3" t="n"/>
       <c r="F355" s="3" t="n"/>
-      <c r="G355" s="4" t="n"/>
-      <c r="H355" s="4" t="n"/>
+      <c r="G355" s="2" t="n"/>
+      <c r="H355" s="2" t="n"/>
       <c r="I355" s="3" t="n"/>
       <c r="J355" s="3" t="n"/>
       <c r="K355" s="2" t="n"/>
@@ -6238,8 +6232,8 @@
       <c r="D356" s="3" t="n"/>
       <c r="E356" s="3" t="n"/>
       <c r="F356" s="3" t="n"/>
-      <c r="G356" s="4" t="n"/>
-      <c r="H356" s="4" t="n"/>
+      <c r="G356" s="2" t="n"/>
+      <c r="H356" s="2" t="n"/>
       <c r="I356" s="3" t="n"/>
       <c r="J356" s="3" t="n"/>
       <c r="K356" s="2" t="n"/>
@@ -6254,8 +6248,8 @@
       <c r="D357" s="3" t="n"/>
       <c r="E357" s="3" t="n"/>
       <c r="F357" s="3" t="n"/>
-      <c r="G357" s="4" t="n"/>
-      <c r="H357" s="4" t="n"/>
+      <c r="G357" s="2" t="n"/>
+      <c r="H357" s="2" t="n"/>
       <c r="I357" s="3" t="n"/>
       <c r="J357" s="3" t="n"/>
       <c r="K357" s="2" t="n"/>
@@ -6270,8 +6264,8 @@
       <c r="D358" s="3" t="n"/>
       <c r="E358" s="3" t="n"/>
       <c r="F358" s="3" t="n"/>
-      <c r="G358" s="4" t="n"/>
-      <c r="H358" s="4" t="n"/>
+      <c r="G358" s="2" t="n"/>
+      <c r="H358" s="2" t="n"/>
       <c r="I358" s="3" t="n"/>
       <c r="J358" s="3" t="n"/>
       <c r="K358" s="2" t="n"/>
@@ -6286,8 +6280,8 @@
       <c r="D359" s="3" t="n"/>
       <c r="E359" s="3" t="n"/>
       <c r="F359" s="3" t="n"/>
-      <c r="G359" s="4" t="n"/>
-      <c r="H359" s="4" t="n"/>
+      <c r="G359" s="2" t="n"/>
+      <c r="H359" s="2" t="n"/>
       <c r="I359" s="3" t="n"/>
       <c r="J359" s="3" t="n"/>
       <c r="K359" s="2" t="n"/>
@@ -6302,8 +6296,8 @@
       <c r="D360" s="3" t="n"/>
       <c r="E360" s="3" t="n"/>
       <c r="F360" s="3" t="n"/>
-      <c r="G360" s="4" t="n"/>
-      <c r="H360" s="4" t="n"/>
+      <c r="G360" s="2" t="n"/>
+      <c r="H360" s="2" t="n"/>
       <c r="I360" s="3" t="n"/>
       <c r="J360" s="3" t="n"/>
       <c r="K360" s="2" t="n"/>
@@ -6318,8 +6312,8 @@
       <c r="D361" s="3" t="n"/>
       <c r="E361" s="3" t="n"/>
       <c r="F361" s="3" t="n"/>
-      <c r="G361" s="4" t="n"/>
-      <c r="H361" s="4" t="n"/>
+      <c r="G361" s="2" t="n"/>
+      <c r="H361" s="2" t="n"/>
       <c r="I361" s="3" t="n"/>
       <c r="J361" s="3" t="n"/>
       <c r="K361" s="2" t="n"/>
@@ -6334,8 +6328,8 @@
       <c r="D362" s="3" t="n"/>
       <c r="E362" s="3" t="n"/>
       <c r="F362" s="3" t="n"/>
-      <c r="G362" s="4" t="n"/>
-      <c r="H362" s="4" t="n"/>
+      <c r="G362" s="2" t="n"/>
+      <c r="H362" s="2" t="n"/>
       <c r="I362" s="3" t="n"/>
       <c r="J362" s="3" t="n"/>
       <c r="K362" s="2" t="n"/>
@@ -6350,8 +6344,8 @@
       <c r="D363" s="3" t="n"/>
       <c r="E363" s="3" t="n"/>
       <c r="F363" s="3" t="n"/>
-      <c r="G363" s="4" t="n"/>
-      <c r="H363" s="4" t="n"/>
+      <c r="G363" s="2" t="n"/>
+      <c r="H363" s="2" t="n"/>
       <c r="I363" s="3" t="n"/>
       <c r="J363" s="3" t="n"/>
       <c r="K363" s="2" t="n"/>
@@ -6366,8 +6360,8 @@
       <c r="D364" s="3" t="n"/>
       <c r="E364" s="3" t="n"/>
       <c r="F364" s="3" t="n"/>
-      <c r="G364" s="4" t="n"/>
-      <c r="H364" s="4" t="n"/>
+      <c r="G364" s="2" t="n"/>
+      <c r="H364" s="2" t="n"/>
       <c r="I364" s="3" t="n"/>
       <c r="J364" s="3" t="n"/>
       <c r="K364" s="2" t="n"/>
@@ -6382,8 +6376,8 @@
       <c r="D365" s="3" t="n"/>
       <c r="E365" s="3" t="n"/>
       <c r="F365" s="3" t="n"/>
-      <c r="G365" s="4" t="n"/>
-      <c r="H365" s="4" t="n"/>
+      <c r="G365" s="2" t="n"/>
+      <c r="H365" s="2" t="n"/>
       <c r="I365" s="3" t="n"/>
       <c r="J365" s="3" t="n"/>
       <c r="K365" s="2" t="n"/>
@@ -6398,8 +6392,8 @@
       <c r="D366" s="3" t="n"/>
       <c r="E366" s="3" t="n"/>
       <c r="F366" s="3" t="n"/>
-      <c r="G366" s="4" t="n"/>
-      <c r="H366" s="4" t="n"/>
+      <c r="G366" s="2" t="n"/>
+      <c r="H366" s="2" t="n"/>
       <c r="I366" s="3" t="n"/>
       <c r="J366" s="3" t="n"/>
       <c r="K366" s="2" t="n"/>
@@ -6414,8 +6408,8 @@
       <c r="D367" s="3" t="n"/>
       <c r="E367" s="3" t="n"/>
       <c r="F367" s="3" t="n"/>
-      <c r="G367" s="4" t="n"/>
-      <c r="H367" s="4" t="n"/>
+      <c r="G367" s="2" t="n"/>
+      <c r="H367" s="2" t="n"/>
       <c r="I367" s="3" t="n"/>
       <c r="J367" s="3" t="n"/>
       <c r="K367" s="2" t="n"/>
@@ -6430,8 +6424,8 @@
       <c r="D368" s="3" t="n"/>
       <c r="E368" s="3" t="n"/>
       <c r="F368" s="3" t="n"/>
-      <c r="G368" s="4" t="n"/>
-      <c r="H368" s="4" t="n"/>
+      <c r="G368" s="2" t="n"/>
+      <c r="H368" s="2" t="n"/>
       <c r="I368" s="3" t="n"/>
       <c r="J368" s="3" t="n"/>
       <c r="K368" s="2" t="n"/>
@@ -6446,8 +6440,8 @@
       <c r="D369" s="3" t="n"/>
       <c r="E369" s="3" t="n"/>
       <c r="F369" s="3" t="n"/>
-      <c r="G369" s="4" t="n"/>
-      <c r="H369" s="4" t="n"/>
+      <c r="G369" s="2" t="n"/>
+      <c r="H369" s="2" t="n"/>
       <c r="I369" s="3" t="n"/>
       <c r="J369" s="3" t="n"/>
       <c r="K369" s="2" t="n"/>
@@ -6462,8 +6456,8 @@
       <c r="D370" s="3" t="n"/>
       <c r="E370" s="3" t="n"/>
       <c r="F370" s="3" t="n"/>
-      <c r="G370" s="4" t="n"/>
-      <c r="H370" s="4" t="n"/>
+      <c r="G370" s="2" t="n"/>
+      <c r="H370" s="2" t="n"/>
       <c r="I370" s="3" t="n"/>
       <c r="J370" s="3" t="n"/>
       <c r="K370" s="2" t="n"/>
@@ -6478,8 +6472,8 @@
       <c r="D371" s="3" t="n"/>
       <c r="E371" s="3" t="n"/>
       <c r="F371" s="3" t="n"/>
-      <c r="G371" s="4" t="n"/>
-      <c r="H371" s="4" t="n"/>
+      <c r="G371" s="2" t="n"/>
+      <c r="H371" s="2" t="n"/>
       <c r="I371" s="3" t="n"/>
       <c r="J371" s="3" t="n"/>
       <c r="K371" s="2" t="n"/>
@@ -6494,8 +6488,8 @@
       <c r="D372" s="3" t="n"/>
       <c r="E372" s="3" t="n"/>
       <c r="F372" s="3" t="n"/>
-      <c r="G372" s="4" t="n"/>
-      <c r="H372" s="4" t="n"/>
+      <c r="G372" s="2" t="n"/>
+      <c r="H372" s="2" t="n"/>
       <c r="I372" s="3" t="n"/>
       <c r="J372" s="3" t="n"/>
       <c r="K372" s="2" t="n"/>
@@ -6510,8 +6504,8 @@
       <c r="D373" s="3" t="n"/>
       <c r="E373" s="3" t="n"/>
       <c r="F373" s="3" t="n"/>
-      <c r="G373" s="4" t="n"/>
-      <c r="H373" s="4" t="n"/>
+      <c r="G373" s="2" t="n"/>
+      <c r="H373" s="2" t="n"/>
       <c r="I373" s="3" t="n"/>
       <c r="J373" s="3" t="n"/>
       <c r="K373" s="2" t="n"/>
@@ -6526,8 +6520,8 @@
       <c r="D374" s="3" t="n"/>
       <c r="E374" s="3" t="n"/>
       <c r="F374" s="3" t="n"/>
-      <c r="G374" s="4" t="n"/>
-      <c r="H374" s="4" t="n"/>
+      <c r="G374" s="2" t="n"/>
+      <c r="H374" s="2" t="n"/>
       <c r="I374" s="3" t="n"/>
       <c r="J374" s="3" t="n"/>
       <c r="K374" s="2" t="n"/>
@@ -6542,8 +6536,8 @@
       <c r="D375" s="3" t="n"/>
       <c r="E375" s="3" t="n"/>
       <c r="F375" s="3" t="n"/>
-      <c r="G375" s="4" t="n"/>
-      <c r="H375" s="4" t="n"/>
+      <c r="G375" s="2" t="n"/>
+      <c r="H375" s="2" t="n"/>
       <c r="I375" s="3" t="n"/>
       <c r="J375" s="3" t="n"/>
       <c r="K375" s="2" t="n"/>
@@ -6558,8 +6552,8 @@
       <c r="D376" s="3" t="n"/>
       <c r="E376" s="3" t="n"/>
       <c r="F376" s="3" t="n"/>
-      <c r="G376" s="4" t="n"/>
-      <c r="H376" s="4" t="n"/>
+      <c r="G376" s="2" t="n"/>
+      <c r="H376" s="2" t="n"/>
       <c r="I376" s="3" t="n"/>
       <c r="J376" s="3" t="n"/>
       <c r="K376" s="2" t="n"/>
@@ -6574,8 +6568,8 @@
       <c r="D377" s="3" t="n"/>
       <c r="E377" s="3" t="n"/>
       <c r="F377" s="3" t="n"/>
-      <c r="G377" s="4" t="n"/>
-      <c r="H377" s="4" t="n"/>
+      <c r="G377" s="2" t="n"/>
+      <c r="H377" s="2" t="n"/>
       <c r="I377" s="3" t="n"/>
       <c r="J377" s="3" t="n"/>
       <c r="K377" s="2" t="n"/>
@@ -6590,8 +6584,8 @@
       <c r="D378" s="3" t="n"/>
       <c r="E378" s="3" t="n"/>
       <c r="F378" s="3" t="n"/>
-      <c r="G378" s="4" t="n"/>
-      <c r="H378" s="4" t="n"/>
+      <c r="G378" s="2" t="n"/>
+      <c r="H378" s="2" t="n"/>
       <c r="I378" s="3" t="n"/>
       <c r="J378" s="3" t="n"/>
       <c r="K378" s="2" t="n"/>
@@ -6606,8 +6600,8 @@
       <c r="D379" s="3" t="n"/>
       <c r="E379" s="3" t="n"/>
       <c r="F379" s="3" t="n"/>
-      <c r="G379" s="4" t="n"/>
-      <c r="H379" s="4" t="n"/>
+      <c r="G379" s="2" t="n"/>
+      <c r="H379" s="2" t="n"/>
       <c r="I379" s="3" t="n"/>
       <c r="J379" s="3" t="n"/>
       <c r="K379" s="2" t="n"/>
@@ -6622,8 +6616,8 @@
       <c r="D380" s="3" t="n"/>
       <c r="E380" s="3" t="n"/>
       <c r="F380" s="3" t="n"/>
-      <c r="G380" s="4" t="n"/>
-      <c r="H380" s="4" t="n"/>
+      <c r="G380" s="2" t="n"/>
+      <c r="H380" s="2" t="n"/>
       <c r="I380" s="3" t="n"/>
       <c r="J380" s="3" t="n"/>
       <c r="K380" s="2" t="n"/>
@@ -6638,8 +6632,8 @@
       <c r="D381" s="3" t="n"/>
       <c r="E381" s="3" t="n"/>
       <c r="F381" s="3" t="n"/>
-      <c r="G381" s="4" t="n"/>
-      <c r="H381" s="4" t="n"/>
+      <c r="G381" s="2" t="n"/>
+      <c r="H381" s="2" t="n"/>
       <c r="I381" s="3" t="n"/>
       <c r="J381" s="3" t="n"/>
       <c r="K381" s="2" t="n"/>
@@ -6654,8 +6648,8 @@
       <c r="D382" s="3" t="n"/>
       <c r="E382" s="3" t="n"/>
       <c r="F382" s="3" t="n"/>
-      <c r="G382" s="4" t="n"/>
-      <c r="H382" s="4" t="n"/>
+      <c r="G382" s="2" t="n"/>
+      <c r="H382" s="2" t="n"/>
       <c r="I382" s="3" t="n"/>
       <c r="J382" s="3" t="n"/>
       <c r="K382" s="2" t="n"/>
@@ -6670,8 +6664,8 @@
       <c r="D383" s="3" t="n"/>
       <c r="E383" s="3" t="n"/>
       <c r="F383" s="3" t="n"/>
-      <c r="G383" s="4" t="n"/>
-      <c r="H383" s="4" t="n"/>
+      <c r="G383" s="2" t="n"/>
+      <c r="H383" s="2" t="n"/>
       <c r="I383" s="3" t="n"/>
       <c r="J383" s="3" t="n"/>
       <c r="K383" s="2" t="n"/>
@@ -6686,8 +6680,8 @@
       <c r="D384" s="3" t="n"/>
       <c r="E384" s="3" t="n"/>
       <c r="F384" s="3" t="n"/>
-      <c r="G384" s="4" t="n"/>
-      <c r="H384" s="4" t="n"/>
+      <c r="G384" s="2" t="n"/>
+      <c r="H384" s="2" t="n"/>
       <c r="I384" s="3" t="n"/>
       <c r="J384" s="3" t="n"/>
       <c r="K384" s="2" t="n"/>
@@ -6702,8 +6696,8 @@
       <c r="D385" s="3" t="n"/>
       <c r="E385" s="3" t="n"/>
       <c r="F385" s="3" t="n"/>
-      <c r="G385" s="4" t="n"/>
-      <c r="H385" s="4" t="n"/>
+      <c r="G385" s="2" t="n"/>
+      <c r="H385" s="2" t="n"/>
       <c r="I385" s="3" t="n"/>
       <c r="J385" s="3" t="n"/>
       <c r="K385" s="2" t="n"/>
@@ -6718,8 +6712,8 @@
       <c r="D386" s="3" t="n"/>
       <c r="E386" s="3" t="n"/>
       <c r="F386" s="3" t="n"/>
-      <c r="G386" s="4" t="n"/>
-      <c r="H386" s="4" t="n"/>
+      <c r="G386" s="2" t="n"/>
+      <c r="H386" s="2" t="n"/>
       <c r="I386" s="3" t="n"/>
       <c r="J386" s="3" t="n"/>
       <c r="K386" s="2" t="n"/>
@@ -6734,8 +6728,8 @@
       <c r="D387" s="3" t="n"/>
       <c r="E387" s="3" t="n"/>
       <c r="F387" s="3" t="n"/>
-      <c r="G387" s="4" t="n"/>
-      <c r="H387" s="4" t="n"/>
+      <c r="G387" s="2" t="n"/>
+      <c r="H387" s="2" t="n"/>
       <c r="I387" s="3" t="n"/>
       <c r="J387" s="3" t="n"/>
       <c r="K387" s="2" t="n"/>
@@ -6750,8 +6744,8 @@
       <c r="D388" s="3" t="n"/>
       <c r="E388" s="3" t="n"/>
       <c r="F388" s="3" t="n"/>
-      <c r="G388" s="4" t="n"/>
-      <c r="H388" s="4" t="n"/>
+      <c r="G388" s="2" t="n"/>
+      <c r="H388" s="2" t="n"/>
       <c r="I388" s="3" t="n"/>
       <c r="J388" s="3" t="n"/>
       <c r="K388" s="2" t="n"/>
@@ -6766,8 +6760,8 @@
       <c r="D389" s="3" t="n"/>
       <c r="E389" s="3" t="n"/>
       <c r="F389" s="3" t="n"/>
-      <c r="G389" s="4" t="n"/>
-      <c r="H389" s="4" t="n"/>
+      <c r="G389" s="2" t="n"/>
+      <c r="H389" s="2" t="n"/>
       <c r="I389" s="3" t="n"/>
       <c r="J389" s="3" t="n"/>
       <c r="K389" s="2" t="n"/>
@@ -6782,8 +6776,8 @@
       <c r="D390" s="3" t="n"/>
       <c r="E390" s="3" t="n"/>
       <c r="F390" s="3" t="n"/>
-      <c r="G390" s="4" t="n"/>
-      <c r="H390" s="4" t="n"/>
+      <c r="G390" s="2" t="n"/>
+      <c r="H390" s="2" t="n"/>
       <c r="I390" s="3" t="n"/>
       <c r="J390" s="3" t="n"/>
       <c r="K390" s="2" t="n"/>
@@ -6798,8 +6792,8 @@
       <c r="D391" s="3" t="n"/>
       <c r="E391" s="3" t="n"/>
       <c r="F391" s="3" t="n"/>
-      <c r="G391" s="4" t="n"/>
-      <c r="H391" s="4" t="n"/>
+      <c r="G391" s="2" t="n"/>
+      <c r="H391" s="2" t="n"/>
       <c r="I391" s="3" t="n"/>
       <c r="J391" s="3" t="n"/>
       <c r="K391" s="2" t="n"/>
@@ -6814,8 +6808,8 @@
       <c r="D392" s="3" t="n"/>
       <c r="E392" s="3" t="n"/>
       <c r="F392" s="3" t="n"/>
-      <c r="G392" s="4" t="n"/>
-      <c r="H392" s="4" t="n"/>
+      <c r="G392" s="2" t="n"/>
+      <c r="H392" s="2" t="n"/>
       <c r="I392" s="3" t="n"/>
       <c r="J392" s="3" t="n"/>
       <c r="K392" s="2" t="n"/>
@@ -6830,8 +6824,8 @@
       <c r="D393" s="3" t="n"/>
       <c r="E393" s="3" t="n"/>
       <c r="F393" s="3" t="n"/>
-      <c r="G393" s="4" t="n"/>
-      <c r="H393" s="4" t="n"/>
+      <c r="G393" s="2" t="n"/>
+      <c r="H393" s="2" t="n"/>
       <c r="I393" s="3" t="n"/>
       <c r="J393" s="3" t="n"/>
       <c r="K393" s="2" t="n"/>
@@ -6846,8 +6840,8 @@
       <c r="D394" s="3" t="n"/>
       <c r="E394" s="3" t="n"/>
       <c r="F394" s="3" t="n"/>
-      <c r="G394" s="4" t="n"/>
-      <c r="H394" s="4" t="n"/>
+      <c r="G394" s="2" t="n"/>
+      <c r="H394" s="2" t="n"/>
       <c r="I394" s="3" t="n"/>
       <c r="J394" s="3" t="n"/>
       <c r="K394" s="2" t="n"/>
@@ -6862,8 +6856,8 @@
       <c r="D395" s="3" t="n"/>
       <c r="E395" s="3" t="n"/>
       <c r="F395" s="3" t="n"/>
-      <c r="G395" s="4" t="n"/>
-      <c r="H395" s="4" t="n"/>
+      <c r="G395" s="2" t="n"/>
+      <c r="H395" s="2" t="n"/>
       <c r="I395" s="3" t="n"/>
       <c r="J395" s="3" t="n"/>
       <c r="K395" s="2" t="n"/>
@@ -6878,8 +6872,8 @@
       <c r="D396" s="3" t="n"/>
       <c r="E396" s="3" t="n"/>
       <c r="F396" s="3" t="n"/>
-      <c r="G396" s="4" t="n"/>
-      <c r="H396" s="4" t="n"/>
+      <c r="G396" s="2" t="n"/>
+      <c r="H396" s="2" t="n"/>
       <c r="I396" s="3" t="n"/>
       <c r="J396" s="3" t="n"/>
       <c r="K396" s="2" t="n"/>
@@ -6894,8 +6888,8 @@
       <c r="D397" s="3" t="n"/>
       <c r="E397" s="3" t="n"/>
       <c r="F397" s="3" t="n"/>
-      <c r="G397" s="4" t="n"/>
-      <c r="H397" s="4" t="n"/>
+      <c r="G397" s="2" t="n"/>
+      <c r="H397" s="2" t="n"/>
       <c r="I397" s="3" t="n"/>
       <c r="J397" s="3" t="n"/>
       <c r="K397" s="2" t="n"/>
@@ -6910,8 +6904,8 @@
       <c r="D398" s="3" t="n"/>
       <c r="E398" s="3" t="n"/>
       <c r="F398" s="3" t="n"/>
-      <c r="G398" s="4" t="n"/>
-      <c r="H398" s="4" t="n"/>
+      <c r="G398" s="2" t="n"/>
+      <c r="H398" s="2" t="n"/>
       <c r="I398" s="3" t="n"/>
       <c r="J398" s="3" t="n"/>
       <c r="K398" s="2" t="n"/>
@@ -6926,8 +6920,8 @@
       <c r="D399" s="3" t="n"/>
       <c r="E399" s="3" t="n"/>
       <c r="F399" s="3" t="n"/>
-      <c r="G399" s="4" t="n"/>
-      <c r="H399" s="4" t="n"/>
+      <c r="G399" s="2" t="n"/>
+      <c r="H399" s="2" t="n"/>
       <c r="I399" s="3" t="n"/>
       <c r="J399" s="3" t="n"/>
       <c r="K399" s="2" t="n"/>
@@ -6942,8 +6936,8 @@
       <c r="D400" s="3" t="n"/>
       <c r="E400" s="3" t="n"/>
       <c r="F400" s="3" t="n"/>
-      <c r="G400" s="4" t="n"/>
-      <c r="H400" s="4" t="n"/>
+      <c r="G400" s="2" t="n"/>
+      <c r="H400" s="2" t="n"/>
       <c r="I400" s="3" t="n"/>
       <c r="J400" s="3" t="n"/>
       <c r="K400" s="2" t="n"/>
@@ -6958,8 +6952,8 @@
       <c r="D401" s="3" t="n"/>
       <c r="E401" s="3" t="n"/>
       <c r="F401" s="3" t="n"/>
-      <c r="G401" s="4" t="n"/>
-      <c r="H401" s="4" t="n"/>
+      <c r="G401" s="2" t="n"/>
+      <c r="H401" s="2" t="n"/>
       <c r="I401" s="3" t="n"/>
       <c r="J401" s="3" t="n"/>
       <c r="K401" s="2" t="n"/>
@@ -6974,8 +6968,8 @@
       <c r="D402" s="3" t="n"/>
       <c r="E402" s="3" t="n"/>
       <c r="F402" s="3" t="n"/>
-      <c r="G402" s="4" t="n"/>
-      <c r="H402" s="4" t="n"/>
+      <c r="G402" s="2" t="n"/>
+      <c r="H402" s="2" t="n"/>
       <c r="I402" s="3" t="n"/>
       <c r="J402" s="3" t="n"/>
       <c r="K402" s="2" t="n"/>
@@ -6990,8 +6984,8 @@
       <c r="D403" s="3" t="n"/>
       <c r="E403" s="3" t="n"/>
       <c r="F403" s="3" t="n"/>
-      <c r="G403" s="4" t="n"/>
-      <c r="H403" s="4" t="n"/>
+      <c r="G403" s="2" t="n"/>
+      <c r="H403" s="2" t="n"/>
       <c r="I403" s="3" t="n"/>
       <c r="J403" s="3" t="n"/>
       <c r="K403" s="2" t="n"/>
@@ -7006,8 +7000,8 @@
       <c r="D404" s="3" t="n"/>
       <c r="E404" s="3" t="n"/>
       <c r="F404" s="3" t="n"/>
-      <c r="G404" s="4" t="n"/>
-      <c r="H404" s="4" t="n"/>
+      <c r="G404" s="2" t="n"/>
+      <c r="H404" s="2" t="n"/>
       <c r="I404" s="3" t="n"/>
       <c r="J404" s="3" t="n"/>
       <c r="K404" s="2" t="n"/>
@@ -7022,8 +7016,8 @@
       <c r="D405" s="3" t="n"/>
       <c r="E405" s="3" t="n"/>
       <c r="F405" s="3" t="n"/>
-      <c r="G405" s="4" t="n"/>
-      <c r="H405" s="4" t="n"/>
+      <c r="G405" s="2" t="n"/>
+      <c r="H405" s="2" t="n"/>
       <c r="I405" s="3" t="n"/>
       <c r="J405" s="3" t="n"/>
       <c r="K405" s="2" t="n"/>
@@ -7038,8 +7032,8 @@
       <c r="D406" s="3" t="n"/>
       <c r="E406" s="3" t="n"/>
       <c r="F406" s="3" t="n"/>
-      <c r="G406" s="4" t="n"/>
-      <c r="H406" s="4" t="n"/>
+      <c r="G406" s="2" t="n"/>
+      <c r="H406" s="2" t="n"/>
       <c r="I406" s="3" t="n"/>
       <c r="J406" s="3" t="n"/>
       <c r="K406" s="2" t="n"/>
@@ -7054,8 +7048,8 @@
       <c r="D407" s="3" t="n"/>
       <c r="E407" s="3" t="n"/>
       <c r="F407" s="3" t="n"/>
-      <c r="G407" s="4" t="n"/>
-      <c r="H407" s="4" t="n"/>
+      <c r="G407" s="2" t="n"/>
+      <c r="H407" s="2" t="n"/>
       <c r="I407" s="3" t="n"/>
       <c r="J407" s="3" t="n"/>
       <c r="K407" s="2" t="n"/>
@@ -7070,8 +7064,8 @@
       <c r="D408" s="3" t="n"/>
       <c r="E408" s="3" t="n"/>
       <c r="F408" s="3" t="n"/>
-      <c r="G408" s="4" t="n"/>
-      <c r="H408" s="4" t="n"/>
+      <c r="G408" s="2" t="n"/>
+      <c r="H408" s="2" t="n"/>
       <c r="I408" s="3" t="n"/>
       <c r="J408" s="3" t="n"/>
       <c r="K408" s="2" t="n"/>
@@ -7086,8 +7080,8 @@
       <c r="D409" s="3" t="n"/>
       <c r="E409" s="3" t="n"/>
       <c r="F409" s="3" t="n"/>
-      <c r="G409" s="4" t="n"/>
-      <c r="H409" s="4" t="n"/>
+      <c r="G409" s="2" t="n"/>
+      <c r="H409" s="2" t="n"/>
       <c r="I409" s="3" t="n"/>
       <c r="J409" s="3" t="n"/>
       <c r="K409" s="2" t="n"/>
@@ -7102,8 +7096,8 @@
       <c r="D410" s="3" t="n"/>
       <c r="E410" s="3" t="n"/>
       <c r="F410" s="3" t="n"/>
-      <c r="G410" s="4" t="n"/>
-      <c r="H410" s="4" t="n"/>
+      <c r="G410" s="2" t="n"/>
+      <c r="H410" s="2" t="n"/>
       <c r="I410" s="3" t="n"/>
       <c r="J410" s="3" t="n"/>
       <c r="K410" s="2" t="n"/>
@@ -7118,8 +7112,8 @@
       <c r="D411" s="3" t="n"/>
       <c r="E411" s="3" t="n"/>
       <c r="F411" s="3" t="n"/>
-      <c r="G411" s="4" t="n"/>
-      <c r="H411" s="4" t="n"/>
+      <c r="G411" s="2" t="n"/>
+      <c r="H411" s="2" t="n"/>
       <c r="I411" s="3" t="n"/>
       <c r="J411" s="3" t="n"/>
       <c r="K411" s="2" t="n"/>
@@ -7134,8 +7128,8 @@
       <c r="D412" s="3" t="n"/>
       <c r="E412" s="3" t="n"/>
       <c r="F412" s="3" t="n"/>
-      <c r="G412" s="4" t="n"/>
-      <c r="H412" s="4" t="n"/>
+      <c r="G412" s="2" t="n"/>
+      <c r="H412" s="2" t="n"/>
       <c r="I412" s="3" t="n"/>
       <c r="J412" s="3" t="n"/>
       <c r="K412" s="2" t="n"/>
@@ -7150,8 +7144,8 @@
       <c r="D413" s="3" t="n"/>
       <c r="E413" s="3" t="n"/>
       <c r="F413" s="3" t="n"/>
-      <c r="G413" s="4" t="n"/>
-      <c r="H413" s="4" t="n"/>
+      <c r="G413" s="2" t="n"/>
+      <c r="H413" s="2" t="n"/>
       <c r="I413" s="3" t="n"/>
       <c r="J413" s="3" t="n"/>
       <c r="K413" s="2" t="n"/>
@@ -7166,8 +7160,8 @@
       <c r="D414" s="3" t="n"/>
       <c r="E414" s="3" t="n"/>
       <c r="F414" s="3" t="n"/>
-      <c r="G414" s="4" t="n"/>
-      <c r="H414" s="4" t="n"/>
+      <c r="G414" s="2" t="n"/>
+      <c r="H414" s="2" t="n"/>
       <c r="I414" s="3" t="n"/>
       <c r="J414" s="3" t="n"/>
       <c r="K414" s="2" t="n"/>
@@ -7182,8 +7176,8 @@
       <c r="D415" s="3" t="n"/>
       <c r="E415" s="3" t="n"/>
       <c r="F415" s="3" t="n"/>
-      <c r="G415" s="4" t="n"/>
-      <c r="H415" s="4" t="n"/>
+      <c r="G415" s="2" t="n"/>
+      <c r="H415" s="2" t="n"/>
       <c r="I415" s="3" t="n"/>
       <c r="J415" s="3" t="n"/>
       <c r="K415" s="2" t="n"/>
@@ -7198,8 +7192,8 @@
       <c r="D416" s="3" t="n"/>
       <c r="E416" s="3" t="n"/>
       <c r="F416" s="3" t="n"/>
-      <c r="G416" s="4" t="n"/>
-      <c r="H416" s="4" t="n"/>
+      <c r="G416" s="2" t="n"/>
+      <c r="H416" s="2" t="n"/>
       <c r="I416" s="3" t="n"/>
       <c r="J416" s="3" t="n"/>
       <c r="K416" s="2" t="n"/>
@@ -7214,8 +7208,8 @@
       <c r="D417" s="3" t="n"/>
       <c r="E417" s="3" t="n"/>
       <c r="F417" s="3" t="n"/>
-      <c r="G417" s="4" t="n"/>
-      <c r="H417" s="4" t="n"/>
+      <c r="G417" s="2" t="n"/>
+      <c r="H417" s="2" t="n"/>
       <c r="I417" s="3" t="n"/>
       <c r="J417" s="3" t="n"/>
       <c r="K417" s="2" t="n"/>
@@ -7230,8 +7224,8 @@
       <c r="D418" s="3" t="n"/>
       <c r="E418" s="3" t="n"/>
       <c r="F418" s="3" t="n"/>
-      <c r="G418" s="4" t="n"/>
-      <c r="H418" s="4" t="n"/>
+      <c r="G418" s="2" t="n"/>
+      <c r="H418" s="2" t="n"/>
       <c r="I418" s="3" t="n"/>
       <c r="J418" s="3" t="n"/>
       <c r="K418" s="2" t="n"/>
@@ -7246,8 +7240,8 @@
       <c r="D419" s="3" t="n"/>
       <c r="E419" s="3" t="n"/>
       <c r="F419" s="3" t="n"/>
-      <c r="G419" s="4" t="n"/>
-      <c r="H419" s="4" t="n"/>
+      <c r="G419" s="2" t="n"/>
+      <c r="H419" s="2" t="n"/>
       <c r="I419" s="3" t="n"/>
       <c r="J419" s="3" t="n"/>
       <c r="K419" s="2" t="n"/>
@@ -7262,8 +7256,8 @@
       <c r="D420" s="3" t="n"/>
       <c r="E420" s="3" t="n"/>
       <c r="F420" s="3" t="n"/>
-      <c r="G420" s="4" t="n"/>
-      <c r="H420" s="4" t="n"/>
+      <c r="G420" s="2" t="n"/>
+      <c r="H420" s="2" t="n"/>
       <c r="I420" s="3" t="n"/>
       <c r="J420" s="3" t="n"/>
       <c r="K420" s="2" t="n"/>
@@ -7278,8 +7272,8 @@
       <c r="D421" s="3" t="n"/>
       <c r="E421" s="3" t="n"/>
       <c r="F421" s="3" t="n"/>
-      <c r="G421" s="4" t="n"/>
-      <c r="H421" s="4" t="n"/>
+      <c r="G421" s="2" t="n"/>
+      <c r="H421" s="2" t="n"/>
       <c r="I421" s="3" t="n"/>
       <c r="J421" s="3" t="n"/>
       <c r="K421" s="2" t="n"/>
@@ -7294,8 +7288,8 @@
       <c r="D422" s="3" t="n"/>
       <c r="E422" s="3" t="n"/>
       <c r="F422" s="3" t="n"/>
-      <c r="G422" s="4" t="n"/>
-      <c r="H422" s="4" t="n"/>
+      <c r="G422" s="2" t="n"/>
+      <c r="H422" s="2" t="n"/>
       <c r="I422" s="3" t="n"/>
       <c r="J422" s="3" t="n"/>
       <c r="K422" s="2" t="n"/>
@@ -7310,8 +7304,8 @@
       <c r="D423" s="3" t="n"/>
       <c r="E423" s="3" t="n"/>
       <c r="F423" s="3" t="n"/>
-      <c r="G423" s="4" t="n"/>
-      <c r="H423" s="4" t="n"/>
+      <c r="G423" s="2" t="n"/>
+      <c r="H423" s="2" t="n"/>
       <c r="I423" s="3" t="n"/>
       <c r="J423" s="3" t="n"/>
       <c r="K423" s="2" t="n"/>
@@ -7326,8 +7320,8 @@
       <c r="D424" s="3" t="n"/>
       <c r="E424" s="3" t="n"/>
       <c r="F424" s="3" t="n"/>
-      <c r="G424" s="4" t="n"/>
-      <c r="H424" s="4" t="n"/>
+      <c r="G424" s="2" t="n"/>
+      <c r="H424" s="2" t="n"/>
       <c r="I424" s="3" t="n"/>
       <c r="J424" s="3" t="n"/>
       <c r="K424" s="2" t="n"/>
@@ -7342,8 +7336,8 @@
       <c r="D425" s="3" t="n"/>
       <c r="E425" s="3" t="n"/>
       <c r="F425" s="3" t="n"/>
-      <c r="G425" s="4" t="n"/>
-      <c r="H425" s="4" t="n"/>
+      <c r="G425" s="2" t="n"/>
+      <c r="H425" s="2" t="n"/>
       <c r="I425" s="3" t="n"/>
       <c r="J425" s="3" t="n"/>
       <c r="K425" s="2" t="n"/>
@@ -7358,8 +7352,8 @@
       <c r="D426" s="3" t="n"/>
       <c r="E426" s="3" t="n"/>
       <c r="F426" s="3" t="n"/>
-      <c r="G426" s="4" t="n"/>
-      <c r="H426" s="4" t="n"/>
+      <c r="G426" s="2" t="n"/>
+      <c r="H426" s="2" t="n"/>
       <c r="I426" s="3" t="n"/>
       <c r="J426" s="3" t="n"/>
       <c r="K426" s="2" t="n"/>
@@ -7374,8 +7368,8 @@
       <c r="D427" s="3" t="n"/>
       <c r="E427" s="3" t="n"/>
       <c r="F427" s="3" t="n"/>
-      <c r="G427" s="4" t="n"/>
-      <c r="H427" s="4" t="n"/>
+      <c r="G427" s="2" t="n"/>
+      <c r="H427" s="2" t="n"/>
       <c r="I427" s="3" t="n"/>
       <c r="J427" s="3" t="n"/>
       <c r="K427" s="2" t="n"/>
@@ -7390,8 +7384,8 @@
       <c r="D428" s="3" t="n"/>
       <c r="E428" s="3" t="n"/>
       <c r="F428" s="3" t="n"/>
-      <c r="G428" s="4" t="n"/>
-      <c r="H428" s="4" t="n"/>
+      <c r="G428" s="2" t="n"/>
+      <c r="H428" s="2" t="n"/>
       <c r="I428" s="3" t="n"/>
       <c r="J428" s="3" t="n"/>
       <c r="K428" s="2" t="n"/>
@@ -7406,8 +7400,8 @@
       <c r="D429" s="3" t="n"/>
       <c r="E429" s="3" t="n"/>
       <c r="F429" s="3" t="n"/>
-      <c r="G429" s="4" t="n"/>
-      <c r="H429" s="4" t="n"/>
+      <c r="G429" s="2" t="n"/>
+      <c r="H429" s="2" t="n"/>
       <c r="I429" s="3" t="n"/>
       <c r="J429" s="3" t="n"/>
       <c r="K429" s="2" t="n"/>
@@ -7422,8 +7416,8 @@
       <c r="D430" s="3" t="n"/>
       <c r="E430" s="3" t="n"/>
       <c r="F430" s="3" t="n"/>
-      <c r="G430" s="4" t="n"/>
-      <c r="H430" s="4" t="n"/>
+      <c r="G430" s="2" t="n"/>
+      <c r="H430" s="2" t="n"/>
       <c r="I430" s="3" t="n"/>
       <c r="J430" s="3" t="n"/>
       <c r="K430" s="2" t="n"/>
@@ -7438,8 +7432,8 @@
       <c r="D431" s="3" t="n"/>
       <c r="E431" s="3" t="n"/>
       <c r="F431" s="3" t="n"/>
-      <c r="G431" s="4" t="n"/>
-      <c r="H431" s="4" t="n"/>
+      <c r="G431" s="2" t="n"/>
+      <c r="H431" s="2" t="n"/>
       <c r="I431" s="3" t="n"/>
       <c r="J431" s="3" t="n"/>
       <c r="K431" s="2" t="n"/>
@@ -7454,8 +7448,8 @@
       <c r="D432" s="3" t="n"/>
       <c r="E432" s="3" t="n"/>
       <c r="F432" s="3" t="n"/>
-      <c r="G432" s="4" t="n"/>
-      <c r="H432" s="4" t="n"/>
+      <c r="G432" s="2" t="n"/>
+      <c r="H432" s="2" t="n"/>
       <c r="I432" s="3" t="n"/>
       <c r="J432" s="3" t="n"/>
       <c r="K432" s="2" t="n"/>
@@ -7470,8 +7464,8 @@
       <c r="D433" s="3" t="n"/>
       <c r="E433" s="3" t="n"/>
       <c r="F433" s="3" t="n"/>
-      <c r="G433" s="4" t="n"/>
-      <c r="H433" s="4" t="n"/>
+      <c r="G433" s="2" t="n"/>
+      <c r="H433" s="2" t="n"/>
       <c r="I433" s="3" t="n"/>
       <c r="J433" s="3" t="n"/>
       <c r="K433" s="2" t="n"/>
@@ -7486,8 +7480,8 @@
       <c r="D434" s="3" t="n"/>
       <c r="E434" s="3" t="n"/>
       <c r="F434" s="3" t="n"/>
-      <c r="G434" s="4" t="n"/>
-      <c r="H434" s="4" t="n"/>
+      <c r="G434" s="2" t="n"/>
+      <c r="H434" s="2" t="n"/>
       <c r="I434" s="3" t="n"/>
       <c r="J434" s="3" t="n"/>
       <c r="K434" s="2" t="n"/>
@@ -7502,8 +7496,8 @@
       <c r="D435" s="3" t="n"/>
       <c r="E435" s="3" t="n"/>
       <c r="F435" s="3" t="n"/>
-      <c r="G435" s="4" t="n"/>
-      <c r="H435" s="4" t="n"/>
+      <c r="G435" s="2" t="n"/>
+      <c r="H435" s="2" t="n"/>
       <c r="I435" s="3" t="n"/>
       <c r="J435" s="3" t="n"/>
       <c r="K435" s="2" t="n"/>
@@ -7518,8 +7512,8 @@
       <c r="D436" s="3" t="n"/>
       <c r="E436" s="3" t="n"/>
       <c r="F436" s="3" t="n"/>
-      <c r="G436" s="4" t="n"/>
-      <c r="H436" s="4" t="n"/>
+      <c r="G436" s="2" t="n"/>
+      <c r="H436" s="2" t="n"/>
       <c r="I436" s="3" t="n"/>
       <c r="J436" s="3" t="n"/>
       <c r="K436" s="2" t="n"/>
@@ -7534,8 +7528,8 @@
       <c r="D437" s="3" t="n"/>
       <c r="E437" s="3" t="n"/>
       <c r="F437" s="3" t="n"/>
-      <c r="G437" s="4" t="n"/>
-      <c r="H437" s="4" t="n"/>
+      <c r="G437" s="2" t="n"/>
+      <c r="H437" s="2" t="n"/>
       <c r="I437" s="3" t="n"/>
       <c r="J437" s="3" t="n"/>
       <c r="K437" s="2" t="n"/>
@@ -7550,8 +7544,8 @@
       <c r="D438" s="3" t="n"/>
       <c r="E438" s="3" t="n"/>
       <c r="F438" s="3" t="n"/>
-      <c r="G438" s="4" t="n"/>
-      <c r="H438" s="4" t="n"/>
+      <c r="G438" s="2" t="n"/>
+      <c r="H438" s="2" t="n"/>
       <c r="I438" s="3" t="n"/>
       <c r="J438" s="3" t="n"/>
       <c r="K438" s="2" t="n"/>
@@ -7566,8 +7560,8 @@
       <c r="D439" s="3" t="n"/>
       <c r="E439" s="3" t="n"/>
       <c r="F439" s="3" t="n"/>
-      <c r="G439" s="4" t="n"/>
-      <c r="H439" s="4" t="n"/>
+      <c r="G439" s="2" t="n"/>
+      <c r="H439" s="2" t="n"/>
       <c r="I439" s="3" t="n"/>
       <c r="J439" s="3" t="n"/>
       <c r="K439" s="2" t="n"/>
@@ -7582,8 +7576,8 @@
       <c r="D440" s="3" t="n"/>
       <c r="E440" s="3" t="n"/>
       <c r="F440" s="3" t="n"/>
-      <c r="G440" s="4" t="n"/>
-      <c r="H440" s="4" t="n"/>
+      <c r="G440" s="2" t="n"/>
+      <c r="H440" s="2" t="n"/>
       <c r="I440" s="3" t="n"/>
       <c r="J440" s="3" t="n"/>
       <c r="K440" s="2" t="n"/>
@@ -7598,8 +7592,8 @@
       <c r="D441" s="3" t="n"/>
       <c r="E441" s="3" t="n"/>
       <c r="F441" s="3" t="n"/>
-      <c r="G441" s="4" t="n"/>
-      <c r="H441" s="4" t="n"/>
+      <c r="G441" s="2" t="n"/>
+      <c r="H441" s="2" t="n"/>
       <c r="I441" s="3" t="n"/>
       <c r="J441" s="3" t="n"/>
       <c r="K441" s="2" t="n"/>
@@ -7614,8 +7608,8 @@
       <c r="D442" s="3" t="n"/>
       <c r="E442" s="3" t="n"/>
       <c r="F442" s="3" t="n"/>
-      <c r="G442" s="4" t="n"/>
-      <c r="H442" s="4" t="n"/>
+      <c r="G442" s="2" t="n"/>
+      <c r="H442" s="2" t="n"/>
       <c r="I442" s="3" t="n"/>
       <c r="J442" s="3" t="n"/>
       <c r="K442" s="2" t="n"/>
@@ -7630,8 +7624,8 @@
       <c r="D443" s="3" t="n"/>
       <c r="E443" s="3" t="n"/>
       <c r="F443" s="3" t="n"/>
-      <c r="G443" s="4" t="n"/>
-      <c r="H443" s="4" t="n"/>
+      <c r="G443" s="2" t="n"/>
+      <c r="H443" s="2" t="n"/>
       <c r="I443" s="3" t="n"/>
       <c r="J443" s="3" t="n"/>
       <c r="K443" s="2" t="n"/>
@@ -7646,8 +7640,8 @@
       <c r="D444" s="3" t="n"/>
       <c r="E444" s="3" t="n"/>
       <c r="F444" s="3" t="n"/>
-      <c r="G444" s="4" t="n"/>
-      <c r="H444" s="4" t="n"/>
+      <c r="G444" s="2" t="n"/>
+      <c r="H444" s="2" t="n"/>
       <c r="I444" s="3" t="n"/>
       <c r="J444" s="3" t="n"/>
       <c r="K444" s="2" t="n"/>
@@ -7662,8 +7656,8 @@
       <c r="D445" s="3" t="n"/>
       <c r="E445" s="3" t="n"/>
       <c r="F445" s="3" t="n"/>
-      <c r="G445" s="4" t="n"/>
-      <c r="H445" s="4" t="n"/>
+      <c r="G445" s="2" t="n"/>
+      <c r="H445" s="2" t="n"/>
       <c r="I445" s="3" t="n"/>
       <c r="J445" s="3" t="n"/>
       <c r="K445" s="2" t="n"/>
@@ -7678,8 +7672,8 @@
       <c r="D446" s="3" t="n"/>
       <c r="E446" s="3" t="n"/>
       <c r="F446" s="3" t="n"/>
-      <c r="G446" s="4" t="n"/>
-      <c r="H446" s="4" t="n"/>
+      <c r="G446" s="2" t="n"/>
+      <c r="H446" s="2" t="n"/>
       <c r="I446" s="3" t="n"/>
       <c r="J446" s="3" t="n"/>
       <c r="K446" s="2" t="n"/>
@@ -7694,8 +7688,8 @@
       <c r="D447" s="3" t="n"/>
       <c r="E447" s="3" t="n"/>
       <c r="F447" s="3" t="n"/>
-      <c r="G447" s="4" t="n"/>
-      <c r="H447" s="4" t="n"/>
+      <c r="G447" s="2" t="n"/>
+      <c r="H447" s="2" t="n"/>
       <c r="I447" s="3" t="n"/>
       <c r="J447" s="3" t="n"/>
       <c r="K447" s="2" t="n"/>
@@ -7710,8 +7704,8 @@
       <c r="D448" s="3" t="n"/>
       <c r="E448" s="3" t="n"/>
       <c r="F448" s="3" t="n"/>
-      <c r="G448" s="4" t="n"/>
-      <c r="H448" s="4" t="n"/>
+      <c r="G448" s="2" t="n"/>
+      <c r="H448" s="2" t="n"/>
       <c r="I448" s="3" t="n"/>
       <c r="J448" s="3" t="n"/>
       <c r="K448" s="2" t="n"/>
@@ -7726,8 +7720,8 @@
       <c r="D449" s="3" t="n"/>
       <c r="E449" s="3" t="n"/>
       <c r="F449" s="3" t="n"/>
-      <c r="G449" s="4" t="n"/>
-      <c r="H449" s="4" t="n"/>
+      <c r="G449" s="2" t="n"/>
+      <c r="H449" s="2" t="n"/>
       <c r="I449" s="3" t="n"/>
       <c r="J449" s="3" t="n"/>
       <c r="K449" s="2" t="n"/>
@@ -7742,8 +7736,8 @@
       <c r="D450" s="3" t="n"/>
       <c r="E450" s="3" t="n"/>
       <c r="F450" s="3" t="n"/>
-      <c r="G450" s="4" t="n"/>
-      <c r="H450" s="4" t="n"/>
+      <c r="G450" s="2" t="n"/>
+      <c r="H450" s="2" t="n"/>
       <c r="I450" s="3" t="n"/>
       <c r="J450" s="3" t="n"/>
       <c r="K450" s="2" t="n"/>
@@ -7758,8 +7752,8 @@
       <c r="D451" s="3" t="n"/>
       <c r="E451" s="3" t="n"/>
       <c r="F451" s="3" t="n"/>
-      <c r="G451" s="4" t="n"/>
-      <c r="H451" s="4" t="n"/>
+      <c r="G451" s="2" t="n"/>
+      <c r="H451" s="2" t="n"/>
       <c r="I451" s="3" t="n"/>
       <c r="J451" s="3" t="n"/>
       <c r="K451" s="2" t="n"/>
@@ -7774,8 +7768,8 @@
       <c r="D452" s="3" t="n"/>
       <c r="E452" s="3" t="n"/>
       <c r="F452" s="3" t="n"/>
-      <c r="G452" s="4" t="n"/>
-      <c r="H452" s="4" t="n"/>
+      <c r="G452" s="2" t="n"/>
+      <c r="H452" s="2" t="n"/>
       <c r="I452" s="3" t="n"/>
       <c r="J452" s="3" t="n"/>
       <c r="K452" s="2" t="n"/>
@@ -7790,8 +7784,8 @@
       <c r="D453" s="3" t="n"/>
       <c r="E453" s="3" t="n"/>
       <c r="F453" s="3" t="n"/>
-      <c r="G453" s="4" t="n"/>
-      <c r="H453" s="4" t="n"/>
+      <c r="G453" s="2" t="n"/>
+      <c r="H453" s="2" t="n"/>
       <c r="I453" s="3" t="n"/>
       <c r="J453" s="3" t="n"/>
       <c r="K453" s="2" t="n"/>
@@ -7806,8 +7800,8 @@
       <c r="D454" s="3" t="n"/>
       <c r="E454" s="3" t="n"/>
       <c r="F454" s="3" t="n"/>
-      <c r="G454" s="4" t="n"/>
-      <c r="H454" s="4" t="n"/>
+      <c r="G454" s="2" t="n"/>
+      <c r="H454" s="2" t="n"/>
       <c r="I454" s="3" t="n"/>
       <c r="J454" s="3" t="n"/>
       <c r="K454" s="2" t="n"/>
@@ -7822,8 +7816,8 @@
       <c r="D455" s="3" t="n"/>
       <c r="E455" s="3" t="n"/>
       <c r="F455" s="3" t="n"/>
-      <c r="G455" s="4" t="n"/>
-      <c r="H455" s="4" t="n"/>
+      <c r="G455" s="2" t="n"/>
+      <c r="H455" s="2" t="n"/>
       <c r="I455" s="3" t="n"/>
       <c r="J455" s="3" t="n"/>
       <c r="K455" s="2" t="n"/>
@@ -7838,8 +7832,8 @@
       <c r="D456" s="3" t="n"/>
       <c r="E456" s="3" t="n"/>
       <c r="F456" s="3" t="n"/>
-      <c r="G456" s="4" t="n"/>
-      <c r="H456" s="4" t="n"/>
+      <c r="G456" s="2" t="n"/>
+      <c r="H456" s="2" t="n"/>
       <c r="I456" s="3" t="n"/>
       <c r="J456" s="3" t="n"/>
       <c r="K456" s="2" t="n"/>
@@ -7854,8 +7848,8 @@
       <c r="D457" s="3" t="n"/>
       <c r="E457" s="3" t="n"/>
       <c r="F457" s="3" t="n"/>
-      <c r="G457" s="4" t="n"/>
-      <c r="H457" s="4" t="n"/>
+      <c r="G457" s="2" t="n"/>
+      <c r="H457" s="2" t="n"/>
       <c r="I457" s="3" t="n"/>
       <c r="J457" s="3" t="n"/>
       <c r="K457" s="2" t="n"/>
@@ -7870,8 +7864,8 @@
       <c r="D458" s="3" t="n"/>
       <c r="E458" s="3" t="n"/>
       <c r="F458" s="3" t="n"/>
-      <c r="G458" s="4" t="n"/>
-      <c r="H458" s="4" t="n"/>
+      <c r="G458" s="2" t="n"/>
+      <c r="H458" s="2" t="n"/>
       <c r="I458" s="3" t="n"/>
       <c r="J458" s="3" t="n"/>
       <c r="K458" s="2" t="n"/>
@@ -7886,8 +7880,8 @@
       <c r="D459" s="3" t="n"/>
       <c r="E459" s="3" t="n"/>
       <c r="F459" s="3" t="n"/>
-      <c r="G459" s="4" t="n"/>
-      <c r="H459" s="4" t="n"/>
+      <c r="G459" s="2" t="n"/>
+      <c r="H459" s="2" t="n"/>
       <c r="I459" s="3" t="n"/>
       <c r="J459" s="3" t="n"/>
       <c r="K459" s="2" t="n"/>
@@ -7902,8 +7896,8 @@
       <c r="D460" s="3" t="n"/>
       <c r="E460" s="3" t="n"/>
       <c r="F460" s="3" t="n"/>
-      <c r="G460" s="4" t="n"/>
-      <c r="H460" s="4" t="n"/>
+      <c r="G460" s="2" t="n"/>
+      <c r="H460" s="2" t="n"/>
       <c r="I460" s="3" t="n"/>
       <c r="J460" s="3" t="n"/>
       <c r="K460" s="2" t="n"/>
@@ -7918,8 +7912,8 @@
       <c r="D461" s="3" t="n"/>
       <c r="E461" s="3" t="n"/>
       <c r="F461" s="3" t="n"/>
-      <c r="G461" s="4" t="n"/>
-      <c r="H461" s="4" t="n"/>
+      <c r="G461" s="2" t="n"/>
+      <c r="H461" s="2" t="n"/>
       <c r="I461" s="3" t="n"/>
       <c r="J461" s="3" t="n"/>
       <c r="K461" s="2" t="n"/>
@@ -7934,8 +7928,8 @@
       <c r="D462" s="3" t="n"/>
       <c r="E462" s="3" t="n"/>
       <c r="F462" s="3" t="n"/>
-      <c r="G462" s="4" t="n"/>
-      <c r="H462" s="4" t="n"/>
+      <c r="G462" s="2" t="n"/>
+      <c r="H462" s="2" t="n"/>
       <c r="I462" s="3" t="n"/>
       <c r="J462" s="3" t="n"/>
       <c r="K462" s="2" t="n"/>
@@ -7950,8 +7944,8 @@
       <c r="D463" s="3" t="n"/>
       <c r="E463" s="3" t="n"/>
       <c r="F463" s="3" t="n"/>
-      <c r="G463" s="4" t="n"/>
-      <c r="H463" s="4" t="n"/>
+      <c r="G463" s="2" t="n"/>
+      <c r="H463" s="2" t="n"/>
       <c r="I463" s="3" t="n"/>
       <c r="J463" s="3" t="n"/>
       <c r="K463" s="2" t="n"/>
@@ -7966,8 +7960,8 @@
       <c r="D464" s="3" t="n"/>
       <c r="E464" s="3" t="n"/>
       <c r="F464" s="3" t="n"/>
-      <c r="G464" s="4" t="n"/>
-      <c r="H464" s="4" t="n"/>
+      <c r="G464" s="2" t="n"/>
+      <c r="H464" s="2" t="n"/>
       <c r="I464" s="3" t="n"/>
       <c r="J464" s="3" t="n"/>
       <c r="K464" s="2" t="n"/>
@@ -7982,8 +7976,8 @@
       <c r="D465" s="3" t="n"/>
       <c r="E465" s="3" t="n"/>
       <c r="F465" s="3" t="n"/>
-      <c r="G465" s="4" t="n"/>
-      <c r="H465" s="4" t="n"/>
+      <c r="G465" s="2" t="n"/>
+      <c r="H465" s="2" t="n"/>
       <c r="I465" s="3" t="n"/>
       <c r="J465" s="3" t="n"/>
       <c r="K465" s="2" t="n"/>
@@ -7998,8 +7992,8 @@
       <c r="D466" s="3" t="n"/>
       <c r="E466" s="3" t="n"/>
       <c r="F466" s="3" t="n"/>
-      <c r="G466" s="4" t="n"/>
-      <c r="H466" s="4" t="n"/>
+      <c r="G466" s="2" t="n"/>
+      <c r="H466" s="2" t="n"/>
       <c r="I466" s="3" t="n"/>
       <c r="J466" s="3" t="n"/>
       <c r="K466" s="2" t="n"/>
@@ -8014,8 +8008,8 @@
       <c r="D467" s="3" t="n"/>
       <c r="E467" s="3" t="n"/>
       <c r="F467" s="3" t="n"/>
-      <c r="G467" s="4" t="n"/>
-      <c r="H467" s="4" t="n"/>
+      <c r="G467" s="2" t="n"/>
+      <c r="H467" s="2" t="n"/>
       <c r="I467" s="3" t="n"/>
       <c r="J467" s="3" t="n"/>
       <c r="K467" s="2" t="n"/>
@@ -8030,8 +8024,8 @@
       <c r="D468" s="3" t="n"/>
       <c r="E468" s="3" t="n"/>
       <c r="F468" s="3" t="n"/>
-      <c r="G468" s="4" t="n"/>
-      <c r="H468" s="4" t="n"/>
+      <c r="G468" s="2" t="n"/>
+      <c r="H468" s="2" t="n"/>
       <c r="I468" s="3" t="n"/>
       <c r="J468" s="3" t="n"/>
       <c r="K468" s="2" t="n"/>
@@ -8046,8 +8040,8 @@
       <c r="D469" s="3" t="n"/>
       <c r="E469" s="3" t="n"/>
       <c r="F469" s="3" t="n"/>
-      <c r="G469" s="4" t="n"/>
-      <c r="H469" s="4" t="n"/>
+      <c r="G469" s="2" t="n"/>
+      <c r="H469" s="2" t="n"/>
       <c r="I469" s="3" t="n"/>
       <c r="J469" s="3" t="n"/>
       <c r="K469" s="2" t="n"/>
@@ -8062,8 +8056,8 @@
       <c r="D470" s="3" t="n"/>
       <c r="E470" s="3" t="n"/>
       <c r="F470" s="3" t="n"/>
-      <c r="G470" s="4" t="n"/>
-      <c r="H470" s="4" t="n"/>
+      <c r="G470" s="2" t="n"/>
+      <c r="H470" s="2" t="n"/>
       <c r="I470" s="3" t="n"/>
       <c r="J470" s="3" t="n"/>
       <c r="K470" s="2" t="n"/>
@@ -8078,8 +8072,8 @@
       <c r="D471" s="3" t="n"/>
       <c r="E471" s="3" t="n"/>
       <c r="F471" s="3" t="n"/>
-      <c r="G471" s="4" t="n"/>
-      <c r="H471" s="4" t="n"/>
+      <c r="G471" s="2" t="n"/>
+      <c r="H471" s="2" t="n"/>
       <c r="I471" s="3" t="n"/>
       <c r="J471" s="3" t="n"/>
       <c r="K471" s="2" t="n"/>
@@ -8094,8 +8088,8 @@
       <c r="D472" s="3" t="n"/>
       <c r="E472" s="3" t="n"/>
       <c r="F472" s="3" t="n"/>
-      <c r="G472" s="4" t="n"/>
-      <c r="H472" s="4" t="n"/>
+      <c r="G472" s="2" t="n"/>
+      <c r="H472" s="2" t="n"/>
       <c r="I472" s="3" t="n"/>
       <c r="J472" s="3" t="n"/>
       <c r="K472" s="2" t="n"/>
@@ -8110,8 +8104,8 @@
       <c r="D473" s="3" t="n"/>
       <c r="E473" s="3" t="n"/>
       <c r="F473" s="3" t="n"/>
-      <c r="G473" s="4" t="n"/>
-      <c r="H473" s="4" t="n"/>
+      <c r="G473" s="2" t="n"/>
+      <c r="H473" s="2" t="n"/>
       <c r="I473" s="3" t="n"/>
       <c r="J473" s="3" t="n"/>
       <c r="K473" s="2" t="n"/>
@@ -8126,8 +8120,8 @@
       <c r="D474" s="3" t="n"/>
       <c r="E474" s="3" t="n"/>
       <c r="F474" s="3" t="n"/>
-      <c r="G474" s="4" t="n"/>
-      <c r="H474" s="4" t="n"/>
+      <c r="G474" s="2" t="n"/>
+      <c r="H474" s="2" t="n"/>
       <c r="I474" s="3" t="n"/>
       <c r="J474" s="3" t="n"/>
       <c r="K474" s="2" t="n"/>
@@ -8142,8 +8136,8 @@
       <c r="D475" s="3" t="n"/>
       <c r="E475" s="3" t="n"/>
       <c r="F475" s="3" t="n"/>
-      <c r="G475" s="4" t="n"/>
-      <c r="H475" s="4" t="n"/>
+      <c r="G475" s="2" t="n"/>
+      <c r="H475" s="2" t="n"/>
       <c r="I475" s="3" t="n"/>
       <c r="J475" s="3" t="n"/>
       <c r="K475" s="2" t="n"/>
@@ -8158,8 +8152,8 @@
       <c r="D476" s="3" t="n"/>
       <c r="E476" s="3" t="n"/>
       <c r="F476" s="3" t="n"/>
-      <c r="G476" s="4" t="n"/>
-      <c r="H476" s="4" t="n"/>
+      <c r="G476" s="2" t="n"/>
+      <c r="H476" s="2" t="n"/>
       <c r="I476" s="3" t="n"/>
       <c r="J476" s="3" t="n"/>
       <c r="K476" s="2" t="n"/>
@@ -8174,8 +8168,8 @@
       <c r="D477" s="3" t="n"/>
       <c r="E477" s="3" t="n"/>
       <c r="F477" s="3" t="n"/>
-      <c r="G477" s="4" t="n"/>
-      <c r="H477" s="4" t="n"/>
+      <c r="G477" s="2" t="n"/>
+      <c r="H477" s="2" t="n"/>
       <c r="I477" s="3" t="n"/>
       <c r="J477" s="3" t="n"/>
       <c r="K477" s="2" t="n"/>
@@ -8190,8 +8184,8 @@
       <c r="D478" s="3" t="n"/>
       <c r="E478" s="3" t="n"/>
       <c r="F478" s="3" t="n"/>
-      <c r="G478" s="4" t="n"/>
-      <c r="H478" s="4" t="n"/>
+      <c r="G478" s="2" t="n"/>
+      <c r="H478" s="2" t="n"/>
       <c r="I478" s="3" t="n"/>
       <c r="J478" s="3" t="n"/>
       <c r="K478" s="2" t="n"/>
@@ -8206,8 +8200,8 @@
       <c r="D479" s="3" t="n"/>
       <c r="E479" s="3" t="n"/>
       <c r="F479" s="3" t="n"/>
-      <c r="G479" s="4" t="n"/>
-      <c r="H479" s="4" t="n"/>
+      <c r="G479" s="2" t="n"/>
+      <c r="H479" s="2" t="n"/>
       <c r="I479" s="3" t="n"/>
       <c r="J479" s="3" t="n"/>
       <c r="K479" s="2" t="n"/>
@@ -8222,8 +8216,8 @@
       <c r="D480" s="3" t="n"/>
       <c r="E480" s="3" t="n"/>
       <c r="F480" s="3" t="n"/>
-      <c r="G480" s="4" t="n"/>
-      <c r="H480" s="4" t="n"/>
+      <c r="G480" s="2" t="n"/>
+      <c r="H480" s="2" t="n"/>
       <c r="I480" s="3" t="n"/>
       <c r="J480" s="3" t="n"/>
       <c r="K480" s="2" t="n"/>
@@ -8238,8 +8232,8 @@
       <c r="D481" s="3" t="n"/>
       <c r="E481" s="3" t="n"/>
       <c r="F481" s="3" t="n"/>
-      <c r="G481" s="4" t="n"/>
-      <c r="H481" s="4" t="n"/>
+      <c r="G481" s="2" t="n"/>
+      <c r="H481" s="2" t="n"/>
       <c r="I481" s="3" t="n"/>
       <c r="J481" s="3" t="n"/>
       <c r="K481" s="2" t="n"/>
@@ -8254,8 +8248,8 @@
       <c r="D482" s="3" t="n"/>
       <c r="E482" s="3" t="n"/>
       <c r="F482" s="3" t="n"/>
-      <c r="G482" s="4" t="n"/>
-      <c r="H482" s="4" t="n"/>
+      <c r="G482" s="2" t="n"/>
+      <c r="H482" s="2" t="n"/>
       <c r="I482" s="3" t="n"/>
       <c r="J482" s="3" t="n"/>
       <c r="K482" s="2" t="n"/>
@@ -8270,8 +8264,8 @@
       <c r="D483" s="3" t="n"/>
       <c r="E483" s="3" t="n"/>
       <c r="F483" s="3" t="n"/>
-      <c r="G483" s="4" t="n"/>
-      <c r="H483" s="4" t="n"/>
+      <c r="G483" s="2" t="n"/>
+      <c r="H483" s="2" t="n"/>
       <c r="I483" s="3" t="n"/>
       <c r="J483" s="3" t="n"/>
       <c r="K483" s="2" t="n"/>
@@ -8286,8 +8280,8 @@
       <c r="D484" s="3" t="n"/>
       <c r="E484" s="3" t="n"/>
       <c r="F484" s="3" t="n"/>
-      <c r="G484" s="4" t="n"/>
-      <c r="H484" s="4" t="n"/>
+      <c r="G484" s="2" t="n"/>
+      <c r="H484" s="2" t="n"/>
       <c r="I484" s="3" t="n"/>
       <c r="J484" s="3" t="n"/>
       <c r="K484" s="2" t="n"/>
@@ -8302,8 +8296,8 @@
       <c r="D485" s="3" t="n"/>
       <c r="E485" s="3" t="n"/>
       <c r="F485" s="3" t="n"/>
-      <c r="G485" s="4" t="n"/>
-      <c r="H485" s="4" t="n"/>
+      <c r="G485" s="2" t="n"/>
+      <c r="H485" s="2" t="n"/>
       <c r="I485" s="3" t="n"/>
       <c r="J485" s="3" t="n"/>
       <c r="K485" s="2" t="n"/>
@@ -8318,8 +8312,8 @@
       <c r="D486" s="3" t="n"/>
       <c r="E486" s="3" t="n"/>
       <c r="F486" s="3" t="n"/>
-      <c r="G486" s="4" t="n"/>
-      <c r="H486" s="4" t="n"/>
+      <c r="G486" s="2" t="n"/>
+      <c r="H486" s="2" t="n"/>
       <c r="I486" s="3" t="n"/>
       <c r="J486" s="3" t="n"/>
       <c r="K486" s="2" t="n"/>
@@ -8334,8 +8328,8 @@
       <c r="D487" s="3" t="n"/>
       <c r="E487" s="3" t="n"/>
       <c r="F487" s="3" t="n"/>
-      <c r="G487" s="4" t="n"/>
-      <c r="H487" s="4" t="n"/>
+      <c r="G487" s="2" t="n"/>
+      <c r="H487" s="2" t="n"/>
       <c r="I487" s="3" t="n"/>
       <c r="J487" s="3" t="n"/>
       <c r="K487" s="2" t="n"/>
@@ -8350,8 +8344,8 @@
       <c r="D488" s="3" t="n"/>
       <c r="E488" s="3" t="n"/>
       <c r="F488" s="3" t="n"/>
-      <c r="G488" s="4" t="n"/>
-      <c r="H488" s="4" t="n"/>
+      <c r="G488" s="2" t="n"/>
+      <c r="H488" s="2" t="n"/>
       <c r="I488" s="3" t="n"/>
       <c r="J488" s="3" t="n"/>
       <c r="K488" s="2" t="n"/>
@@ -8366,8 +8360,8 @@
       <c r="D489" s="3" t="n"/>
       <c r="E489" s="3" t="n"/>
       <c r="F489" s="3" t="n"/>
-      <c r="G489" s="4" t="n"/>
-      <c r="H489" s="4" t="n"/>
+      <c r="G489" s="2" t="n"/>
+      <c r="H489" s="2" t="n"/>
       <c r="I489" s="3" t="n"/>
       <c r="J489" s="3" t="n"/>
       <c r="K489" s="2" t="n"/>
@@ -8382,8 +8376,8 @@
       <c r="D490" s="3" t="n"/>
       <c r="E490" s="3" t="n"/>
       <c r="F490" s="3" t="n"/>
-      <c r="G490" s="4" t="n"/>
-      <c r="H490" s="4" t="n"/>
+      <c r="G490" s="2" t="n"/>
+      <c r="H490" s="2" t="n"/>
       <c r="I490" s="3" t="n"/>
       <c r="J490" s="3" t="n"/>
       <c r="K490" s="2" t="n"/>
@@ -8398,8 +8392,8 @@
       <c r="D491" s="3" t="n"/>
       <c r="E491" s="3" t="n"/>
       <c r="F491" s="3" t="n"/>
-      <c r="G491" s="4" t="n"/>
-      <c r="H491" s="4" t="n"/>
+      <c r="G491" s="2" t="n"/>
+      <c r="H491" s="2" t="n"/>
       <c r="I491" s="3" t="n"/>
       <c r="J491" s="3" t="n"/>
       <c r="K491" s="2" t="n"/>
@@ -8414,8 +8408,8 @@
       <c r="D492" s="3" t="n"/>
       <c r="E492" s="3" t="n"/>
       <c r="F492" s="3" t="n"/>
-      <c r="G492" s="4" t="n"/>
-      <c r="H492" s="4" t="n"/>
+      <c r="G492" s="2" t="n"/>
+      <c r="H492" s="2" t="n"/>
       <c r="I492" s="3" t="n"/>
       <c r="J492" s="3" t="n"/>
       <c r="K492" s="2" t="n"/>
@@ -8430,8 +8424,8 @@
       <c r="D493" s="3" t="n"/>
       <c r="E493" s="3" t="n"/>
       <c r="F493" s="3" t="n"/>
-      <c r="G493" s="4" t="n"/>
-      <c r="H493" s="4" t="n"/>
+      <c r="G493" s="2" t="n"/>
+      <c r="H493" s="2" t="n"/>
       <c r="I493" s="3" t="n"/>
       <c r="J493" s="3" t="n"/>
       <c r="K493" s="2" t="n"/>
@@ -8446,8 +8440,8 @@
       <c r="D494" s="3" t="n"/>
       <c r="E494" s="3" t="n"/>
       <c r="F494" s="3" t="n"/>
-      <c r="G494" s="4" t="n"/>
-      <c r="H494" s="4" t="n"/>
+      <c r="G494" s="2" t="n"/>
+      <c r="H494" s="2" t="n"/>
       <c r="I494" s="3" t="n"/>
       <c r="J494" s="3" t="n"/>
       <c r="K494" s="2" t="n"/>
@@ -8462,8 +8456,8 @@
       <c r="D495" s="3" t="n"/>
       <c r="E495" s="3" t="n"/>
       <c r="F495" s="3" t="n"/>
-      <c r="G495" s="4" t="n"/>
-      <c r="H495" s="4" t="n"/>
+      <c r="G495" s="2" t="n"/>
+      <c r="H495" s="2" t="n"/>
       <c r="I495" s="3" t="n"/>
       <c r="J495" s="3" t="n"/>
       <c r="K495" s="2" t="n"/>
@@ -8478,8 +8472,8 @@
       <c r="D496" s="3" t="n"/>
       <c r="E496" s="3" t="n"/>
       <c r="F496" s="3" t="n"/>
-      <c r="G496" s="4" t="n"/>
-      <c r="H496" s="4" t="n"/>
+      <c r="G496" s="2" t="n"/>
+      <c r="H496" s="2" t="n"/>
       <c r="I496" s="3" t="n"/>
       <c r="J496" s="3" t="n"/>
       <c r="K496" s="2" t="n"/>
@@ -8494,8 +8488,8 @@
       <c r="D497" s="3" t="n"/>
       <c r="E497" s="3" t="n"/>
       <c r="F497" s="3" t="n"/>
-      <c r="G497" s="4" t="n"/>
-      <c r="H497" s="4" t="n"/>
+      <c r="G497" s="2" t="n"/>
+      <c r="H497" s="2" t="n"/>
       <c r="I497" s="3" t="n"/>
       <c r="J497" s="3" t="n"/>
       <c r="K497" s="2" t="n"/>
@@ -8510,8 +8504,8 @@
       <c r="D498" s="3" t="n"/>
       <c r="E498" s="3" t="n"/>
       <c r="F498" s="3" t="n"/>
-      <c r="G498" s="4" t="n"/>
-      <c r="H498" s="4" t="n"/>
+      <c r="G498" s="2" t="n"/>
+      <c r="H498" s="2" t="n"/>
       <c r="I498" s="3" t="n"/>
       <c r="J498" s="3" t="n"/>
       <c r="K498" s="2" t="n"/>
@@ -8526,8 +8520,8 @@
       <c r="D499" s="3" t="n"/>
       <c r="E499" s="3" t="n"/>
       <c r="F499" s="3" t="n"/>
-      <c r="G499" s="4" t="n"/>
-      <c r="H499" s="4" t="n"/>
+      <c r="G499" s="2" t="n"/>
+      <c r="H499" s="2" t="n"/>
       <c r="I499" s="3" t="n"/>
       <c r="J499" s="3" t="n"/>
       <c r="K499" s="2" t="n"/>
@@ -8542,8 +8536,8 @@
       <c r="D500" s="3" t="n"/>
       <c r="E500" s="3" t="n"/>
       <c r="F500" s="3" t="n"/>
-      <c r="G500" s="4" t="n"/>
-      <c r="H500" s="4" t="n"/>
+      <c r="G500" s="2" t="n"/>
+      <c r="H500" s="2" t="n"/>
       <c r="I500" s="3" t="n"/>
       <c r="J500" s="3" t="n"/>
       <c r="K500" s="2" t="n"/>
@@ -8558,8 +8552,8 @@
       <c r="D501" s="3" t="n"/>
       <c r="E501" s="3" t="n"/>
       <c r="F501" s="3" t="n"/>
-      <c r="G501" s="4" t="n"/>
-      <c r="H501" s="4" t="n"/>
+      <c r="G501" s="2" t="n"/>
+      <c r="H501" s="2" t="n"/>
       <c r="I501" s="3" t="n"/>
       <c r="J501" s="3" t="n"/>
       <c r="K501" s="2" t="n"/>
@@ -8572,7 +8566,7 @@
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(D2&lt;&gt;"",COUNTIF(Options4,D2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="15" dxfId="1">
+    <cfRule type="expression" priority="17" dxfId="1">
       <formula>AND(COUNTA($A2:$N2)&gt;0,D2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8580,10 +8574,10 @@
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(E2&lt;&gt;"",COUNTIF(Options5,E2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="16" dxfId="1">
+    <cfRule type="expression" priority="18" dxfId="1">
       <formula>AND(COUNTA($A2:$N2)&gt;0,E2="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="23" dxfId="0">
+    <cfRule type="expression" priority="25" dxfId="0">
       <formula>OR(AND(E2="CEO",D2&lt;&gt;"Phòng BOD"),AND(E2="CEO",COUNTIF($E$2:$E$501,"CEO")&gt;1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8591,7 +8585,7 @@
     <cfRule type="expression" priority="3" dxfId="0">
       <formula>AND(F2&lt;&gt;"",COUNTIF(Options6,F2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="17" dxfId="1">
+    <cfRule type="expression" priority="19" dxfId="1">
       <formula>AND(COUNTA($A2:$N2)&gt;0,F2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8599,7 +8593,7 @@
     <cfRule type="expression" priority="4" dxfId="0">
       <formula>AND(I2&lt;&gt;"",COUNTIF(Options9,I2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="19" dxfId="1">
+    <cfRule type="expression" priority="21" dxfId="1">
       <formula>AND(COUNTA($A2:$N2)&gt;0,I2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8607,7 +8601,7 @@
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(J2&lt;&gt;"",COUNTIF(Options10,J2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="20" dxfId="1">
+    <cfRule type="expression" priority="22" dxfId="1">
       <formula>AND(COUNTA($A2:$N2)&gt;0,J2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8615,7 +8609,7 @@
     <cfRule type="expression" priority="6" dxfId="0">
       <formula>AND(A2&lt;&gt;"",NOT(AND(LEN(A2)&gt;0,LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(A2,"0",""),"1",""),"2",""),"3",""),"4",""),"5",""),"6",""),"7",""),"8",""),"9",""))=0,COUNTIF($A$2:$A$501,A2)=1)))</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" dxfId="1">
+    <cfRule type="expression" priority="14" dxfId="1">
       <formula>AND(COUNTA($A2:$N2)&gt;0,A2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8623,7 +8617,7 @@
     <cfRule type="expression" priority="7" dxfId="0">
       <formula>AND(B2&lt;&gt;"",NOT(AND(LEN(TRIM(B2))&gt;=2,LEN(B2)&lt;=100)))</formula>
     </cfRule>
-    <cfRule type="expression" priority="13" dxfId="1">
+    <cfRule type="expression" priority="15" dxfId="1">
       <formula>AND(COUNTA($A2:$N2)&gt;0,B2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8631,7 +8625,7 @@
     <cfRule type="expression" priority="8" dxfId="0">
       <formula>AND(C2&lt;&gt;"",NOT(AND(LEN(TRIM(C2))&gt;=2,LEN(C2)&lt;=100)))</formula>
     </cfRule>
-    <cfRule type="expression" priority="14" dxfId="1">
+    <cfRule type="expression" priority="16" dxfId="1">
       <formula>AND(COUNTA($A2:$N2)&gt;0,C2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8639,7 +8633,7 @@
     <cfRule type="expression" priority="9" dxfId="0">
       <formula>AND(K2&lt;&gt;"",NOT(AND(LEN(K2)&gt;12,RIGHT(LOWER(K2),12)="@asiafnb.com",LEN(K2)-LEN(SUBSTITUTE(K2,"@",""))=1,ISERROR(SEARCH(" ",K2)))))</formula>
     </cfRule>
-    <cfRule type="expression" priority="21" dxfId="1">
+    <cfRule type="expression" priority="23" dxfId="1">
       <formula>AND(COUNTA($A2:$N2)&gt;0,K2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8647,7 +8641,7 @@
     <cfRule type="expression" priority="10" dxfId="0">
       <formula>AND(L2&lt;&gt;"",NOT(AND(LEN(L2)=10,LEFT(L2,1)="0",ISNUMBER(FIND(MID(L2,2,1),"35789")),LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(L2,"0",""),"1",""),"2",""),"3",""),"4",""),"5",""),"6",""),"7",""),"8",""),"9",""))=0)))</formula>
     </cfRule>
-    <cfRule type="expression" priority="22" dxfId="1">
+    <cfRule type="expression" priority="24" dxfId="1">
       <formula>AND(COUNTA($A2:$N2)&gt;0,L2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8657,8 +8651,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G501">
-    <cfRule type="expression" priority="18" dxfId="1">
+    <cfRule type="expression" priority="12" dxfId="0">
+      <formula>AND(G2&lt;&gt;"",NOT(IFERROR(AND(ISTEXT(G2),LEN(G2)=10,MID(G2,3,1)="/",MID(G2,6,1)="/",VALUE(RIGHT(G2,4))&gt;=1900,VALUE(RIGHT(G2,4))&lt;=2100,TEXT(DATE(VALUE(RIGHT(G2,4)),VALUE(MID(G2,4,2)),VALUE(LEFT(G2,2))),"dd/mm/yyyy")=G2),FALSE)))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="20" dxfId="1">
       <formula>AND(COUNTA($A2:$N2)&gt;0,G2="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H501">
+    <cfRule type="expression" priority="13" dxfId="0">
+      <formula>AND(H2&lt;&gt;"",NOT(IFERROR(AND(ISTEXT(H2),LEN(H2)=10,MID(H2,3,1)="/",MID(H2,6,1)="/",VALUE(RIGHT(H2,4))&gt;=1900,VALUE(RIGHT(H2,4))&lt;=2100,TEXT(DATE(VALUE(RIGHT(H2,4)),VALUE(MID(H2,4,2)),VALUE(LEFT(H2,2))),"dd/mm/yyyy")=H2),FALSE)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="13">
@@ -8695,13 +8697,11 @@
     <dataValidation sqref="N2:N501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Thông tin chưa hợp lệ" error="Mô tả tối đa 2.000 ký tự." promptTitle="Nhập thông tin" prompt="Mô tả tối đa 2.000 ký tự." type="custom" errorStyle="stop">
       <formula1>LEN(N2)&lt;=2000</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Thông tin chưa hợp lệ" error="Nhập ngày hợp lệ theo DD/MM/YYYY." promptTitle="Nhập thông tin" prompt="Nhập ngày hợp lệ theo DD/MM/YYYY." type="date" errorStyle="stop" operator="between">
-      <formula1>DATE(1900,1,1)</formula1>
-      <formula2>DATE(2100,12,31)</formula2>
+    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Thông tin chưa hợp lệ" error="Nhập ngày dưới dạng DD/MM/YYYY, ví dụ 25/10/2005." promptTitle="Nhập thông tin" prompt="Nhập ngày dưới dạng DD/MM/YYYY, ví dụ 25/10/2005." type="custom" errorStyle="stop">
+      <formula1>IFERROR(AND(ISTEXT(G2),LEN(G2)=10,MID(G2,3,1)="/",MID(G2,6,1)="/",VALUE(RIGHT(G2,4))&gt;=1900,VALUE(RIGHT(G2,4))&lt;=2100,TEXT(DATE(VALUE(RIGHT(G2,4)),VALUE(MID(G2,4,2)),VALUE(LEFT(G2,2))),"dd/mm/yyyy")=G2),FALSE)</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Thông tin chưa hợp lệ" error="Nhập ngày hợp lệ theo DD/MM/YYYY." promptTitle="Nhập thông tin" prompt="Nhập ngày hợp lệ theo DD/MM/YYYY." type="date" errorStyle="stop" operator="between">
-      <formula1>DATE(1900,1,1)</formula1>
-      <formula2>DATE(2100,12,31)</formula2>
+    <dataValidation sqref="H2:H501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Thông tin chưa hợp lệ" error="Nhập ngày dưới dạng DD/MM/YYYY, ví dụ 25/10/2005." promptTitle="Nhập thông tin" prompt="Nhập ngày dưới dạng DD/MM/YYYY, ví dụ 25/10/2005." type="custom" errorStyle="stop">
+      <formula1>IFERROR(AND(ISTEXT(H2),LEN(H2)=10,MID(H2,3,1)="/",MID(H2,6,1)="/",VALUE(RIGHT(H2,4))&gt;=1900,VALUE(RIGHT(H2,4))&lt;=2100,TEXT(DATE(VALUE(RIGHT(H2,4)),VALUE(MID(H2,4,2)),VALUE(LEFT(H2,2))),"dd/mm/yyyy")=H2),FALSE)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8734,108 +8734,108 @@
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Cách dùng</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Điền sheet Nhập nhân viên từ dòng 2. Mỗi dòng một người. Không sửa tên hoặc thứ tự cột. Tối đa 500 nhân viên.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Danh sách chọn</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Chọn phòng ban, cấp bậc, giới tính, địa điểm và trạng thái từ danh sách trong ô.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Kiểm tra</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Dấu * là bắt buộc. Mã, email và số điện thoại không được trùng nhau hoặc trùng hồ sơ hiện có, kể cả thùng rác. Nếu một dòng sai, toàn bộ file không được nhập.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Mã và điện thoại</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Nhập dưới dạng văn bản để giữ số 0 đầu. Mã nhân viên chỉ gồm chữ số.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Ngày tháng</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Nhập DD/MM/YYYY. Ngày gia nhập bắt buộc; ngày sinh tùy chọn.</t>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Nhập trực tiếp dưới dạng văn bản DD/MM/YYYY, ví dụ 25/10/2005 hoặc 01/02/2026. Không đổi định dạng ô sang Date. Ngày gia nhập bắt buộc; ngày sinh tùy chọn.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Cấp bậc</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>CEO phải thuộc Phòng BOD. Công ty chỉ có một CEO.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Ảnh</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Để trống cột ảnh; cập nhật ảnh trong trang chỉnh sửa sau khi nhập.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Văn bản thuần, tối đa 2.000 ký tự.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Sheet Ví dụ chỉ minh họa, không được nhập. Điền dữ liệu vào sheet Nhập nhân viên.</t>
         </is>
@@ -8878,510 +8878,510 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Phòng BOD</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>BOD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Phòng Kinh doanh quốc tế</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>INTERNATIONAL_SALES</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Phòng Kinh doanh nội địa</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>DOMESTIC_SALES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Phòng Sales Admin</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>SALES_ADMIN</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Phòng Marketing &amp; Truyền thông</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>MARKETING_COMMUNICATIONS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Phòng Thiết kế</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>DESIGN</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Phòng Operations Admin</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>OPERATIONS_ADMIN</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Phòng Mua hàng / Sourcing</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>SOURCING_PURCHASING</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Phòng Logistics / XNK</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>LOGISTICS_IMPORT_EXPORT</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Phòng Kho / Inventory</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>INVENTORY</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Phòng R&amp;D / Product Development</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>PRODUCT_DEVELOPMENT</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Phòng RA / Compliance</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>RA_COMPLIANCE</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Phòng Tài chính – Kế toán</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>FINANCE_ACCOUNTING</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Phòng Nhân sự &amp; Hành chính</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>HR_ADMIN</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Phòng Pháp chế</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Phòng ban</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Phòng IT + ERP</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>IT_ERP</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Cấp bậc</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Cấp bậc</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Quản lý cấp cao</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Senior Management</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Cấp bậc</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Quản lý cấp trung</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Middle Management</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Cấp bậc</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Nhân sự cấp trung</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Intermediate Personnel</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Cấp bậc</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Chuyên viên/Nhân viên</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Giới tính</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Nam</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Giới tính</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Nữ</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Giới tính</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Khác</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Văn phòng / Địa điểm làm việc</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Văn Phòng Á Châu Dĩ An</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Văn Phòng Á Châu Dĩ An</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Văn phòng / Địa điểm làm việc</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Bình Dương (Nhà máy số 1)</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Bình Dương</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Văn phòng / Địa điểm làm việc</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Long An (Nhà máy số 2)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Long An</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Trạng thái làm việc</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Đang làm việc</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Trạng thái làm việc</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Thử việc</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>probation</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Trạng thái làm việc</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Đã nghỉ việc</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>inactive</t>
         </is>
@@ -9490,62 +9490,64 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>000123</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Nguyễn Văn An</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Chuyên viên nhân sự</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Phòng Nhân sự &amp; Hành chính</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Chuyên viên/Nhân viên</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Nam</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>46296</v>
-      </c>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>Văn Phòng Á Châu Dĩ An</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Đang làm việc</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>nguyenvanan@asiafnb.com</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>0901234567</t>
         </is>
       </c>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>Phụ trách tuyển dụng.</t>
         </is>
